--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
-  </si>
-  <si>
-    <t>04.09.202648</t>
-  </si>
-  <si>
-    <t>04.09.202649</t>
-  </si>
-  <si>
-    <t>04.09.202650</t>
-  </si>
-  <si>
-    <t>04.09.202651</t>
-  </si>
-  <si>
-    <t>04.09.202652</t>
-  </si>
-  <si>
-    <t>04.09.202653</t>
-  </si>
-  <si>
-    <t>04.09.202654</t>
-  </si>
-  <si>
-    <t>04.09.202655</t>
-  </si>
-  <si>
-    <t>04.09.202656</t>
-  </si>
-  <si>
-    <t>04.09.202657</t>
-  </si>
-  <si>
-    <t>04.09.202658</t>
-  </si>
-  <si>
-    <t>04.09.202659</t>
-  </si>
-  <si>
-    <t>04.09.202660</t>
-  </si>
-  <si>
-    <t>04.09.202661</t>
-  </si>
-  <si>
-    <t>04.09.202662</t>
-  </si>
-  <si>
-    <t>04.09.202663</t>
-  </si>
-  <si>
-    <t>04.09.202664</t>
-  </si>
-  <si>
-    <t>04.09.202665</t>
-  </si>
-  <si>
-    <t>04.09.202666</t>
-  </si>
-  <si>
-    <t>04.09.202667</t>
-  </si>
-  <si>
-    <t>04.09.202668</t>
-  </si>
-  <si>
-    <t>04.09.202669</t>
-  </si>
-  <si>
-    <t>04.09.202670</t>
-  </si>
-  <si>
-    <t>04.09.202671</t>
-  </si>
-  <si>
-    <t>04.09.202672</t>
-  </si>
-  <si>
-    <t>04.09.202673</t>
-  </si>
-  <si>
-    <t>04.09.202674</t>
-  </si>
-  <si>
-    <t>04.09.202675</t>
-  </si>
-  <si>
-    <t>04.09.202676</t>
-  </si>
-  <si>
-    <t>04.09.202677</t>
-  </si>
-  <si>
-    <t>04.09.202678</t>
-  </si>
-  <si>
-    <t>04.09.202679</t>
-  </si>
-  <si>
-    <t>04.09.202680</t>
-  </si>
-  <si>
-    <t>04.09.202681</t>
-  </si>
-  <si>
-    <t>04.09.202682</t>
-  </si>
-  <si>
-    <t>04.09.202683</t>
-  </si>
-  <si>
-    <t>04.09.202684</t>
-  </si>
-  <si>
-    <t>04.09.202685</t>
-  </si>
-  <si>
-    <t>04.09.202686</t>
-  </si>
-  <si>
-    <t>04.09.202687</t>
-  </si>
-  <si>
-    <t>04.09.202688</t>
-  </si>
-  <si>
-    <t>04.09.202689</t>
-  </si>
-  <si>
-    <t>04.09.202690</t>
-  </si>
-  <si>
-    <t>04.09.202691</t>
-  </si>
-  <si>
-    <t>04.09.202692</t>
-  </si>
-  <si>
-    <t>04.09.202693</t>
-  </si>
-  <si>
-    <t>04.09.202694</t>
-  </si>
-  <si>
-    <t>04.09.202695</t>
-  </si>
-  <si>
-    <t>04.09.202696</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
+  </si>
+  <si>
+    <t>13.09.202691</t>
+  </si>
+  <si>
+    <t>13.09.202692</t>
+  </si>
+  <si>
+    <t>13.09.202693</t>
+  </si>
+  <si>
+    <t>13.09.202694</t>
+  </si>
+  <si>
+    <t>13.09.202695</t>
+  </si>
+  <si>
+    <t>13.09.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>5410</v>
+        <v>5230</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>5370</v>
+        <v>5190</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>5340</v>
+        <v>5160</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>5300</v>
+        <v>5140</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>5270</v>
+        <v>5090</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>5240</v>
+        <v>5070</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>5230</v>
+        <v>5070</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>5240</v>
+        <v>5060</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>5250</v>
+        <v>5030</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>5270</v>
+        <v>5020</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>5280</v>
+        <v>5020</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>5290</v>
+        <v>5020</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>5290</v>
+        <v>5030</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>5290</v>
+        <v>5030</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>5300</v>
+        <v>5030</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>5310</v>
+        <v>5030</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>5330</v>
+        <v>5030</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>5370</v>
+        <v>5050</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>5430</v>
+        <v>5080</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>5500</v>
+        <v>5110</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>5590</v>
+        <v>5160</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>5680</v>
+        <v>5200</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>5780</v>
+        <v>5230</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>5870</v>
+        <v>5280</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>5970</v>
+        <v>5340</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>6050</v>
+        <v>5370</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>6120</v>
+        <v>5400</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>6170</v>
+        <v>5420</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>6210</v>
+        <v>5450</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>6230</v>
+        <v>5450</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>6230</v>
+        <v>5450</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>6210</v>
+        <v>5450</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>6170</v>
+        <v>5420</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>6110</v>
+        <v>5370</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>6030</v>
+        <v>5300</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>5940</v>
+        <v>5220</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>5840</v>
+        <v>5120</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>5740</v>
+        <v>5020</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>5630</v>
+        <v>4960</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>5530</v>
+        <v>4880</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>5440</v>
+        <v>4810</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>5370</v>
+        <v>4760</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>5320</v>
+        <v>4730</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>5290</v>
+        <v>4710</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>5280</v>
+        <v>4680</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>5290</v>
+        <v>4680</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>5310</v>
+        <v>4680</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>5350</v>
+        <v>4680</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>5390</v>
+        <v>4660</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>5440</v>
+        <v>4650</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>5480</v>
+        <v>4650</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>5520</v>
+        <v>4650</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>5570</v>
+        <v>4650</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>5590</v>
+        <v>4650</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>5610</v>
+        <v>4670</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>5630</v>
+        <v>4740</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>5650</v>
+        <v>4780</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>5680</v>
+        <v>4810</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>5730</v>
+        <v>4860</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>5790</v>
+        <v>4930</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>5860</v>
+        <v>5000</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>5940</v>
+        <v>5080</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>6030</v>
+        <v>5190</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>6120</v>
+        <v>5310</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>6210</v>
+        <v>5440</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>6300</v>
+        <v>5560</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>6380</v>
+        <v>5700</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>6460</v>
+        <v>5840</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>6540</v>
+        <v>5960</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>6620</v>
+        <v>6080</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>6710</v>
+        <v>6200</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>6800</v>
+        <v>6300</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>6880</v>
+        <v>6410</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>6950</v>
+        <v>6510</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>7020</v>
+        <v>6580</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>7080</v>
+        <v>6640</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>7140</v>
+        <v>6670</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>7160</v>
+        <v>6660</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>7150</v>
+        <v>6630</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>7090</v>
+        <v>6540</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>7000</v>
+        <v>6450</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>6900</v>
+        <v>6360</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>6750</v>
+        <v>6250</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>6600</v>
+        <v>6110</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>6480</v>
+        <v>5970</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>6350</v>
+        <v>5830</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>6210</v>
+        <v>5710</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>6080</v>
+        <v>5610</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>5940</v>
+        <v>5500</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>5820</v>
+        <v>5390</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>5700</v>
+        <v>5280</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>5600</v>
+        <v>5220</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>5520</v>
+        <v>5150</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>5470</v>
+        <v>5080</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>5410</v>
+        <v>5030</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>5360</v>
+        <v>4970</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>5300</v>
+        <v>4910</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>5260</v>
+        <v>4870</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>5220</v>
+        <v>4830</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>5180</v>
+        <v>4770</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>5170</v>
+        <v>4750</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>5170</v>
+        <v>4730</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>5180</v>
+        <v>4720</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>5200</v>
+        <v>4710</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>5220</v>
+        <v>4710</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>5240</v>
+        <v>4710</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>5250</v>
+        <v>4700</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>5260</v>
+        <v>4700</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>5280</v>
+        <v>4700</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>5310</v>
+        <v>4700</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>5350</v>
+        <v>4710</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>5390</v>
+        <v>4720</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>5430</v>
+        <v>4740</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>5490</v>
+        <v>4760</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>5550</v>
+        <v>4780</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>5620</v>
+        <v>4790</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>5700</v>
+        <v>4800</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>5790</v>
+        <v>4820</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>5870</v>
+        <v>4830</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>5940</v>
+        <v>4840</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>6000</v>
+        <v>4840</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>6040</v>
+        <v>4830</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>6050</v>
+        <v>4800</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>6040</v>
+        <v>4770</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>5990</v>
+        <v>4730</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>5910</v>
+        <v>4680</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>5800</v>
+        <v>4630</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>5670</v>
+        <v>4570</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B132">
-        <v>5530</v>
+        <v>4500</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B133">
-        <v>5370</v>
+        <v>4450</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B134">
-        <v>5210</v>
+        <v>4410</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B135">
-        <v>5050</v>
+        <v>4360</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B136">
-        <v>4910</v>
+        <v>4320</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B137">
-        <v>4790</v>
+        <v>4290</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B138">
-        <v>4690</v>
+        <v>4260</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B139">
-        <v>4620</v>
+        <v>4240</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B140">
-        <v>4570</v>
+        <v>4230</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B141">
-        <v>4540</v>
+        <v>4220</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B142">
-        <v>4540</v>
+        <v>4210</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B143">
-        <v>4550</v>
+        <v>4210</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B144">
-        <v>4570</v>
+        <v>4220</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B145">
-        <v>4600</v>
+        <v>4220</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B146">
-        <v>4630</v>
+        <v>4230</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B147">
-        <v>4660</v>
+        <v>4240</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B148">
-        <v>4690</v>
+        <v>4250</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B149">
-        <v>4720</v>
+        <v>4260</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B150">
-        <v>4750</v>
+        <v>4270</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B151">
-        <v>4770</v>
+        <v>4280</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B152">
-        <v>4800</v>
+        <v>4280</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B153">
-        <v>4820</v>
+        <v>4290</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B154">
-        <v>4860</v>
+        <v>4300</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B155">
-        <v>4900</v>
+        <v>4310</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B156">
-        <v>4960</v>
+        <v>4330</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B157">
-        <v>5030</v>
+        <v>4370</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B158">
-        <v>5110</v>
+        <v>4430</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B159">
-        <v>5200</v>
+        <v>4510</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B160">
-        <v>5310</v>
+        <v>4610</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B161">
-        <v>5420</v>
+        <v>4740</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B162">
-        <v>5540</v>
+        <v>4890</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B163">
-        <v>5670</v>
+        <v>5040</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B164">
-        <v>5810</v>
+        <v>5200</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B165">
-        <v>5950</v>
+        <v>5340</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B166">
-        <v>6090</v>
+        <v>5480</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B167">
-        <v>6230</v>
+        <v>5600</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B168">
-        <v>6360</v>
+        <v>5710</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B169">
-        <v>6480</v>
+        <v>5810</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B170">
-        <v>6580</v>
+        <v>5900</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B171">
-        <v>6670</v>
+        <v>5980</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B172">
-        <v>6760</v>
+        <v>6040</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B173">
-        <v>6850</v>
+        <v>6080</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B174">
-        <v>6900</v>
+        <v>6120</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B175">
-        <v>6940</v>
+        <v>6140</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B176">
-        <v>6970</v>
+        <v>6140</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B177">
-        <v>6950</v>
+        <v>6110</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B178">
-        <v>6910</v>
+        <v>6060</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B179">
-        <v>6840</v>
+        <v>6000</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B180">
-        <v>6750</v>
+        <v>5930</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B181">
-        <v>6650</v>
+        <v>5830</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B182">
-        <v>6530</v>
+        <v>5720</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B183">
-        <v>6400</v>
+        <v>5610</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B184">
-        <v>6270</v>
+        <v>5500</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B185">
-        <v>6150</v>
+        <v>5420</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B186">
-        <v>6060</v>
+        <v>5320</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B187">
-        <v>5940</v>
+        <v>5220</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B188">
-        <v>5850</v>
+        <v>5120</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B189">
-        <v>5750</v>
+        <v>5000</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46269.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B190">
-        <v>5690</v>
+        <v>4940</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46269.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B191">
-        <v>5650</v>
+        <v>4900</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46269.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B192">
-        <v>5580</v>
+        <v>4830</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46269.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B193">
-        <v>5510</v>
+        <v>4780</v>
       </c>
       <c r="C193">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.09.20261</t>
-  </si>
-  <si>
-    <t>12.09.20262</t>
-  </si>
-  <si>
-    <t>12.09.20263</t>
-  </si>
-  <si>
-    <t>12.09.20264</t>
-  </si>
-  <si>
-    <t>12.09.20265</t>
-  </si>
-  <si>
-    <t>12.09.20266</t>
-  </si>
-  <si>
-    <t>12.09.20267</t>
-  </si>
-  <si>
-    <t>12.09.20268</t>
-  </si>
-  <si>
-    <t>12.09.20269</t>
-  </si>
-  <si>
-    <t>12.09.202610</t>
-  </si>
-  <si>
-    <t>12.09.202611</t>
-  </si>
-  <si>
-    <t>12.09.202612</t>
-  </si>
-  <si>
-    <t>12.09.202613</t>
-  </si>
-  <si>
-    <t>12.09.202614</t>
-  </si>
-  <si>
-    <t>12.09.202615</t>
-  </si>
-  <si>
-    <t>12.09.202616</t>
-  </si>
-  <si>
-    <t>12.09.202617</t>
-  </si>
-  <si>
-    <t>12.09.202618</t>
-  </si>
-  <si>
-    <t>12.09.202619</t>
-  </si>
-  <si>
-    <t>12.09.202620</t>
-  </si>
-  <si>
-    <t>12.09.202621</t>
-  </si>
-  <si>
-    <t>12.09.202622</t>
-  </si>
-  <si>
-    <t>12.09.202623</t>
-  </si>
-  <si>
-    <t>12.09.202624</t>
-  </si>
-  <si>
-    <t>12.09.202625</t>
-  </si>
-  <si>
-    <t>12.09.202626</t>
-  </si>
-  <si>
-    <t>12.09.202627</t>
-  </si>
-  <si>
-    <t>12.09.202628</t>
-  </si>
-  <si>
-    <t>12.09.202629</t>
-  </si>
-  <si>
-    <t>12.09.202630</t>
-  </si>
-  <si>
-    <t>12.09.202631</t>
-  </si>
-  <si>
-    <t>12.09.202632</t>
-  </si>
-  <si>
-    <t>12.09.202633</t>
-  </si>
-  <si>
-    <t>12.09.202634</t>
-  </si>
-  <si>
-    <t>12.09.202635</t>
-  </si>
-  <si>
-    <t>12.09.202636</t>
-  </si>
-  <si>
-    <t>12.09.202637</t>
-  </si>
-  <si>
-    <t>12.09.202638</t>
-  </si>
-  <si>
-    <t>12.09.202639</t>
-  </si>
-  <si>
-    <t>12.09.202640</t>
-  </si>
-  <si>
-    <t>12.09.202641</t>
-  </si>
-  <si>
-    <t>12.09.202642</t>
-  </si>
-  <si>
-    <t>12.09.202643</t>
-  </si>
-  <si>
-    <t>12.09.202644</t>
-  </si>
-  <si>
-    <t>12.09.202645</t>
-  </si>
-  <si>
-    <t>12.09.202646</t>
-  </si>
-  <si>
-    <t>12.09.202647</t>
-  </si>
-  <si>
-    <t>12.09.202648</t>
-  </si>
-  <si>
-    <t>12.09.202649</t>
-  </si>
-  <si>
-    <t>12.09.202650</t>
-  </si>
-  <si>
-    <t>12.09.202651</t>
-  </si>
-  <si>
-    <t>12.09.202652</t>
-  </si>
-  <si>
-    <t>12.09.202653</t>
-  </si>
-  <si>
-    <t>12.09.202654</t>
-  </si>
-  <si>
-    <t>12.09.202655</t>
-  </si>
-  <si>
-    <t>12.09.202656</t>
-  </si>
-  <si>
-    <t>12.09.202657</t>
-  </si>
-  <si>
-    <t>12.09.202658</t>
-  </si>
-  <si>
-    <t>12.09.202659</t>
-  </si>
-  <si>
-    <t>12.09.202660</t>
-  </si>
-  <si>
-    <t>12.09.202661</t>
-  </si>
-  <si>
-    <t>12.09.202662</t>
-  </si>
-  <si>
-    <t>12.09.202663</t>
-  </si>
-  <si>
-    <t>12.09.202664</t>
-  </si>
-  <si>
-    <t>12.09.202665</t>
-  </si>
-  <si>
-    <t>12.09.202666</t>
-  </si>
-  <si>
-    <t>12.09.202667</t>
-  </si>
-  <si>
-    <t>12.09.202668</t>
-  </si>
-  <si>
-    <t>12.09.202669</t>
-  </si>
-  <si>
-    <t>12.09.202670</t>
-  </si>
-  <si>
-    <t>12.09.202671</t>
-  </si>
-  <si>
-    <t>12.09.202672</t>
-  </si>
-  <si>
-    <t>12.09.202673</t>
-  </si>
-  <si>
-    <t>12.09.202674</t>
-  </si>
-  <si>
-    <t>12.09.202675</t>
-  </si>
-  <si>
-    <t>12.09.202676</t>
-  </si>
-  <si>
-    <t>12.09.202677</t>
-  </si>
-  <si>
-    <t>12.09.202678</t>
-  </si>
-  <si>
-    <t>12.09.202679</t>
-  </si>
-  <si>
-    <t>12.09.202680</t>
-  </si>
-  <si>
-    <t>12.09.202681</t>
-  </si>
-  <si>
-    <t>12.09.202682</t>
-  </si>
-  <si>
-    <t>12.09.202683</t>
-  </si>
-  <si>
-    <t>12.09.202684</t>
-  </si>
-  <si>
-    <t>12.09.202685</t>
-  </si>
-  <si>
-    <t>12.09.202686</t>
-  </si>
-  <si>
-    <t>12.09.202687</t>
-  </si>
-  <si>
-    <t>12.09.202688</t>
-  </si>
-  <si>
-    <t>12.09.202689</t>
-  </si>
-  <si>
-    <t>12.09.202690</t>
-  </si>
-  <si>
-    <t>12.09.202691</t>
-  </si>
-  <si>
-    <t>12.09.202692</t>
-  </si>
-  <si>
-    <t>12.09.202693</t>
-  </si>
-  <si>
-    <t>12.09.202694</t>
-  </si>
-  <si>
-    <t>12.09.202695</t>
-  </si>
-  <si>
-    <t>12.09.202696</t>
-  </si>
-  <si>
     <t>13.09.20261</t>
   </si>
   <si>
@@ -602,6 +314,1446 @@
   </si>
   <si>
     <t>13.09.202696</t>
+  </si>
+  <si>
+    <t>14.09.20261</t>
+  </si>
+  <si>
+    <t>14.09.20262</t>
+  </si>
+  <si>
+    <t>14.09.20263</t>
+  </si>
+  <si>
+    <t>14.09.20264</t>
+  </si>
+  <si>
+    <t>14.09.20265</t>
+  </si>
+  <si>
+    <t>14.09.20266</t>
+  </si>
+  <si>
+    <t>14.09.20267</t>
+  </si>
+  <si>
+    <t>14.09.20268</t>
+  </si>
+  <si>
+    <t>14.09.20269</t>
+  </si>
+  <si>
+    <t>14.09.202610</t>
+  </si>
+  <si>
+    <t>14.09.202611</t>
+  </si>
+  <si>
+    <t>14.09.202612</t>
+  </si>
+  <si>
+    <t>14.09.202613</t>
+  </si>
+  <si>
+    <t>14.09.202614</t>
+  </si>
+  <si>
+    <t>14.09.202615</t>
+  </si>
+  <si>
+    <t>14.09.202616</t>
+  </si>
+  <si>
+    <t>14.09.202617</t>
+  </si>
+  <si>
+    <t>14.09.202618</t>
+  </si>
+  <si>
+    <t>14.09.202619</t>
+  </si>
+  <si>
+    <t>14.09.202620</t>
+  </si>
+  <si>
+    <t>14.09.202621</t>
+  </si>
+  <si>
+    <t>14.09.202622</t>
+  </si>
+  <si>
+    <t>14.09.202623</t>
+  </si>
+  <si>
+    <t>14.09.202624</t>
+  </si>
+  <si>
+    <t>14.09.202625</t>
+  </si>
+  <si>
+    <t>14.09.202626</t>
+  </si>
+  <si>
+    <t>14.09.202627</t>
+  </si>
+  <si>
+    <t>14.09.202628</t>
+  </si>
+  <si>
+    <t>14.09.202629</t>
+  </si>
+  <si>
+    <t>14.09.202630</t>
+  </si>
+  <si>
+    <t>14.09.202631</t>
+  </si>
+  <si>
+    <t>14.09.202632</t>
+  </si>
+  <si>
+    <t>14.09.202633</t>
+  </si>
+  <si>
+    <t>14.09.202634</t>
+  </si>
+  <si>
+    <t>14.09.202635</t>
+  </si>
+  <si>
+    <t>14.09.202636</t>
+  </si>
+  <si>
+    <t>14.09.202637</t>
+  </si>
+  <si>
+    <t>14.09.202638</t>
+  </si>
+  <si>
+    <t>14.09.202639</t>
+  </si>
+  <si>
+    <t>14.09.202640</t>
+  </si>
+  <si>
+    <t>14.09.202641</t>
+  </si>
+  <si>
+    <t>14.09.202642</t>
+  </si>
+  <si>
+    <t>14.09.202643</t>
+  </si>
+  <si>
+    <t>14.09.202644</t>
+  </si>
+  <si>
+    <t>14.09.202645</t>
+  </si>
+  <si>
+    <t>14.09.202646</t>
+  </si>
+  <si>
+    <t>14.09.202647</t>
+  </si>
+  <si>
+    <t>14.09.202648</t>
+  </si>
+  <si>
+    <t>14.09.202649</t>
+  </si>
+  <si>
+    <t>14.09.202650</t>
+  </si>
+  <si>
+    <t>14.09.202651</t>
+  </si>
+  <si>
+    <t>14.09.202652</t>
+  </si>
+  <si>
+    <t>14.09.202653</t>
+  </si>
+  <si>
+    <t>14.09.202654</t>
+  </si>
+  <si>
+    <t>14.09.202655</t>
+  </si>
+  <si>
+    <t>14.09.202656</t>
+  </si>
+  <si>
+    <t>14.09.202657</t>
+  </si>
+  <si>
+    <t>14.09.202658</t>
+  </si>
+  <si>
+    <t>14.09.202659</t>
+  </si>
+  <si>
+    <t>14.09.202660</t>
+  </si>
+  <si>
+    <t>14.09.202661</t>
+  </si>
+  <si>
+    <t>14.09.202662</t>
+  </si>
+  <si>
+    <t>14.09.202663</t>
+  </si>
+  <si>
+    <t>14.09.202664</t>
+  </si>
+  <si>
+    <t>14.09.202665</t>
+  </si>
+  <si>
+    <t>14.09.202666</t>
+  </si>
+  <si>
+    <t>14.09.202667</t>
+  </si>
+  <si>
+    <t>14.09.202668</t>
+  </si>
+  <si>
+    <t>14.09.202669</t>
+  </si>
+  <si>
+    <t>14.09.202670</t>
+  </si>
+  <si>
+    <t>14.09.202671</t>
+  </si>
+  <si>
+    <t>14.09.202672</t>
+  </si>
+  <si>
+    <t>14.09.202673</t>
+  </si>
+  <si>
+    <t>14.09.202674</t>
+  </si>
+  <si>
+    <t>14.09.202675</t>
+  </si>
+  <si>
+    <t>14.09.202676</t>
+  </si>
+  <si>
+    <t>14.09.202677</t>
+  </si>
+  <si>
+    <t>14.09.202678</t>
+  </si>
+  <si>
+    <t>14.09.202679</t>
+  </si>
+  <si>
+    <t>14.09.202680</t>
+  </si>
+  <si>
+    <t>14.09.202681</t>
+  </si>
+  <si>
+    <t>14.09.202682</t>
+  </si>
+  <si>
+    <t>14.09.202683</t>
+  </si>
+  <si>
+    <t>14.09.202684</t>
+  </si>
+  <si>
+    <t>14.09.202685</t>
+  </si>
+  <si>
+    <t>14.09.202686</t>
+  </si>
+  <si>
+    <t>14.09.202687</t>
+  </si>
+  <si>
+    <t>14.09.202688</t>
+  </si>
+  <si>
+    <t>14.09.202689</t>
+  </si>
+  <si>
+    <t>14.09.202690</t>
+  </si>
+  <si>
+    <t>14.09.202691</t>
+  </si>
+  <si>
+    <t>14.09.202692</t>
+  </si>
+  <si>
+    <t>14.09.202693</t>
+  </si>
+  <si>
+    <t>14.09.202694</t>
+  </si>
+  <si>
+    <t>14.09.202695</t>
+  </si>
+  <si>
+    <t>14.09.202696</t>
+  </si>
+  <si>
+    <t>15.09.20261</t>
+  </si>
+  <si>
+    <t>15.09.20262</t>
+  </si>
+  <si>
+    <t>15.09.20263</t>
+  </si>
+  <si>
+    <t>15.09.20264</t>
+  </si>
+  <si>
+    <t>15.09.20265</t>
+  </si>
+  <si>
+    <t>15.09.20266</t>
+  </si>
+  <si>
+    <t>15.09.20267</t>
+  </si>
+  <si>
+    <t>15.09.20268</t>
+  </si>
+  <si>
+    <t>15.09.20269</t>
+  </si>
+  <si>
+    <t>15.09.202610</t>
+  </si>
+  <si>
+    <t>15.09.202611</t>
+  </si>
+  <si>
+    <t>15.09.202612</t>
+  </si>
+  <si>
+    <t>15.09.202613</t>
+  </si>
+  <si>
+    <t>15.09.202614</t>
+  </si>
+  <si>
+    <t>15.09.202615</t>
+  </si>
+  <si>
+    <t>15.09.202616</t>
+  </si>
+  <si>
+    <t>15.09.202617</t>
+  </si>
+  <si>
+    <t>15.09.202618</t>
+  </si>
+  <si>
+    <t>15.09.202619</t>
+  </si>
+  <si>
+    <t>15.09.202620</t>
+  </si>
+  <si>
+    <t>15.09.202621</t>
+  </si>
+  <si>
+    <t>15.09.202622</t>
+  </si>
+  <si>
+    <t>15.09.202623</t>
+  </si>
+  <si>
+    <t>15.09.202624</t>
+  </si>
+  <si>
+    <t>15.09.202625</t>
+  </si>
+  <si>
+    <t>15.09.202626</t>
+  </si>
+  <si>
+    <t>15.09.202627</t>
+  </si>
+  <si>
+    <t>15.09.202628</t>
+  </si>
+  <si>
+    <t>15.09.202629</t>
+  </si>
+  <si>
+    <t>15.09.202630</t>
+  </si>
+  <si>
+    <t>15.09.202631</t>
+  </si>
+  <si>
+    <t>15.09.202632</t>
+  </si>
+  <si>
+    <t>15.09.202633</t>
+  </si>
+  <si>
+    <t>15.09.202634</t>
+  </si>
+  <si>
+    <t>15.09.202635</t>
+  </si>
+  <si>
+    <t>15.09.202636</t>
+  </si>
+  <si>
+    <t>15.09.202637</t>
+  </si>
+  <si>
+    <t>15.09.202638</t>
+  </si>
+  <si>
+    <t>15.09.202639</t>
+  </si>
+  <si>
+    <t>15.09.202640</t>
+  </si>
+  <si>
+    <t>15.09.202641</t>
+  </si>
+  <si>
+    <t>15.09.202642</t>
+  </si>
+  <si>
+    <t>15.09.202643</t>
+  </si>
+  <si>
+    <t>15.09.202644</t>
+  </si>
+  <si>
+    <t>15.09.202645</t>
+  </si>
+  <si>
+    <t>15.09.202646</t>
+  </si>
+  <si>
+    <t>15.09.202647</t>
+  </si>
+  <si>
+    <t>15.09.202648</t>
+  </si>
+  <si>
+    <t>15.09.202649</t>
+  </si>
+  <si>
+    <t>15.09.202650</t>
+  </si>
+  <si>
+    <t>15.09.202651</t>
+  </si>
+  <si>
+    <t>15.09.202652</t>
+  </si>
+  <si>
+    <t>15.09.202653</t>
+  </si>
+  <si>
+    <t>15.09.202654</t>
+  </si>
+  <si>
+    <t>15.09.202655</t>
+  </si>
+  <si>
+    <t>15.09.202656</t>
+  </si>
+  <si>
+    <t>15.09.202657</t>
+  </si>
+  <si>
+    <t>15.09.202658</t>
+  </si>
+  <si>
+    <t>15.09.202659</t>
+  </si>
+  <si>
+    <t>15.09.202660</t>
+  </si>
+  <si>
+    <t>15.09.202661</t>
+  </si>
+  <si>
+    <t>15.09.202662</t>
+  </si>
+  <si>
+    <t>15.09.202663</t>
+  </si>
+  <si>
+    <t>15.09.202664</t>
+  </si>
+  <si>
+    <t>15.09.202665</t>
+  </si>
+  <si>
+    <t>15.09.202666</t>
+  </si>
+  <si>
+    <t>15.09.202667</t>
+  </si>
+  <si>
+    <t>15.09.202668</t>
+  </si>
+  <si>
+    <t>15.09.202669</t>
+  </si>
+  <si>
+    <t>15.09.202670</t>
+  </si>
+  <si>
+    <t>15.09.202671</t>
+  </si>
+  <si>
+    <t>15.09.202672</t>
+  </si>
+  <si>
+    <t>15.09.202673</t>
+  </si>
+  <si>
+    <t>15.09.202674</t>
+  </si>
+  <si>
+    <t>15.09.202675</t>
+  </si>
+  <si>
+    <t>15.09.202676</t>
+  </si>
+  <si>
+    <t>15.09.202677</t>
+  </si>
+  <si>
+    <t>15.09.202678</t>
+  </si>
+  <si>
+    <t>15.09.202679</t>
+  </si>
+  <si>
+    <t>15.09.202680</t>
+  </si>
+  <si>
+    <t>15.09.202681</t>
+  </si>
+  <si>
+    <t>15.09.202682</t>
+  </si>
+  <si>
+    <t>15.09.202683</t>
+  </si>
+  <si>
+    <t>15.09.202684</t>
+  </si>
+  <si>
+    <t>15.09.202685</t>
+  </si>
+  <si>
+    <t>15.09.202686</t>
+  </si>
+  <si>
+    <t>15.09.202687</t>
+  </si>
+  <si>
+    <t>15.09.202688</t>
+  </si>
+  <si>
+    <t>15.09.202689</t>
+  </si>
+  <si>
+    <t>15.09.202690</t>
+  </si>
+  <si>
+    <t>15.09.202691</t>
+  </si>
+  <si>
+    <t>15.09.202692</t>
+  </si>
+  <si>
+    <t>15.09.202693</t>
+  </si>
+  <si>
+    <t>15.09.202694</t>
+  </si>
+  <si>
+    <t>15.09.202695</t>
+  </si>
+  <si>
+    <t>15.09.202696</t>
+  </si>
+  <si>
+    <t>16.09.20261</t>
+  </si>
+  <si>
+    <t>16.09.20262</t>
+  </si>
+  <si>
+    <t>16.09.20263</t>
+  </si>
+  <si>
+    <t>16.09.20264</t>
+  </si>
+  <si>
+    <t>16.09.20265</t>
+  </si>
+  <si>
+    <t>16.09.20266</t>
+  </si>
+  <si>
+    <t>16.09.20267</t>
+  </si>
+  <si>
+    <t>16.09.20268</t>
+  </si>
+  <si>
+    <t>16.09.20269</t>
+  </si>
+  <si>
+    <t>16.09.202610</t>
+  </si>
+  <si>
+    <t>16.09.202611</t>
+  </si>
+  <si>
+    <t>16.09.202612</t>
+  </si>
+  <si>
+    <t>16.09.202613</t>
+  </si>
+  <si>
+    <t>16.09.202614</t>
+  </si>
+  <si>
+    <t>16.09.202615</t>
+  </si>
+  <si>
+    <t>16.09.202616</t>
+  </si>
+  <si>
+    <t>16.09.202617</t>
+  </si>
+  <si>
+    <t>16.09.202618</t>
+  </si>
+  <si>
+    <t>16.09.202619</t>
+  </si>
+  <si>
+    <t>16.09.202620</t>
+  </si>
+  <si>
+    <t>16.09.202621</t>
+  </si>
+  <si>
+    <t>16.09.202622</t>
+  </si>
+  <si>
+    <t>16.09.202623</t>
+  </si>
+  <si>
+    <t>16.09.202624</t>
+  </si>
+  <si>
+    <t>16.09.202625</t>
+  </si>
+  <si>
+    <t>16.09.202626</t>
+  </si>
+  <si>
+    <t>16.09.202627</t>
+  </si>
+  <si>
+    <t>16.09.202628</t>
+  </si>
+  <si>
+    <t>16.09.202629</t>
+  </si>
+  <si>
+    <t>16.09.202630</t>
+  </si>
+  <si>
+    <t>16.09.202631</t>
+  </si>
+  <si>
+    <t>16.09.202632</t>
+  </si>
+  <si>
+    <t>16.09.202633</t>
+  </si>
+  <si>
+    <t>16.09.202634</t>
+  </si>
+  <si>
+    <t>16.09.202635</t>
+  </si>
+  <si>
+    <t>16.09.202636</t>
+  </si>
+  <si>
+    <t>16.09.202637</t>
+  </si>
+  <si>
+    <t>16.09.202638</t>
+  </si>
+  <si>
+    <t>16.09.202639</t>
+  </si>
+  <si>
+    <t>16.09.202640</t>
+  </si>
+  <si>
+    <t>16.09.202641</t>
+  </si>
+  <si>
+    <t>16.09.202642</t>
+  </si>
+  <si>
+    <t>16.09.202643</t>
+  </si>
+  <si>
+    <t>16.09.202644</t>
+  </si>
+  <si>
+    <t>16.09.202645</t>
+  </si>
+  <si>
+    <t>16.09.202646</t>
+  </si>
+  <si>
+    <t>16.09.202647</t>
+  </si>
+  <si>
+    <t>16.09.202648</t>
+  </si>
+  <si>
+    <t>16.09.202649</t>
+  </si>
+  <si>
+    <t>16.09.202650</t>
+  </si>
+  <si>
+    <t>16.09.202651</t>
+  </si>
+  <si>
+    <t>16.09.202652</t>
+  </si>
+  <si>
+    <t>16.09.202653</t>
+  </si>
+  <si>
+    <t>16.09.202654</t>
+  </si>
+  <si>
+    <t>16.09.202655</t>
+  </si>
+  <si>
+    <t>16.09.202656</t>
+  </si>
+  <si>
+    <t>16.09.202657</t>
+  </si>
+  <si>
+    <t>16.09.202658</t>
+  </si>
+  <si>
+    <t>16.09.202659</t>
+  </si>
+  <si>
+    <t>16.09.202660</t>
+  </si>
+  <si>
+    <t>16.09.202661</t>
+  </si>
+  <si>
+    <t>16.09.202662</t>
+  </si>
+  <si>
+    <t>16.09.202663</t>
+  </si>
+  <si>
+    <t>16.09.202664</t>
+  </si>
+  <si>
+    <t>16.09.202665</t>
+  </si>
+  <si>
+    <t>16.09.202666</t>
+  </si>
+  <si>
+    <t>16.09.202667</t>
+  </si>
+  <si>
+    <t>16.09.202668</t>
+  </si>
+  <si>
+    <t>16.09.202669</t>
+  </si>
+  <si>
+    <t>16.09.202670</t>
+  </si>
+  <si>
+    <t>16.09.202671</t>
+  </si>
+  <si>
+    <t>16.09.202672</t>
+  </si>
+  <si>
+    <t>16.09.202673</t>
+  </si>
+  <si>
+    <t>16.09.202674</t>
+  </si>
+  <si>
+    <t>16.09.202675</t>
+  </si>
+  <si>
+    <t>16.09.202676</t>
+  </si>
+  <si>
+    <t>16.09.202677</t>
+  </si>
+  <si>
+    <t>16.09.202678</t>
+  </si>
+  <si>
+    <t>16.09.202679</t>
+  </si>
+  <si>
+    <t>16.09.202680</t>
+  </si>
+  <si>
+    <t>16.09.202681</t>
+  </si>
+  <si>
+    <t>16.09.202682</t>
+  </si>
+  <si>
+    <t>16.09.202683</t>
+  </si>
+  <si>
+    <t>16.09.202684</t>
+  </si>
+  <si>
+    <t>16.09.202685</t>
+  </si>
+  <si>
+    <t>16.09.202686</t>
+  </si>
+  <si>
+    <t>16.09.202687</t>
+  </si>
+  <si>
+    <t>16.09.202688</t>
+  </si>
+  <si>
+    <t>16.09.202689</t>
+  </si>
+  <si>
+    <t>16.09.202690</t>
+  </si>
+  <si>
+    <t>16.09.202691</t>
+  </si>
+  <si>
+    <t>16.09.202692</t>
+  </si>
+  <si>
+    <t>16.09.202693</t>
+  </si>
+  <si>
+    <t>16.09.202694</t>
+  </si>
+  <si>
+    <t>16.09.202695</t>
+  </si>
+  <si>
+    <t>16.09.202696</t>
+  </si>
+  <si>
+    <t>17.09.20261</t>
+  </si>
+  <si>
+    <t>17.09.20262</t>
+  </si>
+  <si>
+    <t>17.09.20263</t>
+  </si>
+  <si>
+    <t>17.09.20264</t>
+  </si>
+  <si>
+    <t>17.09.20265</t>
+  </si>
+  <si>
+    <t>17.09.20266</t>
+  </si>
+  <si>
+    <t>17.09.20267</t>
+  </si>
+  <si>
+    <t>17.09.20268</t>
+  </si>
+  <si>
+    <t>17.09.20269</t>
+  </si>
+  <si>
+    <t>17.09.202610</t>
+  </si>
+  <si>
+    <t>17.09.202611</t>
+  </si>
+  <si>
+    <t>17.09.202612</t>
+  </si>
+  <si>
+    <t>17.09.202613</t>
+  </si>
+  <si>
+    <t>17.09.202614</t>
+  </si>
+  <si>
+    <t>17.09.202615</t>
+  </si>
+  <si>
+    <t>17.09.202616</t>
+  </si>
+  <si>
+    <t>17.09.202617</t>
+  </si>
+  <si>
+    <t>17.09.202618</t>
+  </si>
+  <si>
+    <t>17.09.202619</t>
+  </si>
+  <si>
+    <t>17.09.202620</t>
+  </si>
+  <si>
+    <t>17.09.202621</t>
+  </si>
+  <si>
+    <t>17.09.202622</t>
+  </si>
+  <si>
+    <t>17.09.202623</t>
+  </si>
+  <si>
+    <t>17.09.202624</t>
+  </si>
+  <si>
+    <t>17.09.202625</t>
+  </si>
+  <si>
+    <t>17.09.202626</t>
+  </si>
+  <si>
+    <t>17.09.202627</t>
+  </si>
+  <si>
+    <t>17.09.202628</t>
+  </si>
+  <si>
+    <t>17.09.202629</t>
+  </si>
+  <si>
+    <t>17.09.202630</t>
+  </si>
+  <si>
+    <t>17.09.202631</t>
+  </si>
+  <si>
+    <t>17.09.202632</t>
+  </si>
+  <si>
+    <t>17.09.202633</t>
+  </si>
+  <si>
+    <t>17.09.202634</t>
+  </si>
+  <si>
+    <t>17.09.202635</t>
+  </si>
+  <si>
+    <t>17.09.202636</t>
+  </si>
+  <si>
+    <t>17.09.202637</t>
+  </si>
+  <si>
+    <t>17.09.202638</t>
+  </si>
+  <si>
+    <t>17.09.202639</t>
+  </si>
+  <si>
+    <t>17.09.202640</t>
+  </si>
+  <si>
+    <t>17.09.202641</t>
+  </si>
+  <si>
+    <t>17.09.202642</t>
+  </si>
+  <si>
+    <t>17.09.202643</t>
+  </si>
+  <si>
+    <t>17.09.202644</t>
+  </si>
+  <si>
+    <t>17.09.202645</t>
+  </si>
+  <si>
+    <t>17.09.202646</t>
+  </si>
+  <si>
+    <t>17.09.202647</t>
+  </si>
+  <si>
+    <t>17.09.202648</t>
+  </si>
+  <si>
+    <t>17.09.202649</t>
+  </si>
+  <si>
+    <t>17.09.202650</t>
+  </si>
+  <si>
+    <t>17.09.202651</t>
+  </si>
+  <si>
+    <t>17.09.202652</t>
+  </si>
+  <si>
+    <t>17.09.202653</t>
+  </si>
+  <si>
+    <t>17.09.202654</t>
+  </si>
+  <si>
+    <t>17.09.202655</t>
+  </si>
+  <si>
+    <t>17.09.202656</t>
+  </si>
+  <si>
+    <t>17.09.202657</t>
+  </si>
+  <si>
+    <t>17.09.202658</t>
+  </si>
+  <si>
+    <t>17.09.202659</t>
+  </si>
+  <si>
+    <t>17.09.202660</t>
+  </si>
+  <si>
+    <t>17.09.202661</t>
+  </si>
+  <si>
+    <t>17.09.202662</t>
+  </si>
+  <si>
+    <t>17.09.202663</t>
+  </si>
+  <si>
+    <t>17.09.202664</t>
+  </si>
+  <si>
+    <t>17.09.202665</t>
+  </si>
+  <si>
+    <t>17.09.202666</t>
+  </si>
+  <si>
+    <t>17.09.202667</t>
+  </si>
+  <si>
+    <t>17.09.202668</t>
+  </si>
+  <si>
+    <t>17.09.202669</t>
+  </si>
+  <si>
+    <t>17.09.202670</t>
+  </si>
+  <si>
+    <t>17.09.202671</t>
+  </si>
+  <si>
+    <t>17.09.202672</t>
+  </si>
+  <si>
+    <t>17.09.202673</t>
+  </si>
+  <si>
+    <t>17.09.202674</t>
+  </si>
+  <si>
+    <t>17.09.202675</t>
+  </si>
+  <si>
+    <t>17.09.202676</t>
+  </si>
+  <si>
+    <t>17.09.202677</t>
+  </si>
+  <si>
+    <t>17.09.202678</t>
+  </si>
+  <si>
+    <t>17.09.202679</t>
+  </si>
+  <si>
+    <t>17.09.202680</t>
+  </si>
+  <si>
+    <t>17.09.202681</t>
+  </si>
+  <si>
+    <t>17.09.202682</t>
+  </si>
+  <si>
+    <t>17.09.202683</t>
+  </si>
+  <si>
+    <t>17.09.202684</t>
+  </si>
+  <si>
+    <t>17.09.202685</t>
+  </si>
+  <si>
+    <t>17.09.202686</t>
+  </si>
+  <si>
+    <t>17.09.202687</t>
+  </si>
+  <si>
+    <t>17.09.202688</t>
+  </si>
+  <si>
+    <t>17.09.202689</t>
+  </si>
+  <si>
+    <t>17.09.202690</t>
+  </si>
+  <si>
+    <t>17.09.202691</t>
+  </si>
+  <si>
+    <t>17.09.202692</t>
+  </si>
+  <si>
+    <t>17.09.202693</t>
+  </si>
+  <si>
+    <t>17.09.202694</t>
+  </si>
+  <si>
+    <t>17.09.202695</t>
+  </si>
+  <si>
+    <t>17.09.202696</t>
+  </si>
+  <si>
+    <t>18.09.20261</t>
+  </si>
+  <si>
+    <t>18.09.20262</t>
+  </si>
+  <si>
+    <t>18.09.20263</t>
+  </si>
+  <si>
+    <t>18.09.20264</t>
+  </si>
+  <si>
+    <t>18.09.20265</t>
+  </si>
+  <si>
+    <t>18.09.20266</t>
+  </si>
+  <si>
+    <t>18.09.20267</t>
+  </si>
+  <si>
+    <t>18.09.20268</t>
+  </si>
+  <si>
+    <t>18.09.20269</t>
+  </si>
+  <si>
+    <t>18.09.202610</t>
+  </si>
+  <si>
+    <t>18.09.202611</t>
+  </si>
+  <si>
+    <t>18.09.202612</t>
+  </si>
+  <si>
+    <t>18.09.202613</t>
+  </si>
+  <si>
+    <t>18.09.202614</t>
+  </si>
+  <si>
+    <t>18.09.202615</t>
+  </si>
+  <si>
+    <t>18.09.202616</t>
+  </si>
+  <si>
+    <t>18.09.202617</t>
+  </si>
+  <si>
+    <t>18.09.202618</t>
+  </si>
+  <si>
+    <t>18.09.202619</t>
+  </si>
+  <si>
+    <t>18.09.202620</t>
+  </si>
+  <si>
+    <t>18.09.202621</t>
+  </si>
+  <si>
+    <t>18.09.202622</t>
+  </si>
+  <si>
+    <t>18.09.202623</t>
+  </si>
+  <si>
+    <t>18.09.202624</t>
+  </si>
+  <si>
+    <t>18.09.202625</t>
+  </si>
+  <si>
+    <t>18.09.202626</t>
+  </si>
+  <si>
+    <t>18.09.202627</t>
+  </si>
+  <si>
+    <t>18.09.202628</t>
+  </si>
+  <si>
+    <t>18.09.202629</t>
+  </si>
+  <si>
+    <t>18.09.202630</t>
+  </si>
+  <si>
+    <t>18.09.202631</t>
+  </si>
+  <si>
+    <t>18.09.202632</t>
+  </si>
+  <si>
+    <t>18.09.202633</t>
+  </si>
+  <si>
+    <t>18.09.202634</t>
+  </si>
+  <si>
+    <t>18.09.202635</t>
+  </si>
+  <si>
+    <t>18.09.202636</t>
+  </si>
+  <si>
+    <t>18.09.202637</t>
+  </si>
+  <si>
+    <t>18.09.202638</t>
+  </si>
+  <si>
+    <t>18.09.202639</t>
+  </si>
+  <si>
+    <t>18.09.202640</t>
+  </si>
+  <si>
+    <t>18.09.202641</t>
+  </si>
+  <si>
+    <t>18.09.202642</t>
+  </si>
+  <si>
+    <t>18.09.202643</t>
+  </si>
+  <si>
+    <t>18.09.202644</t>
+  </si>
+  <si>
+    <t>18.09.202645</t>
+  </si>
+  <si>
+    <t>18.09.202646</t>
+  </si>
+  <si>
+    <t>18.09.202647</t>
+  </si>
+  <si>
+    <t>18.09.202648</t>
+  </si>
+  <si>
+    <t>18.09.202649</t>
+  </si>
+  <si>
+    <t>18.09.202650</t>
+  </si>
+  <si>
+    <t>18.09.202651</t>
+  </si>
+  <si>
+    <t>18.09.202652</t>
+  </si>
+  <si>
+    <t>18.09.202653</t>
+  </si>
+  <si>
+    <t>18.09.202654</t>
+  </si>
+  <si>
+    <t>18.09.202655</t>
+  </si>
+  <si>
+    <t>18.09.202656</t>
+  </si>
+  <si>
+    <t>18.09.202657</t>
+  </si>
+  <si>
+    <t>18.09.202658</t>
+  </si>
+  <si>
+    <t>18.09.202659</t>
+  </si>
+  <si>
+    <t>18.09.202660</t>
+  </si>
+  <si>
+    <t>18.09.202661</t>
+  </si>
+  <si>
+    <t>18.09.202662</t>
+  </si>
+  <si>
+    <t>18.09.202663</t>
+  </si>
+  <si>
+    <t>18.09.202664</t>
+  </si>
+  <si>
+    <t>18.09.202665</t>
+  </si>
+  <si>
+    <t>18.09.202666</t>
+  </si>
+  <si>
+    <t>18.09.202667</t>
+  </si>
+  <si>
+    <t>18.09.202668</t>
+  </si>
+  <si>
+    <t>18.09.202669</t>
+  </si>
+  <si>
+    <t>18.09.202670</t>
+  </si>
+  <si>
+    <t>18.09.202671</t>
+  </si>
+  <si>
+    <t>18.09.202672</t>
+  </si>
+  <si>
+    <t>18.09.202673</t>
+  </si>
+  <si>
+    <t>18.09.202674</t>
+  </si>
+  <si>
+    <t>18.09.202675</t>
+  </si>
+  <si>
+    <t>18.09.202676</t>
+  </si>
+  <si>
+    <t>18.09.202677</t>
+  </si>
+  <si>
+    <t>18.09.202678</t>
+  </si>
+  <si>
+    <t>18.09.202679</t>
+  </si>
+  <si>
+    <t>18.09.202680</t>
+  </si>
+  <si>
+    <t>18.09.202681</t>
+  </si>
+  <si>
+    <t>18.09.202682</t>
+  </si>
+  <si>
+    <t>18.09.202683</t>
+  </si>
+  <si>
+    <t>18.09.202684</t>
+  </si>
+  <si>
+    <t>18.09.202685</t>
+  </si>
+  <si>
+    <t>18.09.202686</t>
+  </si>
+  <si>
+    <t>18.09.202687</t>
+  </si>
+  <si>
+    <t>18.09.202688</t>
+  </si>
+  <si>
+    <t>18.09.202689</t>
+  </si>
+  <si>
+    <t>18.09.202690</t>
+  </si>
+  <si>
+    <t>18.09.202691</t>
+  </si>
+  <si>
+    <t>18.09.202692</t>
+  </si>
+  <si>
+    <t>18.09.202693</t>
+  </si>
+  <si>
+    <t>18.09.202694</t>
+  </si>
+  <si>
+    <t>18.09.202695</t>
+  </si>
+  <si>
+    <t>18.09.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +2134,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>5230</v>
+        <v>4970</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +2148,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46277.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>5190</v>
+        <v>4910</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +2162,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46277.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>5160</v>
+        <v>4870</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +2176,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46277.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>5140</v>
+        <v>4830</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +2190,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46277.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>5090</v>
+        <v>4800</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +2204,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46277.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>5070</v>
+        <v>4770</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +2218,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46277.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>5070</v>
+        <v>4750</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +2232,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46277.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>5060</v>
+        <v>4730</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +2246,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46277.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>5030</v>
+        <v>4720</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +2260,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46277.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>5020</v>
+        <v>4710</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +2274,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46277.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>5020</v>
+        <v>4710</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +2288,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46277.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>5020</v>
+        <v>4710</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +2302,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46277.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>5030</v>
+        <v>4700</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +2316,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46277.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>5030</v>
+        <v>4700</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +2330,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46277.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>5030</v>
+        <v>4700</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +2344,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46277.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>5030</v>
+        <v>4700</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +2358,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46277.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>5030</v>
+        <v>4710</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +2372,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46277.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>5050</v>
+        <v>4720</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +2386,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46277.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>5080</v>
+        <v>4740</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +2400,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46277.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>5110</v>
+        <v>4760</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +2414,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46277.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>5160</v>
+        <v>4780</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +2428,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46277.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>5200</v>
+        <v>4790</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +2442,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46277.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>5230</v>
+        <v>4800</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +2456,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46277.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>5280</v>
+        <v>4820</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +2470,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46277.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>5340</v>
+        <v>4830</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +2484,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46277.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>5370</v>
+        <v>4840</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +2498,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46277.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>5400</v>
+        <v>4840</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +2512,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46277.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>5420</v>
+        <v>4830</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +2526,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46277.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>5450</v>
+        <v>4800</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +2540,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46277.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>5450</v>
+        <v>4770</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +2554,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46277.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>5450</v>
+        <v>4730</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +2568,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46277.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>5450</v>
+        <v>4680</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2582,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46277.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>5420</v>
+        <v>4630</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2596,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46277.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>5370</v>
+        <v>4570</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2610,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46277.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2624,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46277.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>5220</v>
+        <v>4450</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2638,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46277.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>5120</v>
+        <v>4410</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2652,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46277.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B39">
-        <v>5020</v>
+        <v>4360</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2666,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46277.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B40">
-        <v>4960</v>
+        <v>4320</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2680,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46277.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B41">
-        <v>4880</v>
+        <v>4290</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2694,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46277.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B42">
-        <v>4810</v>
+        <v>4260</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2708,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46277.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B43">
-        <v>4760</v>
+        <v>4240</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2722,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46277.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B44">
-        <v>4730</v>
+        <v>4230</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2736,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46277.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B45">
-        <v>4710</v>
+        <v>4220</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2750,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46277.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B46">
-        <v>4680</v>
+        <v>4210</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2764,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46277.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B47">
-        <v>4680</v>
+        <v>4210</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2778,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46277.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B48">
-        <v>4680</v>
+        <v>4220</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2792,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46277.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B49">
-        <v>4680</v>
+        <v>4220</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2806,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46277.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B50">
-        <v>4660</v>
+        <v>4230</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2820,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46277.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B51">
-        <v>4650</v>
+        <v>4240</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2834,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46277.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B52">
-        <v>4650</v>
+        <v>4250</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2848,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46277.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B53">
-        <v>4650</v>
+        <v>4260</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2862,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46277.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B54">
-        <v>4650</v>
+        <v>4270</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2876,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46277.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B55">
-        <v>4650</v>
+        <v>4280</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2890,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46277.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B56">
-        <v>4650</v>
+        <v>4280</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2904,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46277.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B57">
-        <v>4670</v>
+        <v>4290</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2918,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46277.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B58">
-        <v>4740</v>
+        <v>4300</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2932,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46277.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B59">
-        <v>4780</v>
+        <v>4310</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2946,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46277.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B60">
-        <v>4810</v>
+        <v>4330</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2960,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46277.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B61">
-        <v>4860</v>
+        <v>4370</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2974,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46277.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B62">
-        <v>4930</v>
+        <v>4430</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2988,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46277.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B63">
-        <v>5000</v>
+        <v>4510</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +3002,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46277.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B64">
-        <v>5080</v>
+        <v>4610</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +3016,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46277.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B65">
-        <v>5190</v>
+        <v>4740</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +3030,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46277.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B66">
-        <v>5310</v>
+        <v>4890</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +3044,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46277.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B67">
-        <v>5440</v>
+        <v>5040</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +3058,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46277.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B68">
-        <v>5560</v>
+        <v>5200</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +3072,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46277.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B69">
-        <v>5700</v>
+        <v>5340</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +3086,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46277.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B70">
-        <v>5840</v>
+        <v>5480</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +3100,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46277.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B71">
-        <v>5960</v>
+        <v>5600</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +3114,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46277.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B72">
-        <v>6080</v>
+        <v>5710</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +3128,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46277.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B73">
-        <v>6200</v>
+        <v>5810</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +3142,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46277.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B74">
-        <v>6300</v>
+        <v>5900</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +3156,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46277.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B75">
-        <v>6410</v>
+        <v>5980</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +3170,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46277.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B76">
-        <v>6510</v>
+        <v>6040</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +3184,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46277.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B77">
-        <v>6580</v>
+        <v>6080</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +3198,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46277.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B78">
-        <v>6640</v>
+        <v>6120</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +3212,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46277.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B79">
-        <v>6670</v>
+        <v>6140</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +3226,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46277.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B80">
-        <v>6660</v>
+        <v>6140</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +3240,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46277.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B81">
-        <v>6630</v>
+        <v>6110</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +3254,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46277.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B82">
-        <v>6540</v>
+        <v>6060</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +3268,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46277.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B83">
-        <v>6450</v>
+        <v>6000</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +3282,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46277.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B84">
-        <v>6360</v>
+        <v>5930</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +3296,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46277.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B85">
-        <v>6250</v>
+        <v>5830</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +3310,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46277.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B86">
-        <v>6110</v>
+        <v>5720</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +3324,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46277.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B87">
-        <v>5970</v>
+        <v>5610</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +3338,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46277.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B88">
-        <v>5830</v>
+        <v>5500</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +3352,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46277.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B89">
-        <v>5710</v>
+        <v>5420</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +3366,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46277.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B90">
-        <v>5610</v>
+        <v>5320</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +3380,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46277.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B91">
-        <v>5500</v>
+        <v>5220</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +3394,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46277.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B92">
-        <v>5390</v>
+        <v>5120</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +3408,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46277.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B93">
-        <v>5280</v>
+        <v>5000</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +3422,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46277.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B94">
-        <v>5220</v>
+        <v>4800</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +3436,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46277.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B95">
-        <v>5150</v>
+        <v>4720</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +3450,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46277.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B96">
-        <v>5080</v>
+        <v>4640</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +3464,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46277.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B97">
-        <v>5030</v>
+        <v>4570</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +3478,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B98">
-        <v>4970</v>
+        <v>4520</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +3492,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46278.01041666666</v>
+        <v>46279.01041666666</v>
       </c>
       <c r="B99">
-        <v>4910</v>
+        <v>4480</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +3506,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46278.02083333334</v>
+        <v>46279.02083333334</v>
       </c>
       <c r="B100">
-        <v>4870</v>
+        <v>4460</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +3520,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46278.03125</v>
+        <v>46279.03125</v>
       </c>
       <c r="B101">
-        <v>4830</v>
+        <v>4430</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +3534,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46278.04166666666</v>
+        <v>46279.04166666666</v>
       </c>
       <c r="B102">
-        <v>4800</v>
+        <v>4410</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +3548,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46278.05208333334</v>
+        <v>46279.05208333334</v>
       </c>
       <c r="B103">
-        <v>4770</v>
+        <v>4410</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +3562,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46278.0625</v>
+        <v>46279.0625</v>
       </c>
       <c r="B104">
-        <v>4750</v>
+        <v>4390</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3576,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46278.07291666666</v>
+        <v>46279.07291666666</v>
       </c>
       <c r="B105">
-        <v>4730</v>
+        <v>4370</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3590,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46278.08333333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="B106">
-        <v>4720</v>
+        <v>4360</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3604,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46278.09375</v>
+        <v>46279.09375</v>
       </c>
       <c r="B107">
-        <v>4710</v>
+        <v>4360</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3618,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46278.10416666666</v>
+        <v>46279.10416666666</v>
       </c>
       <c r="B108">
-        <v>4710</v>
+        <v>4360</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3632,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46278.11458333334</v>
+        <v>46279.11458333334</v>
       </c>
       <c r="B109">
-        <v>4710</v>
+        <v>4370</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3646,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46278.125</v>
+        <v>46279.125</v>
       </c>
       <c r="B110">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3660,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46278.13541666666</v>
+        <v>46279.13541666666</v>
       </c>
       <c r="B111">
-        <v>4700</v>
+        <v>4420</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3674,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46278.14583333334</v>
+        <v>46279.14583333334</v>
       </c>
       <c r="B112">
-        <v>4700</v>
+        <v>4460</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3688,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46278.15625</v>
+        <v>46279.15625</v>
       </c>
       <c r="B113">
-        <v>4700</v>
+        <v>4520</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3702,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46278.16666666666</v>
+        <v>46279.16666666666</v>
       </c>
       <c r="B114">
-        <v>4710</v>
+        <v>4580</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3716,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46278.17708333334</v>
+        <v>46279.17708333334</v>
       </c>
       <c r="B115">
-        <v>4720</v>
+        <v>4670</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3730,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46278.1875</v>
+        <v>46279.1875</v>
       </c>
       <c r="B116">
-        <v>4740</v>
+        <v>4780</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3744,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46278.19791666666</v>
+        <v>46279.19791666666</v>
       </c>
       <c r="B117">
-        <v>4760</v>
+        <v>4900</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3758,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46278.20833333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="B118">
-        <v>4780</v>
+        <v>5050</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3772,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46278.21875</v>
+        <v>46279.21875</v>
       </c>
       <c r="B119">
-        <v>4790</v>
+        <v>5200</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3786,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46278.22916666666</v>
+        <v>46279.22916666666</v>
       </c>
       <c r="B120">
-        <v>4800</v>
+        <v>5370</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3800,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46278.23958333334</v>
+        <v>46279.23958333334</v>
       </c>
       <c r="B121">
-        <v>4820</v>
+        <v>5530</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3814,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46278.25</v>
+        <v>46279.25</v>
       </c>
       <c r="B122">
-        <v>4830</v>
+        <v>5680</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3828,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46278.26041666666</v>
+        <v>46279.26041666666</v>
       </c>
       <c r="B123">
-        <v>4840</v>
+        <v>5810</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3842,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46278.27083333334</v>
+        <v>46279.27083333334</v>
       </c>
       <c r="B124">
-        <v>4840</v>
+        <v>5910</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3856,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46278.28125</v>
+        <v>46279.28125</v>
       </c>
       <c r="B125">
-        <v>4830</v>
+        <v>5990</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3870,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46278.29166666666</v>
+        <v>46279.29166666666</v>
       </c>
       <c r="B126">
-        <v>4800</v>
+        <v>6020</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3884,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46278.30208333334</v>
+        <v>46279.30208333334</v>
       </c>
       <c r="B127">
-        <v>4770</v>
+        <v>6020</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3898,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46278.3125</v>
+        <v>46279.3125</v>
       </c>
       <c r="B128">
-        <v>4730</v>
+        <v>5980</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3912,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46278.32291666666</v>
+        <v>46279.32291666666</v>
       </c>
       <c r="B129">
-        <v>4680</v>
+        <v>5900</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3926,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46278.33333333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="B130">
-        <v>4630</v>
+        <v>5800</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3940,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46278.34375</v>
+        <v>46279.34375</v>
       </c>
       <c r="B131">
-        <v>4570</v>
+        <v>5680</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3954,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46278.35416666666</v>
+        <v>46279.35416666666</v>
       </c>
       <c r="B132">
-        <v>4500</v>
+        <v>5540</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3968,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46278.36458333334</v>
+        <v>46279.36458333334</v>
       </c>
       <c r="B133">
-        <v>4450</v>
+        <v>5410</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3982,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46278.375</v>
+        <v>46279.375</v>
       </c>
       <c r="B134">
-        <v>4410</v>
+        <v>5270</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3996,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46278.38541666666</v>
+        <v>46279.38541666666</v>
       </c>
       <c r="B135">
-        <v>4360</v>
+        <v>5140</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +4010,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46278.39583333334</v>
+        <v>46279.39583333334</v>
       </c>
       <c r="B136">
-        <v>4320</v>
+        <v>5030</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +4024,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46278.40625</v>
+        <v>46279.40625</v>
       </c>
       <c r="B137">
-        <v>4290</v>
+        <v>4930</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +4038,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46278.41666666666</v>
+        <v>46279.41666666666</v>
       </c>
       <c r="B138">
-        <v>4260</v>
+        <v>4850</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +4052,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46278.42708333334</v>
+        <v>46279.42708333334</v>
       </c>
       <c r="B139">
-        <v>4240</v>
+        <v>4780</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +4066,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46278.4375</v>
+        <v>46279.4375</v>
       </c>
       <c r="B140">
-        <v>4230</v>
+        <v>4730</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +4080,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46278.44791666666</v>
+        <v>46279.44791666666</v>
       </c>
       <c r="B141">
-        <v>4220</v>
+        <v>4700</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +4094,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46278.45833333334</v>
+        <v>46279.45833333334</v>
       </c>
       <c r="B142">
-        <v>4210</v>
+        <v>4670</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +4108,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46278.46875</v>
+        <v>46279.46875</v>
       </c>
       <c r="B143">
-        <v>4210</v>
+        <v>4660</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +4122,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46278.47916666666</v>
+        <v>46279.47916666666</v>
       </c>
       <c r="B144">
-        <v>4220</v>
+        <v>4660</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +4136,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46278.48958333334</v>
+        <v>46279.48958333334</v>
       </c>
       <c r="B145">
-        <v>4220</v>
+        <v>4660</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +4150,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46278.5</v>
+        <v>46279.5</v>
       </c>
       <c r="B146">
-        <v>4230</v>
+        <v>4680</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +4164,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46278.51041666666</v>
+        <v>46279.51041666666</v>
       </c>
       <c r="B147">
-        <v>4240</v>
+        <v>4710</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +4178,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46278.52083333334</v>
+        <v>46279.52083333334</v>
       </c>
       <c r="B148">
-        <v>4250</v>
+        <v>4740</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +4192,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46278.53125</v>
+        <v>46279.53125</v>
       </c>
       <c r="B149">
-        <v>4260</v>
+        <v>4770</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +4206,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46278.54166666666</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="B150">
-        <v>4270</v>
+        <v>4810</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +4220,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46278.55208333334</v>
+        <v>46279.55208333334</v>
       </c>
       <c r="B151">
-        <v>4280</v>
+        <v>4840</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +4234,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46278.5625</v>
+        <v>46279.5625</v>
       </c>
       <c r="B152">
-        <v>4280</v>
+        <v>4870</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +4248,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46278.57291666666</v>
+        <v>46279.57291666666</v>
       </c>
       <c r="B153">
-        <v>4290</v>
+        <v>4900</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +4262,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46278.58333333334</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="B154">
-        <v>4300</v>
+        <v>4920</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +4276,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46278.59375</v>
+        <v>46279.59375</v>
       </c>
       <c r="B155">
-        <v>4310</v>
+        <v>4950</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +4290,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46278.60416666666</v>
+        <v>46279.60416666666</v>
       </c>
       <c r="B156">
-        <v>4330</v>
+        <v>4990</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +4304,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46278.61458333334</v>
+        <v>46279.61458333334</v>
       </c>
       <c r="B157">
-        <v>4370</v>
+        <v>5050</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +4318,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46278.625</v>
+        <v>46279.625</v>
       </c>
       <c r="B158">
-        <v>4430</v>
+        <v>5130</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +4332,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46278.63541666666</v>
+        <v>46279.63541666666</v>
       </c>
       <c r="B159">
-        <v>4510</v>
+        <v>5240</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +4346,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46278.64583333334</v>
+        <v>46279.64583333334</v>
       </c>
       <c r="B160">
-        <v>4610</v>
+        <v>5380</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +4360,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46278.65625</v>
+        <v>46279.65625</v>
       </c>
       <c r="B161">
-        <v>4740</v>
+        <v>5550</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +4374,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46278.66666666666</v>
+        <v>46279.66666666666</v>
       </c>
       <c r="B162">
-        <v>4890</v>
+        <v>5730</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +4388,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46278.67708333334</v>
+        <v>46279.67708333334</v>
       </c>
       <c r="B163">
-        <v>5040</v>
+        <v>5910</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +4402,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46278.6875</v>
+        <v>46279.6875</v>
       </c>
       <c r="B164">
-        <v>5200</v>
+        <v>6080</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +4416,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46278.69791666666</v>
+        <v>46279.69791666666</v>
       </c>
       <c r="B165">
-        <v>5340</v>
+        <v>6230</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +4430,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46278.70833333334</v>
+        <v>46279.70833333334</v>
       </c>
       <c r="B166">
-        <v>5480</v>
+        <v>6360</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +4444,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46278.71875</v>
+        <v>46279.71875</v>
       </c>
       <c r="B167">
-        <v>5600</v>
+        <v>6470</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +4458,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46278.72916666666</v>
+        <v>46279.72916666666</v>
       </c>
       <c r="B168">
-        <v>5710</v>
+        <v>6580</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +4472,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46278.73958333334</v>
+        <v>46279.73958333334</v>
       </c>
       <c r="B169">
-        <v>5810</v>
+        <v>6670</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +4486,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46278.75</v>
+        <v>46279.75</v>
       </c>
       <c r="B170">
-        <v>5900</v>
+        <v>6760</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +4500,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46278.76041666666</v>
+        <v>46279.76041666666</v>
       </c>
       <c r="B171">
-        <v>5980</v>
+        <v>6840</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +4514,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46278.77083333334</v>
+        <v>46279.77083333334</v>
       </c>
       <c r="B172">
-        <v>6040</v>
+        <v>6900</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +4528,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46278.78125</v>
+        <v>46279.78125</v>
       </c>
       <c r="B173">
-        <v>6080</v>
+        <v>6930</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +4542,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46278.79166666666</v>
+        <v>46279.79166666666</v>
       </c>
       <c r="B174">
-        <v>6120</v>
+        <v>6960</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +4556,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46278.80208333334</v>
+        <v>46279.80208333334</v>
       </c>
       <c r="B175">
-        <v>6140</v>
+        <v>6970</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +4570,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46278.8125</v>
+        <v>46279.8125</v>
       </c>
       <c r="B176">
-        <v>6140</v>
+        <v>6950</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4584,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46278.82291666666</v>
+        <v>46279.82291666666</v>
       </c>
       <c r="B177">
-        <v>6110</v>
+        <v>6900</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4598,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46278.83333333334</v>
+        <v>46279.83333333334</v>
       </c>
       <c r="B178">
-        <v>6060</v>
+        <v>6800</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4612,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46278.84375</v>
+        <v>46279.84375</v>
       </c>
       <c r="B179">
-        <v>6000</v>
+        <v>6680</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4626,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46278.85416666666</v>
+        <v>46279.85416666666</v>
       </c>
       <c r="B180">
-        <v>5930</v>
+        <v>6560</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4640,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46278.86458333334</v>
+        <v>46279.86458333334</v>
       </c>
       <c r="B181">
-        <v>5830</v>
+        <v>6460</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4654,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46278.875</v>
+        <v>46279.875</v>
       </c>
       <c r="B182">
-        <v>5720</v>
+        <v>6320</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4668,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46278.88541666666</v>
+        <v>46279.88541666666</v>
       </c>
       <c r="B183">
-        <v>5610</v>
+        <v>6180</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4682,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46278.89583333334</v>
+        <v>46279.89583333334</v>
       </c>
       <c r="B184">
-        <v>5500</v>
+        <v>6020</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4696,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46278.90625</v>
+        <v>46279.90625</v>
       </c>
       <c r="B185">
-        <v>5420</v>
+        <v>5870</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4710,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46278.91666666666</v>
+        <v>46279.91666666666</v>
       </c>
       <c r="B186">
-        <v>5320</v>
+        <v>5730</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4724,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46278.92708333334</v>
+        <v>46279.92708333334</v>
       </c>
       <c r="B187">
-        <v>5220</v>
+        <v>5580</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4738,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46278.9375</v>
+        <v>46279.9375</v>
       </c>
       <c r="B188">
-        <v>5120</v>
+        <v>5440</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4752,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46278.94791666666</v>
+        <v>46279.94791666666</v>
       </c>
       <c r="B189">
-        <v>5000</v>
+        <v>5330</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4766,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46278.95833333334</v>
+        <v>46279.95833333334</v>
       </c>
       <c r="B190">
-        <v>4940</v>
+        <v>5340</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4780,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46278.96875</v>
+        <v>46279.96875</v>
       </c>
       <c r="B191">
-        <v>4900</v>
+        <v>5270</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4794,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46278.97916666666</v>
+        <v>46279.97916666666</v>
       </c>
       <c r="B192">
-        <v>4830</v>
+        <v>5210</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4808,5392 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46278.98958333334</v>
+        <v>46279.98958333334</v>
       </c>
       <c r="B193">
-        <v>4780</v>
+        <v>5180</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B194">
+        <v>5130</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46280.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>5110</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46280.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>5090</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46280.03125</v>
+      </c>
+      <c r="B197">
+        <v>5070</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46280.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>5030</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46280.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>5000</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46280.0625</v>
+      </c>
+      <c r="B200">
+        <v>4990</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46280.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4980</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4980</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46280.09375</v>
+      </c>
+      <c r="B203">
+        <v>4980</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46280.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4980</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46280.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4990</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46280.125</v>
+      </c>
+      <c r="B206">
+        <v>5020</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46280.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>5030</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46280.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>5030</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46280.15625</v>
+      </c>
+      <c r="B209">
+        <v>5040</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46280.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>5090</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46280.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>5150</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46280.1875</v>
+      </c>
+      <c r="B212">
+        <v>5210</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46280.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>5280</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46280.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5370</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46280.21875</v>
+      </c>
+      <c r="B215">
+        <v>5460</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46280.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>5540</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46280.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>5650</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46280.25</v>
+      </c>
+      <c r="B218">
+        <v>5860</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46280.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>5960</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46280.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>6020</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46280.28125</v>
+      </c>
+      <c r="B221">
+        <v>6030</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46280.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>6020</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46280.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>6000</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46280.3125</v>
+      </c>
+      <c r="B224">
+        <v>5960</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46280.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>5890</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46280.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>5790</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46280.34375</v>
+      </c>
+      <c r="B227">
+        <v>5690</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46280.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>5580</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46280.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>5460</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46280.375</v>
+      </c>
+      <c r="B230">
+        <v>5340</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46280.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>5230</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46280.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>5120</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46280.40625</v>
+      </c>
+      <c r="B233">
+        <v>5030</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46280.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>4950</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46280.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>4880</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46280.4375</v>
+      </c>
+      <c r="B236">
+        <v>4820</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46280.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>4770</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46280.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>4690</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46280.46875</v>
+      </c>
+      <c r="B239">
+        <v>4670</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46280.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>4670</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46280.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>4670</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46280.5</v>
+      </c>
+      <c r="B242">
+        <v>4710</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46280.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>4740</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46280.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>4760</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46280.53125</v>
+      </c>
+      <c r="B245">
+        <v>4780</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46280.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>4800</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46280.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>4810</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46280.5625</v>
+      </c>
+      <c r="B248">
+        <v>4830</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46280.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>4860</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46280.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>4900</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46280.59375</v>
+      </c>
+      <c r="B251">
+        <v>4940</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46280.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>4990</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46280.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>5050</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46280.625</v>
+      </c>
+      <c r="B254">
+        <v>5150</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46280.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>5250</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46280.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>5380</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46280.65625</v>
+      </c>
+      <c r="B257">
+        <v>5520</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46280.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>5680</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46280.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>5830</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46280.6875</v>
+      </c>
+      <c r="B260">
+        <v>5980</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46280.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>6130</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46280.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>6290</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46280.71875</v>
+      </c>
+      <c r="B263">
+        <v>6410</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46280.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>6520</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46280.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>6630</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46280.75</v>
+      </c>
+      <c r="B266">
+        <v>6710</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46280.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>6790</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46280.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>6870</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46280.78125</v>
+      </c>
+      <c r="B269">
+        <v>6950</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46280.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>7040</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46280.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>7090</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46280.8125</v>
+      </c>
+      <c r="B272">
+        <v>7090</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46280.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>7060</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46280.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6940</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46280.84375</v>
+      </c>
+      <c r="B275">
+        <v>6800</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46280.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>6700</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46280.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>6590</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46280.875</v>
+      </c>
+      <c r="B278">
+        <v>6420</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46280.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>6290</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46280.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>6130</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46280.90625</v>
+      </c>
+      <c r="B281">
+        <v>5990</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46280.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5870</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46280.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5740</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46280.9375</v>
+      </c>
+      <c r="B284">
+        <v>5630</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46280.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5520</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5240</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46280.96875</v>
+      </c>
+      <c r="B287">
+        <v>5170</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46280.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>5120</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46280.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>5090</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B290">
+        <v>5040</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46281.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>5000</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46281.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4990</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46281.03125</v>
+      </c>
+      <c r="B293">
+        <v>4980</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46281.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4950</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46281.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4950</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46281.0625</v>
+      </c>
+      <c r="B296">
+        <v>4950</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46281.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4960</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46281.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>5010</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46281.09375</v>
+      </c>
+      <c r="B299">
+        <v>5040</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46281.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>5070</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46281.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>5100</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46281.125</v>
+      </c>
+      <c r="B302">
+        <v>5130</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46281.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>5150</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46281.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>5160</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46281.15625</v>
+      </c>
+      <c r="B305">
+        <v>5160</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46281.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>5160</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46281.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>5170</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46281.1875</v>
+      </c>
+      <c r="B308">
+        <v>5210</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46281.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5270</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46281.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5350</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46281.21875</v>
+      </c>
+      <c r="B311">
+        <v>5450</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46281.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5550</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46281.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5660</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46281.25</v>
+      </c>
+      <c r="B314">
+        <v>5850</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46281.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>5940</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46281.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6000</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46281.28125</v>
+      </c>
+      <c r="B317">
+        <v>6020</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46281.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6000</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46281.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>5950</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46281.3125</v>
+      </c>
+      <c r="B320">
+        <v>5880</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46281.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>5780</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46281.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>5620</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46281.34375</v>
+      </c>
+      <c r="B323">
+        <v>5480</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46281.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>5330</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46281.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>5180</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46281.375</v>
+      </c>
+      <c r="B326">
+        <v>5040</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46281.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>4890</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46281.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4760</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46281.40625</v>
+      </c>
+      <c r="B329">
+        <v>4630</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4500</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46281.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4400</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46281.4375</v>
+      </c>
+      <c r="B332">
+        <v>4300</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46281.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>4200</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46281.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>4120</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46281.46875</v>
+      </c>
+      <c r="B335">
+        <v>4100</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46281.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>4100</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46281.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>4100</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46281.5</v>
+      </c>
+      <c r="B338">
+        <v>4110</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46281.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>4170</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46281.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>4220</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46281.53125</v>
+      </c>
+      <c r="B341">
+        <v>4300</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46281.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>4380</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46281.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>4470</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46281.5625</v>
+      </c>
+      <c r="B344">
+        <v>4530</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46281.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>4610</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46281.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>4690</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46281.59375</v>
+      </c>
+      <c r="B347">
+        <v>4770</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46281.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>4840</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46281.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>4920</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46281.625</v>
+      </c>
+      <c r="B350">
+        <v>5020</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46281.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>5140</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46281.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>5260</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46281.65625</v>
+      </c>
+      <c r="B353">
+        <v>5380</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46281.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>5510</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46281.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>5650</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46281.6875</v>
+      </c>
+      <c r="B356">
+        <v>5770</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46281.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>5890</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46281.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6030</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46281.71875</v>
+      </c>
+      <c r="B359">
+        <v>6140</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46281.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6250</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46281.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>6370</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46281.75</v>
+      </c>
+      <c r="B362">
+        <v>6490</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46281.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>6610</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46281.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>6720</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46281.78125</v>
+      </c>
+      <c r="B365">
+        <v>6810</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46281.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>6920</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46281.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>6970</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46281.8125</v>
+      </c>
+      <c r="B368">
+        <v>6970</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46281.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>6940</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46281.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6790</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46281.84375</v>
+      </c>
+      <c r="B371">
+        <v>6650</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46281.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6540</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46281.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6420</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46281.875</v>
+      </c>
+      <c r="B374">
+        <v>6250</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46281.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6110</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46281.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5980</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46281.90625</v>
+      </c>
+      <c r="B377">
+        <v>5860</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46281.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5760</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46281.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5650</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46281.9375</v>
+      </c>
+      <c r="B380">
+        <v>5530</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46281.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5420</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46281.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5290</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46281.96875</v>
+      </c>
+      <c r="B383">
+        <v>5230</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46281.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5180</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46281.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5130</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B386">
+        <v>5070</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46282.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>5040</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46282.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>5020</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46282.03125</v>
+      </c>
+      <c r="B389">
+        <v>5010</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46282.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>5010</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46282.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>5010</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46282.0625</v>
+      </c>
+      <c r="B392">
+        <v>5020</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46282.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>5050</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46282.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>5100</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46282.09375</v>
+      </c>
+      <c r="B395">
+        <v>5130</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46282.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>5160</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46282.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>5170</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46282.125</v>
+      </c>
+      <c r="B398">
+        <v>5150</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46282.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>5150</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46282.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>5150</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46282.15625</v>
+      </c>
+      <c r="B401">
+        <v>5150</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46282.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>5170</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46282.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>5220</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46282.1875</v>
+      </c>
+      <c r="B404">
+        <v>5270</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46282.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>5330</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46282.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5390</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46282.21875</v>
+      </c>
+      <c r="B407">
+        <v>5480</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46282.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>5560</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46282.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>5690</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46282.25</v>
+      </c>
+      <c r="B410">
+        <v>5900</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46282.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>5990</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46282.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>6010</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46282.28125</v>
+      </c>
+      <c r="B413">
+        <v>6010</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46282.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>5980</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46282.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>5890</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46282.3125</v>
+      </c>
+      <c r="B416">
+        <v>5810</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46282.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>5710</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46282.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>5570</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46282.34375</v>
+      </c>
+      <c r="B419">
+        <v>5420</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46282.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>5260</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46282.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>5090</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46282.375</v>
+      </c>
+      <c r="B422">
+        <v>4920</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46282.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>4760</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46282.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>4620</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46282.40625</v>
+      </c>
+      <c r="B425">
+        <v>4490</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46282.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>4310</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46282.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>4220</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46282.4375</v>
+      </c>
+      <c r="B428">
+        <v>4160</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46282.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>4120</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46282.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>4120</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46282.46875</v>
+      </c>
+      <c r="B431">
+        <v>4140</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46282.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>4160</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46282.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>4180</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46282.5</v>
+      </c>
+      <c r="B434">
+        <v>4220</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46282.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>4260</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46282.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>4300</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46282.53125</v>
+      </c>
+      <c r="B437">
+        <v>4350</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46282.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>4410</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46282.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>4480</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46282.5625</v>
+      </c>
+      <c r="B440">
+        <v>4560</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46282.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>4630</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46282.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>4730</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46282.59375</v>
+      </c>
+      <c r="B443">
+        <v>4810</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46282.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>4890</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46282.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>4980</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46282.625</v>
+      </c>
+      <c r="B446">
+        <v>5070</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46282.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>5180</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46282.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>5310</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46282.65625</v>
+      </c>
+      <c r="B449">
+        <v>5450</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46282.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>5630</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46282.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>5780</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46282.6875</v>
+      </c>
+      <c r="B452">
+        <v>5930</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46282.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>6060</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46282.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>6200</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46282.71875</v>
+      </c>
+      <c r="B455">
+        <v>6300</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46282.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>6400</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46282.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>6500</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46282.75</v>
+      </c>
+      <c r="B458">
+        <v>6590</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46282.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>6680</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46282.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>6780</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46282.78125</v>
+      </c>
+      <c r="B461">
+        <v>6870</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46282.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>6980</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46282.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>7030</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46282.8125</v>
+      </c>
+      <c r="B464">
+        <v>7020</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46282.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>6980</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>6840</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46282.84375</v>
+      </c>
+      <c r="B467">
+        <v>6690</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46282.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>6590</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46282.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>6470</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46282.875</v>
+      </c>
+      <c r="B470">
+        <v>6290</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46282.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>6140</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46282.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>6000</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46282.90625</v>
+      </c>
+      <c r="B473">
+        <v>5870</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46282.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>5780</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46282.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>5690</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46282.9375</v>
+      </c>
+      <c r="B476">
+        <v>5590</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46282.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>5470</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46282.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>5250</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46282.96875</v>
+      </c>
+      <c r="B479">
+        <v>5180</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46282.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>5130</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46282.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>5090</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B482">
+        <v>5040</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" s="2">
+        <v>46283.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>5010</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" s="2">
+        <v>46283.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>4990</v>
+      </c>
+      <c r="C484">
+        <v>3</v>
+      </c>
+      <c r="D484" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" s="2">
+        <v>46283.03125</v>
+      </c>
+      <c r="B485">
+        <v>4960</v>
+      </c>
+      <c r="C485">
+        <v>4</v>
+      </c>
+      <c r="D485" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" s="2">
+        <v>46283.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>4930</v>
+      </c>
+      <c r="C486">
+        <v>5</v>
+      </c>
+      <c r="D486" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" s="2">
+        <v>46283.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>4930</v>
+      </c>
+      <c r="C487">
+        <v>6</v>
+      </c>
+      <c r="D487" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" s="2">
+        <v>46283.0625</v>
+      </c>
+      <c r="B488">
+        <v>4930</v>
+      </c>
+      <c r="C488">
+        <v>7</v>
+      </c>
+      <c r="D488" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" s="2">
+        <v>46283.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>4940</v>
+      </c>
+      <c r="C489">
+        <v>8</v>
+      </c>
+      <c r="D489" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" s="2">
+        <v>46283.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>5020</v>
+      </c>
+      <c r="C490">
+        <v>9</v>
+      </c>
+      <c r="D490" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" s="2">
+        <v>46283.09375</v>
+      </c>
+      <c r="B491">
+        <v>5060</v>
+      </c>
+      <c r="C491">
+        <v>10</v>
+      </c>
+      <c r="D491" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="2">
+        <v>46283.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>5100</v>
+      </c>
+      <c r="C492">
+        <v>11</v>
+      </c>
+      <c r="D492" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" s="2">
+        <v>46283.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>5140</v>
+      </c>
+      <c r="C493">
+        <v>12</v>
+      </c>
+      <c r="D493" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" s="2">
+        <v>46283.125</v>
+      </c>
+      <c r="B494">
+        <v>5170</v>
+      </c>
+      <c r="C494">
+        <v>13</v>
+      </c>
+      <c r="D494" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" s="2">
+        <v>46283.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>5180</v>
+      </c>
+      <c r="C495">
+        <v>14</v>
+      </c>
+      <c r="D495" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" s="2">
+        <v>46283.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>5180</v>
+      </c>
+      <c r="C496">
+        <v>15</v>
+      </c>
+      <c r="D496" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" s="2">
+        <v>46283.15625</v>
+      </c>
+      <c r="B497">
+        <v>5190</v>
+      </c>
+      <c r="C497">
+        <v>16</v>
+      </c>
+      <c r="D497" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" s="2">
+        <v>46283.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>5210</v>
+      </c>
+      <c r="C498">
+        <v>17</v>
+      </c>
+      <c r="D498" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" s="2">
+        <v>46283.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>5240</v>
+      </c>
+      <c r="C499">
+        <v>18</v>
+      </c>
+      <c r="D499" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" s="2">
+        <v>46283.1875</v>
+      </c>
+      <c r="B500">
+        <v>5290</v>
+      </c>
+      <c r="C500">
+        <v>19</v>
+      </c>
+      <c r="D500" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" s="2">
+        <v>46283.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>5350</v>
+      </c>
+      <c r="C501">
+        <v>20</v>
+      </c>
+      <c r="D501" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" s="2">
+        <v>46283.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>5410</v>
+      </c>
+      <c r="C502">
+        <v>21</v>
+      </c>
+      <c r="D502" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" s="2">
+        <v>46283.21875</v>
+      </c>
+      <c r="B503">
+        <v>5510</v>
+      </c>
+      <c r="C503">
+        <v>22</v>
+      </c>
+      <c r="D503" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="2">
+        <v>46283.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>5620</v>
+      </c>
+      <c r="C504">
+        <v>23</v>
+      </c>
+      <c r="D504" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="2">
+        <v>46283.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>5750</v>
+      </c>
+      <c r="C505">
+        <v>24</v>
+      </c>
+      <c r="D505" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="2">
+        <v>46283.25</v>
+      </c>
+      <c r="B506">
+        <v>5960</v>
+      </c>
+      <c r="C506">
+        <v>25</v>
+      </c>
+      <c r="D506" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="2">
+        <v>46283.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>6080</v>
+      </c>
+      <c r="C507">
+        <v>26</v>
+      </c>
+      <c r="D507" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="2">
+        <v>46283.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>6170</v>
+      </c>
+      <c r="C508">
+        <v>27</v>
+      </c>
+      <c r="D508" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="2">
+        <v>46283.28125</v>
+      </c>
+      <c r="B509">
+        <v>6190</v>
+      </c>
+      <c r="C509">
+        <v>28</v>
+      </c>
+      <c r="D509" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="2">
+        <v>46283.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>6190</v>
+      </c>
+      <c r="C510">
+        <v>29</v>
+      </c>
+      <c r="D510" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="2">
+        <v>46283.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>6190</v>
+      </c>
+      <c r="C511">
+        <v>30</v>
+      </c>
+      <c r="D511" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="2">
+        <v>46283.3125</v>
+      </c>
+      <c r="B512">
+        <v>6190</v>
+      </c>
+      <c r="C512">
+        <v>31</v>
+      </c>
+      <c r="D512" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="2">
+        <v>46283.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>6140</v>
+      </c>
+      <c r="C513">
+        <v>32</v>
+      </c>
+      <c r="D513" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="2">
+        <v>46283.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>6020</v>
+      </c>
+      <c r="C514">
+        <v>33</v>
+      </c>
+      <c r="D514" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="2">
+        <v>46283.34375</v>
+      </c>
+      <c r="B515">
+        <v>5870</v>
+      </c>
+      <c r="C515">
+        <v>34</v>
+      </c>
+      <c r="D515" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="2">
+        <v>46283.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>5730</v>
+      </c>
+      <c r="C516">
+        <v>35</v>
+      </c>
+      <c r="D516" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="2">
+        <v>46283.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>5590</v>
+      </c>
+      <c r="C517">
+        <v>36</v>
+      </c>
+      <c r="D517" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="2">
+        <v>46283.375</v>
+      </c>
+      <c r="B518">
+        <v>5450</v>
+      </c>
+      <c r="C518">
+        <v>37</v>
+      </c>
+      <c r="D518" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>5310</v>
+      </c>
+      <c r="C519">
+        <v>38</v>
+      </c>
+      <c r="D519" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>5180</v>
+      </c>
+      <c r="C520">
+        <v>39</v>
+      </c>
+      <c r="D520" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B521">
+        <v>5060</v>
+      </c>
+      <c r="C521">
+        <v>40</v>
+      </c>
+      <c r="D521" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" s="2">
+        <v>46283.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>4920</v>
+      </c>
+      <c r="C522">
+        <v>41</v>
+      </c>
+      <c r="D522" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" s="2">
+        <v>46283.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>4820</v>
+      </c>
+      <c r="C523">
+        <v>42</v>
+      </c>
+      <c r="D523" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" s="2">
+        <v>46283.4375</v>
+      </c>
+      <c r="B524">
+        <v>4760</v>
+      </c>
+      <c r="C524">
+        <v>43</v>
+      </c>
+      <c r="D524" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" s="2">
+        <v>46283.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>4710</v>
+      </c>
+      <c r="C525">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" s="2">
+        <v>46283.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>4660</v>
+      </c>
+      <c r="C526">
+        <v>45</v>
+      </c>
+      <c r="D526" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" s="2">
+        <v>46283.46875</v>
+      </c>
+      <c r="B527">
+        <v>4650</v>
+      </c>
+      <c r="C527">
+        <v>46</v>
+      </c>
+      <c r="D527" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" s="2">
+        <v>46283.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>4650</v>
+      </c>
+      <c r="C528">
+        <v>47</v>
+      </c>
+      <c r="D528" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" s="2">
+        <v>46283.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>4650</v>
+      </c>
+      <c r="C529">
+        <v>48</v>
+      </c>
+      <c r="D529" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" s="2">
+        <v>46283.5</v>
+      </c>
+      <c r="B530">
+        <v>4660</v>
+      </c>
+      <c r="C530">
+        <v>49</v>
+      </c>
+      <c r="D530" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" s="2">
+        <v>46283.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>4680</v>
+      </c>
+      <c r="C531">
+        <v>50</v>
+      </c>
+      <c r="D531" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" s="2">
+        <v>46283.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>4710</v>
+      </c>
+      <c r="C532">
+        <v>51</v>
+      </c>
+      <c r="D532" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" s="2">
+        <v>46283.53125</v>
+      </c>
+      <c r="B533">
+        <v>4740</v>
+      </c>
+      <c r="C533">
+        <v>52</v>
+      </c>
+      <c r="D533" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" s="2">
+        <v>46283.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>4790</v>
+      </c>
+      <c r="C534">
+        <v>53</v>
+      </c>
+      <c r="D534" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" s="2">
+        <v>46283.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>4850</v>
+      </c>
+      <c r="C535">
+        <v>54</v>
+      </c>
+      <c r="D535" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" s="2">
+        <v>46283.5625</v>
+      </c>
+      <c r="B536">
+        <v>4900</v>
+      </c>
+      <c r="C536">
+        <v>55</v>
+      </c>
+      <c r="D536" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" s="2">
+        <v>46283.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>4970</v>
+      </c>
+      <c r="C537">
+        <v>56</v>
+      </c>
+      <c r="D537" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" s="2">
+        <v>46283.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>5040</v>
+      </c>
+      <c r="C538">
+        <v>57</v>
+      </c>
+      <c r="D538" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" s="2">
+        <v>46283.59375</v>
+      </c>
+      <c r="B539">
+        <v>5120</v>
+      </c>
+      <c r="C539">
+        <v>58</v>
+      </c>
+      <c r="D539" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" s="2">
+        <v>46283.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>5180</v>
+      </c>
+      <c r="C540">
+        <v>59</v>
+      </c>
+      <c r="D540" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" s="2">
+        <v>46283.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>5260</v>
+      </c>
+      <c r="C541">
+        <v>60</v>
+      </c>
+      <c r="D541" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" s="2">
+        <v>46283.625</v>
+      </c>
+      <c r="B542">
+        <v>5340</v>
+      </c>
+      <c r="C542">
+        <v>61</v>
+      </c>
+      <c r="D542" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" s="2">
+        <v>46283.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>5430</v>
+      </c>
+      <c r="C543">
+        <v>62</v>
+      </c>
+      <c r="D543" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" s="2">
+        <v>46283.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>5510</v>
+      </c>
+      <c r="C544">
+        <v>63</v>
+      </c>
+      <c r="D544" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" s="2">
+        <v>46283.65625</v>
+      </c>
+      <c r="B545">
+        <v>5610</v>
+      </c>
+      <c r="C545">
+        <v>64</v>
+      </c>
+      <c r="D545" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" s="2">
+        <v>46283.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>5710</v>
+      </c>
+      <c r="C546">
+        <v>65</v>
+      </c>
+      <c r="D546" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" s="2">
+        <v>46283.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>5820</v>
+      </c>
+      <c r="C547">
+        <v>66</v>
+      </c>
+      <c r="D547" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" s="2">
+        <v>46283.6875</v>
+      </c>
+      <c r="B548">
+        <v>5940</v>
+      </c>
+      <c r="C548">
+        <v>67</v>
+      </c>
+      <c r="D548" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" s="2">
+        <v>46283.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>6050</v>
+      </c>
+      <c r="C549">
+        <v>68</v>
+      </c>
+      <c r="D549" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" s="2">
+        <v>46283.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>6180</v>
+      </c>
+      <c r="C550">
+        <v>69</v>
+      </c>
+      <c r="D550" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" s="2">
+        <v>46283.71875</v>
+      </c>
+      <c r="B551">
+        <v>6290</v>
+      </c>
+      <c r="C551">
+        <v>70</v>
+      </c>
+      <c r="D551" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" s="2">
+        <v>46283.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>6410</v>
+      </c>
+      <c r="C552">
+        <v>71</v>
+      </c>
+      <c r="D552" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" s="2">
+        <v>46283.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>6510</v>
+      </c>
+      <c r="C553">
+        <v>72</v>
+      </c>
+      <c r="D553" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" s="2">
+        <v>46283.75</v>
+      </c>
+      <c r="B554">
+        <v>6610</v>
+      </c>
+      <c r="C554">
+        <v>73</v>
+      </c>
+      <c r="D554" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" s="2">
+        <v>46283.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>6720</v>
+      </c>
+      <c r="C555">
+        <v>74</v>
+      </c>
+      <c r="D555" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" s="2">
+        <v>46283.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>6800</v>
+      </c>
+      <c r="C556">
+        <v>75</v>
+      </c>
+      <c r="D556" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" s="2">
+        <v>46283.78125</v>
+      </c>
+      <c r="B557">
+        <v>6870</v>
+      </c>
+      <c r="C557">
+        <v>76</v>
+      </c>
+      <c r="D557" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" s="2">
+        <v>46283.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>6930</v>
+      </c>
+      <c r="C558">
+        <v>77</v>
+      </c>
+      <c r="D558" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" s="2">
+        <v>46283.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>6980</v>
+      </c>
+      <c r="C559">
+        <v>78</v>
+      </c>
+      <c r="D559" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" s="2">
+        <v>46283.8125</v>
+      </c>
+      <c r="B560">
+        <v>6970</v>
+      </c>
+      <c r="C560">
+        <v>79</v>
+      </c>
+      <c r="D560" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" s="2">
+        <v>46283.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>6920</v>
+      </c>
+      <c r="C561">
+        <v>80</v>
+      </c>
+      <c r="D561" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" s="2">
+        <v>46283.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>6780</v>
+      </c>
+      <c r="C562">
+        <v>81</v>
+      </c>
+      <c r="D562" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" s="2">
+        <v>46283.84375</v>
+      </c>
+      <c r="B563">
+        <v>6630</v>
+      </c>
+      <c r="C563">
+        <v>82</v>
+      </c>
+      <c r="D563" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" s="2">
+        <v>46283.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>6540</v>
+      </c>
+      <c r="C564">
+        <v>83</v>
+      </c>
+      <c r="D564" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" s="2">
+        <v>46283.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>6450</v>
+      </c>
+      <c r="C565">
+        <v>84</v>
+      </c>
+      <c r="D565" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" s="2">
+        <v>46283.875</v>
+      </c>
+      <c r="B566">
+        <v>6290</v>
+      </c>
+      <c r="C566">
+        <v>85</v>
+      </c>
+      <c r="D566" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" s="2">
+        <v>46283.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>6140</v>
+      </c>
+      <c r="C567">
+        <v>86</v>
+      </c>
+      <c r="D567" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="2">
+        <v>46283.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>5990</v>
+      </c>
+      <c r="C568">
+        <v>87</v>
+      </c>
+      <c r="D568" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="2">
+        <v>46283.90625</v>
+      </c>
+      <c r="B569">
+        <v>5860</v>
+      </c>
+      <c r="C569">
+        <v>88</v>
+      </c>
+      <c r="D569" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="2">
+        <v>46283.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>5770</v>
+      </c>
+      <c r="C570">
+        <v>89</v>
+      </c>
+      <c r="D570" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="2">
+        <v>46283.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>5650</v>
+      </c>
+      <c r="C571">
+        <v>90</v>
+      </c>
+      <c r="D571" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="2">
+        <v>46283.9375</v>
+      </c>
+      <c r="B572">
+        <v>5530</v>
+      </c>
+      <c r="C572">
+        <v>91</v>
+      </c>
+      <c r="D572" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="2">
+        <v>46283.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>5420</v>
+      </c>
+      <c r="C573">
+        <v>92</v>
+      </c>
+      <c r="D573" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
+      <c r="A574" s="2">
+        <v>46283.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>5300</v>
+      </c>
+      <c r="C574">
+        <v>93</v>
+      </c>
+      <c r="D574" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4">
+      <c r="A575" s="2">
+        <v>46283.96875</v>
+      </c>
+      <c r="B575">
+        <v>5240</v>
+      </c>
+      <c r="C575">
+        <v>94</v>
+      </c>
+      <c r="D575" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4">
+      <c r="A576" s="2">
+        <v>46283.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>5190</v>
+      </c>
+      <c r="C576">
+        <v>95</v>
+      </c>
+      <c r="D576" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
+      <c r="A577" s="2">
+        <v>46283.98958333334</v>
+      </c>
+      <c r="B577">
+        <v>5140</v>
+      </c>
+      <c r="C577">
+        <v>96</v>
+      </c>
+      <c r="D577" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,868 +28,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
-  </si>
-  <si>
-    <t>20.09.202639</t>
-  </si>
-  <si>
-    <t>20.09.202640</t>
-  </si>
-  <si>
-    <t>20.09.202641</t>
-  </si>
-  <si>
-    <t>20.09.202642</t>
-  </si>
-  <si>
-    <t>20.09.202643</t>
-  </si>
-  <si>
-    <t>20.09.202644</t>
-  </si>
-  <si>
-    <t>20.09.202645</t>
-  </si>
-  <si>
-    <t>20.09.202646</t>
-  </si>
-  <si>
-    <t>20.09.202647</t>
-  </si>
-  <si>
-    <t>20.09.202648</t>
-  </si>
-  <si>
-    <t>20.09.202649</t>
-  </si>
-  <si>
-    <t>20.09.202650</t>
-  </si>
-  <si>
-    <t>20.09.202651</t>
-  </si>
-  <si>
-    <t>20.09.202652</t>
-  </si>
-  <si>
-    <t>20.09.202653</t>
-  </si>
-  <si>
-    <t>20.09.202654</t>
-  </si>
-  <si>
-    <t>20.09.202655</t>
-  </si>
-  <si>
-    <t>20.09.202656</t>
-  </si>
-  <si>
-    <t>20.09.202657</t>
-  </si>
-  <si>
-    <t>20.09.202658</t>
-  </si>
-  <si>
-    <t>20.09.202659</t>
-  </si>
-  <si>
-    <t>20.09.202660</t>
-  </si>
-  <si>
-    <t>20.09.202661</t>
-  </si>
-  <si>
-    <t>20.09.202662</t>
-  </si>
-  <si>
-    <t>20.09.202663</t>
-  </si>
-  <si>
-    <t>20.09.202664</t>
-  </si>
-  <si>
-    <t>20.09.202665</t>
-  </si>
-  <si>
-    <t>20.09.202666</t>
-  </si>
-  <si>
-    <t>20.09.202667</t>
-  </si>
-  <si>
-    <t>20.09.202668</t>
-  </si>
-  <si>
-    <t>20.09.202669</t>
-  </si>
-  <si>
-    <t>20.09.202670</t>
-  </si>
-  <si>
-    <t>20.09.202671</t>
-  </si>
-  <si>
-    <t>20.09.202672</t>
-  </si>
-  <si>
-    <t>20.09.202673</t>
-  </si>
-  <si>
-    <t>20.09.202674</t>
-  </si>
-  <si>
-    <t>20.09.202675</t>
-  </si>
-  <si>
-    <t>20.09.202676</t>
-  </si>
-  <si>
-    <t>20.09.202677</t>
-  </si>
-  <si>
-    <t>20.09.202678</t>
-  </si>
-  <si>
-    <t>20.09.202679</t>
-  </si>
-  <si>
-    <t>20.09.202680</t>
-  </si>
-  <si>
-    <t>20.09.202681</t>
-  </si>
-  <si>
-    <t>20.09.202682</t>
-  </si>
-  <si>
-    <t>20.09.202683</t>
-  </si>
-  <si>
-    <t>20.09.202684</t>
-  </si>
-  <si>
-    <t>20.09.202685</t>
-  </si>
-  <si>
-    <t>20.09.202686</t>
-  </si>
-  <si>
-    <t>20.09.202687</t>
-  </si>
-  <si>
-    <t>20.09.202688</t>
-  </si>
-  <si>
-    <t>20.09.202689</t>
-  </si>
-  <si>
-    <t>20.09.202690</t>
-  </si>
-  <si>
-    <t>20.09.202691</t>
-  </si>
-  <si>
-    <t>20.09.202692</t>
-  </si>
-  <si>
-    <t>20.09.202693</t>
-  </si>
-  <si>
-    <t>20.09.202694</t>
-  </si>
-  <si>
-    <t>20.09.202695</t>
-  </si>
-  <si>
-    <t>20.09.202696</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
+  </si>
+  <si>
+    <t>30.09.202640</t>
+  </si>
+  <si>
+    <t>30.09.202641</t>
+  </si>
+  <si>
+    <t>30.09.202642</t>
+  </si>
+  <si>
+    <t>30.09.202643</t>
+  </si>
+  <si>
+    <t>30.09.202644</t>
+  </si>
+  <si>
+    <t>30.09.202645</t>
+  </si>
+  <si>
+    <t>30.09.202646</t>
+  </si>
+  <si>
+    <t>30.09.202647</t>
+  </si>
+  <si>
+    <t>30.09.202648</t>
+  </si>
+  <si>
+    <t>30.09.202649</t>
+  </si>
+  <si>
+    <t>30.09.202650</t>
+  </si>
+  <si>
+    <t>30.09.202651</t>
+  </si>
+  <si>
+    <t>30.09.202652</t>
+  </si>
+  <si>
+    <t>30.09.202653</t>
+  </si>
+  <si>
+    <t>30.09.202654</t>
+  </si>
+  <si>
+    <t>30.09.202655</t>
+  </si>
+  <si>
+    <t>30.09.202656</t>
+  </si>
+  <si>
+    <t>30.09.202657</t>
+  </si>
+  <si>
+    <t>30.09.202658</t>
+  </si>
+  <si>
+    <t>30.09.202659</t>
+  </si>
+  <si>
+    <t>30.09.202660</t>
+  </si>
+  <si>
+    <t>30.09.202661</t>
+  </si>
+  <si>
+    <t>30.09.202662</t>
+  </si>
+  <si>
+    <t>30.09.202663</t>
+  </si>
+  <si>
+    <t>30.09.202664</t>
+  </si>
+  <si>
+    <t>30.09.202665</t>
+  </si>
+  <si>
+    <t>30.09.202666</t>
+  </si>
+  <si>
+    <t>30.09.202667</t>
+  </si>
+  <si>
+    <t>30.09.202668</t>
+  </si>
+  <si>
+    <t>30.09.202669</t>
+  </si>
+  <si>
+    <t>30.09.202670</t>
+  </si>
+  <si>
+    <t>30.09.202671</t>
+  </si>
+  <si>
+    <t>30.09.202672</t>
+  </si>
+  <si>
+    <t>30.09.202673</t>
+  </si>
+  <si>
+    <t>30.09.202674</t>
+  </si>
+  <si>
+    <t>30.09.202675</t>
+  </si>
+  <si>
+    <t>30.09.202676</t>
+  </si>
+  <si>
+    <t>30.09.202677</t>
+  </si>
+  <si>
+    <t>30.09.202678</t>
+  </si>
+  <si>
+    <t>30.09.202679</t>
+  </si>
+  <si>
+    <t>30.09.202680</t>
+  </si>
+  <si>
+    <t>30.09.202681</t>
+  </si>
+  <si>
+    <t>30.09.202682</t>
+  </si>
+  <si>
+    <t>30.09.202683</t>
+  </si>
+  <si>
+    <t>30.09.202684</t>
+  </si>
+  <si>
+    <t>30.09.202685</t>
+  </si>
+  <si>
+    <t>30.09.202686</t>
+  </si>
+  <si>
+    <t>30.09.202687</t>
+  </si>
+  <si>
+    <t>30.09.202688</t>
+  </si>
+  <si>
+    <t>30.09.202689</t>
+  </si>
+  <si>
+    <t>30.09.202690</t>
+  </si>
+  <si>
+    <t>30.09.202691</t>
+  </si>
+  <si>
+    <t>30.09.202692</t>
+  </si>
+  <si>
+    <t>30.09.202693</t>
+  </si>
+  <si>
+    <t>30.09.202694</t>
+  </si>
+  <si>
+    <t>30.09.202695</t>
+  </si>
+  <si>
+    <t>30.09.202696</t>
   </si>
 </sst>
 </file>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>5040</v>
+        <v>4660</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>5010</v>
+        <v>4640</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>4990</v>
+        <v>4600</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>4960</v>
+        <v>4560</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>4930</v>
+        <v>4520</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>4930</v>
+        <v>4490</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>4930</v>
+        <v>4460</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>4940</v>
+        <v>4450</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>5020</v>
+        <v>4450</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>5060</v>
+        <v>4450</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>5100</v>
+        <v>4460</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>5140</v>
+        <v>4470</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>5170</v>
+        <v>4510</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>5180</v>
+        <v>4560</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>5180</v>
+        <v>4610</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>5190</v>
+        <v>4680</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>5210</v>
+        <v>4760</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>5240</v>
+        <v>4840</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>5290</v>
+        <v>4940</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>5350</v>
+        <v>5040</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>5410</v>
+        <v>5170</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>5510</v>
+        <v>5290</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>5620</v>
+        <v>5420</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>5750</v>
+        <v>5540</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>5960</v>
+        <v>5680</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>6080</v>
+        <v>5810</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>6170</v>
+        <v>5910</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>6190</v>
+        <v>6000</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>6190</v>
+        <v>6080</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>6190</v>
+        <v>6120</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>6190</v>
+        <v>6130</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>6140</v>
+        <v>6120</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>6020</v>
+        <v>6080</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>5870</v>
+        <v>6000</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>5730</v>
+        <v>5920</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>5590</v>
+        <v>5820</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>5450</v>
+        <v>5710</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>5310</v>
+        <v>5600</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>5180</v>
+        <v>5500</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>5060</v>
+        <v>5380</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>4920</v>
+        <v>5250</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>4820</v>
+        <v>5160</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>4760</v>
+        <v>5100</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>4710</v>
+        <v>5050</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>4660</v>
+        <v>5010</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>4650</v>
+        <v>5000</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>4650</v>
+        <v>5000</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>4650</v>
+        <v>5000</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>4660</v>
+        <v>5000</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>4680</v>
+        <v>5000</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1970,10 +1970,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>4710</v>
+        <v>5010</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>4740</v>
+        <v>5020</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>4790</v>
+        <v>5060</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>4850</v>
+        <v>5080</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>4970</v>
+        <v>5120</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>5040</v>
+        <v>5160</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>5120</v>
+        <v>5190</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>5180</v>
+        <v>5220</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
         <v>5340</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>5430</v>
+        <v>5420</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>5510</v>
+        <v>5520</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>5610</v>
+        <v>5640</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>5710</v>
+        <v>5770</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>5820</v>
+        <v>5890</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>5940</v>
+        <v>6010</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>6050</v>
+        <v>6150</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>6180</v>
+        <v>6290</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>6290</v>
+        <v>6420</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>6410</v>
+        <v>6560</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>6510</v>
+        <v>6720</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>6610</v>
+        <v>6890</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>6720</v>
+        <v>7030</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>6800</v>
+        <v>7110</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>6870</v>
+        <v>7150</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>6930</v>
+        <v>7150</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>6980</v>
+        <v>7140</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>6970</v>
+        <v>7090</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>6920</v>
+        <v>7020</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>6780</v>
+        <v>6900</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>6630</v>
+        <v>6760</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>6540</v>
+        <v>6640</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>6450</v>
+        <v>6500</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>6290</v>
+        <v>6320</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>6140</v>
+        <v>6180</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>5860</v>
+        <v>5880</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>5770</v>
+        <v>5730</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>5530</v>
+        <v>5490</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>5420</v>
+        <v>5370</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>5220</v>
+        <v>5280</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>5150</v>
+        <v>5220</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>4980</v>
+        <v>5060</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>4920</v>
+        <v>5020</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>4870</v>
+        <v>5000</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>4820</v>
+        <v>5000</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>4790</v>
+        <v>4970</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>4750</v>
+        <v>4950</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>4740</v>
+        <v>4940</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>4730</v>
+        <v>4940</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>4730</v>
+        <v>4920</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>4730</v>
+        <v>4920</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>4740</v>
+        <v>4920</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>4740</v>
+        <v>4930</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>4750</v>
+        <v>4960</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>4760</v>
+        <v>4970</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>4770</v>
+        <v>4980</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>4780</v>
+        <v>5010</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>4780</v>
+        <v>5040</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>4790</v>
+        <v>5100</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2866,10 +2866,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>4810</v>
+        <v>5170</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2880,10 +2880,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>4830</v>
+        <v>5270</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>4860</v>
+        <v>5370</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>4900</v>
+        <v>5500</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>4940</v>
+        <v>5630</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>4990</v>
+        <v>5790</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>5040</v>
+        <v>5970</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>5090</v>
+        <v>6090</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>5130</v>
+        <v>6180</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>5160</v>
+        <v>6240</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>5180</v>
+        <v>6260</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>5180</v>
+        <v>6270</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>5170</v>
+        <v>6240</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>5140</v>
+        <v>6190</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>5090</v>
+        <v>6060</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -3076,10 +3076,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>5030</v>
+        <v>5950</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>4970</v>
+        <v>5810</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>4900</v>
+        <v>5660</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>4840</v>
+        <v>5520</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>4790</v>
+        <v>5370</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>4750</v>
+        <v>5220</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>4720</v>
+        <v>5090</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>4700</v>
+        <v>4930</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>4700</v>
+        <v>4810</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>4700</v>
+        <v>4750</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
         <v>4710</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>4720</v>
+        <v>4670</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>4730</v>
+        <v>4670</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>4750</v>
+        <v>4670</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>4780</v>
+        <v>4680</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>4810</v>
+        <v>4720</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>4830</v>
+        <v>4740</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>4850</v>
+        <v>4750</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>4870</v>
+        <v>4770</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>4890</v>
+        <v>4790</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>4910</v>
+        <v>4820</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>4920</v>
+        <v>4850</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>4940</v>
+        <v>4900</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
         <v>4950</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>4980</v>
+        <v>5000</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>5010</v>
+        <v>5070</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>5040</v>
+        <v>5170</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>5090</v>
+        <v>5280</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>5160</v>
+        <v>5390</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>5240</v>
+        <v>5510</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>5330</v>
+        <v>5650</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>5430</v>
+        <v>5790</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>5530</v>
+        <v>5920</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>5630</v>
+        <v>6050</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>5720</v>
+        <v>6190</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>5820</v>
+        <v>6330</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>5910</v>
+        <v>6470</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>6010</v>
+        <v>6610</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>6110</v>
+        <v>6740</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3636,10 +3636,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>6200</v>
+        <v>6870</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>6280</v>
+        <v>6960</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>6320</v>
+        <v>7020</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>6360</v>
+        <v>7050</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>6360</v>
+        <v>7050</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>6330</v>
+        <v>7030</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>6280</v>
+        <v>6990</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>6200</v>
+        <v>6880</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>6100</v>
+        <v>6770</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>6000</v>
+        <v>6650</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>5920</v>
+        <v>6510</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>5800</v>
+        <v>6330</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>5680</v>
+        <v>6160</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>5550</v>
+        <v>6020</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>5420</v>
+        <v>5910</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>5300</v>
+        <v>5810</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>5180</v>
+        <v>5670</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>5080</v>
+        <v>5560</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>4970</v>
+        <v>5450</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>4850</v>
+        <v>5330</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3916,10 +3916,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>4790</v>
+        <v>5280</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3930,10 +3930,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>4740</v>
+        <v>5220</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>4700</v>
+        <v>5170</v>
       </c>
       <c r="C193">
         <v>96</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>4650</v>
+        <v>5090</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>4610</v>
+        <v>5050</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>4590</v>
+        <v>5040</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>4550</v>
+        <v>5040</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>4510</v>
+        <v>5040</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>4480</v>
+        <v>5040</v>
       </c>
       <c r="C199">
         <v>6</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>4460</v>
+        <v>5050</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -4056,10 +4056,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>4440</v>
+        <v>5070</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>4410</v>
+        <v>5080</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="C203">
         <v>10</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>4400</v>
+        <v>5110</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>4400</v>
+        <v>5110</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>4400</v>
+        <v>5130</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>4400</v>
+        <v>5140</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>4400</v>
+        <v>5140</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>4410</v>
+        <v>5140</v>
       </c>
       <c r="C209">
         <v>16</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>4430</v>
+        <v>5140</v>
       </c>
       <c r="C210">
         <v>17</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>4440</v>
+        <v>5150</v>
       </c>
       <c r="C211">
         <v>18</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>4460</v>
+        <v>5210</v>
       </c>
       <c r="C212">
         <v>19</v>
@@ -4224,10 +4224,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>4470</v>
+        <v>5300</v>
       </c>
       <c r="C213">
         <v>20</v>
@@ -4238,10 +4238,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>4470</v>
+        <v>5440</v>
       </c>
       <c r="C214">
         <v>21</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>4470</v>
+        <v>5580</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>4470</v>
+        <v>5720</v>
       </c>
       <c r="C216">
         <v>23</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>4470</v>
+        <v>5860</v>
       </c>
       <c r="C217">
         <v>24</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>4470</v>
+        <v>6060</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>4450</v>
+        <v>6190</v>
       </c>
       <c r="C219">
         <v>26</v>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>4450</v>
+        <v>6260</v>
       </c>
       <c r="C220">
         <v>27</v>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>4410</v>
+        <v>6290</v>
       </c>
       <c r="C221">
         <v>28</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>4350</v>
+        <v>6280</v>
       </c>
       <c r="C222">
         <v>29</v>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>4290</v>
+        <v>6240</v>
       </c>
       <c r="C223">
         <v>30</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>4220</v>
+        <v>6150</v>
       </c>
       <c r="C224">
         <v>31</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>4140</v>
+        <v>6010</v>
       </c>
       <c r="C225">
         <v>32</v>
@@ -4406,10 +4406,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>4020</v>
+        <v>5850</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>3910</v>
+        <v>5660</v>
       </c>
       <c r="C227">
         <v>34</v>
@@ -4434,10 +4434,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>3810</v>
+        <v>5450</v>
       </c>
       <c r="C228">
         <v>35</v>
@@ -4448,10 +4448,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>3700</v>
+        <v>5230</v>
       </c>
       <c r="C229">
         <v>36</v>
@@ -4462,10 +4462,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>3590</v>
+        <v>4950</v>
       </c>
       <c r="C230">
         <v>37</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>3490</v>
+        <v>4740</v>
       </c>
       <c r="C231">
         <v>38</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B232">
-        <v>3400</v>
+        <v>4550</v>
       </c>
       <c r="C232">
         <v>39</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B233">
-        <v>3330</v>
+        <v>4380</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B234">
-        <v>3260</v>
+        <v>4250</v>
       </c>
       <c r="C234">
         <v>41</v>
@@ -4532,10 +4532,10 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B235">
-        <v>3210</v>
+        <v>4140</v>
       </c>
       <c r="C235">
         <v>42</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B236">
-        <v>3180</v>
+        <v>4050</v>
       </c>
       <c r="C236">
         <v>43</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B237">
-        <v>3150</v>
+        <v>3980</v>
       </c>
       <c r="C237">
         <v>44</v>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B238">
-        <v>3110</v>
+        <v>3910</v>
       </c>
       <c r="C238">
         <v>45</v>
@@ -4588,10 +4588,10 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B239">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="C239">
         <v>46</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B240">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="C240">
         <v>47</v>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B241">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="C241">
         <v>48</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B242">
-        <v>3100</v>
+        <v>3950</v>
       </c>
       <c r="C242">
         <v>49</v>
@@ -4644,10 +4644,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B243">
-        <v>3100</v>
+        <v>3980</v>
       </c>
       <c r="C243">
         <v>50</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B244">
-        <v>3100</v>
+        <v>4010</v>
       </c>
       <c r="C244">
         <v>51</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B245">
-        <v>3100</v>
+        <v>4060</v>
       </c>
       <c r="C245">
         <v>52</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B246">
-        <v>3130</v>
+        <v>4130</v>
       </c>
       <c r="C246">
         <v>53</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B247">
-        <v>3170</v>
+        <v>4190</v>
       </c>
       <c r="C247">
         <v>54</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B248">
-        <v>3220</v>
+        <v>4250</v>
       </c>
       <c r="C248">
         <v>55</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B249">
-        <v>3290</v>
+        <v>4310</v>
       </c>
       <c r="C249">
         <v>56</v>
@@ -4742,10 +4742,10 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B250">
-        <v>3360</v>
+        <v>4410</v>
       </c>
       <c r="C250">
         <v>57</v>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B251">
-        <v>3450</v>
+        <v>4510</v>
       </c>
       <c r="C251">
         <v>58</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B252">
-        <v>3540</v>
+        <v>4620</v>
       </c>
       <c r="C252">
         <v>59</v>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B253">
-        <v>3650</v>
+        <v>4750</v>
       </c>
       <c r="C253">
         <v>60</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B254">
-        <v>3770</v>
+        <v>4920</v>
       </c>
       <c r="C254">
         <v>61</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B255">
-        <v>3910</v>
+        <v>5080</v>
       </c>
       <c r="C255">
         <v>62</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B256">
-        <v>4050</v>
+        <v>5250</v>
       </c>
       <c r="C256">
         <v>63</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B257">
-        <v>4200</v>
+        <v>5430</v>
       </c>
       <c r="C257">
         <v>64</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B258">
-        <v>4350</v>
+        <v>5600</v>
       </c>
       <c r="C258">
         <v>65</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B259">
-        <v>4510</v>
+        <v>5780</v>
       </c>
       <c r="C259">
         <v>66</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B260">
-        <v>4660</v>
+        <v>5940</v>
       </c>
       <c r="C260">
         <v>67</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B261">
-        <v>4820</v>
+        <v>6100</v>
       </c>
       <c r="C261">
         <v>68</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B262">
-        <v>4980</v>
+        <v>6280</v>
       </c>
       <c r="C262">
         <v>69</v>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B263">
-        <v>5130</v>
+        <v>6430</v>
       </c>
       <c r="C263">
         <v>70</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B264">
-        <v>5270</v>
+        <v>6580</v>
       </c>
       <c r="C264">
         <v>71</v>
@@ -4952,10 +4952,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B265">
-        <v>5420</v>
+        <v>6720</v>
       </c>
       <c r="C265">
         <v>72</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B266">
-        <v>5560</v>
+        <v>6850</v>
       </c>
       <c r="C266">
         <v>73</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B267">
-        <v>5690</v>
+        <v>6970</v>
       </c>
       <c r="C267">
         <v>74</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B268">
-        <v>5800</v>
+        <v>7060</v>
       </c>
       <c r="C268">
         <v>75</v>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B269">
-        <v>5870</v>
+        <v>7120</v>
       </c>
       <c r="C269">
         <v>76</v>
@@ -5022,10 +5022,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B270">
-        <v>5920</v>
+        <v>7130</v>
       </c>
       <c r="C270">
         <v>77</v>
@@ -5036,10 +5036,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B271">
-        <v>5950</v>
+        <v>7130</v>
       </c>
       <c r="C271">
         <v>78</v>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B272">
-        <v>5940</v>
+        <v>7100</v>
       </c>
       <c r="C272">
         <v>79</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B273">
-        <v>5910</v>
+        <v>7040</v>
       </c>
       <c r="C273">
         <v>80</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B274">
-        <v>5810</v>
+        <v>6910</v>
       </c>
       <c r="C274">
         <v>81</v>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B275">
-        <v>5720</v>
+        <v>6780</v>
       </c>
       <c r="C275">
         <v>82</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B276">
-        <v>5640</v>
+        <v>6680</v>
       </c>
       <c r="C276">
         <v>83</v>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B277">
-        <v>5540</v>
+        <v>6540</v>
       </c>
       <c r="C277">
         <v>84</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B278">
-        <v>5400</v>
+        <v>6350</v>
       </c>
       <c r="C278">
         <v>85</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B279">
-        <v>5280</v>
+        <v>6190</v>
       </c>
       <c r="C279">
         <v>86</v>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B280">
-        <v>5170</v>
+        <v>6030</v>
       </c>
       <c r="C280">
         <v>87</v>
@@ -5176,10 +5176,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B281">
-        <v>5070</v>
+        <v>5920</v>
       </c>
       <c r="C281">
         <v>88</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B282">
-        <v>5000</v>
+        <v>5850</v>
       </c>
       <c r="C282">
         <v>89</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B283">
-        <v>4910</v>
+        <v>5750</v>
       </c>
       <c r="C283">
         <v>90</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B284">
-        <v>4830</v>
+        <v>5640</v>
       </c>
       <c r="C284">
         <v>91</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B285">
-        <v>4740</v>
+        <v>5530</v>
       </c>
       <c r="C285">
         <v>92</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="2">
-        <v>46285.95833333334</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="B286">
-        <v>4750</v>
+        <v>5400</v>
       </c>
       <c r="C286">
         <v>93</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="2">
-        <v>46285.96875</v>
+        <v>46295.96875</v>
       </c>
       <c r="B287">
-        <v>4690</v>
+        <v>5330</v>
       </c>
       <c r="C287">
         <v>94</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="2">
-        <v>46285.97916666666</v>
+        <v>46295.97916666666</v>
       </c>
       <c r="B288">
-        <v>4640</v>
+        <v>5290</v>
       </c>
       <c r="C288">
         <v>95</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="2">
-        <v>46285.98958333334</v>
+        <v>46295.98958333334</v>
       </c>
       <c r="B289">
-        <v>4590</v>
+        <v>5250</v>
       </c>
       <c r="C289">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,868 +28,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
-  </si>
-  <si>
-    <t>30.09.202640</t>
-  </si>
-  <si>
-    <t>30.09.202641</t>
-  </si>
-  <si>
-    <t>30.09.202642</t>
-  </si>
-  <si>
-    <t>30.09.202643</t>
-  </si>
-  <si>
-    <t>30.09.202644</t>
-  </si>
-  <si>
-    <t>30.09.202645</t>
-  </si>
-  <si>
-    <t>30.09.202646</t>
-  </si>
-  <si>
-    <t>30.09.202647</t>
-  </si>
-  <si>
-    <t>30.09.202648</t>
-  </si>
-  <si>
-    <t>30.09.202649</t>
-  </si>
-  <si>
-    <t>30.09.202650</t>
-  </si>
-  <si>
-    <t>30.09.202651</t>
-  </si>
-  <si>
-    <t>30.09.202652</t>
-  </si>
-  <si>
-    <t>30.09.202653</t>
-  </si>
-  <si>
-    <t>30.09.202654</t>
-  </si>
-  <si>
-    <t>30.09.202655</t>
-  </si>
-  <si>
-    <t>30.09.202656</t>
-  </si>
-  <si>
-    <t>30.09.202657</t>
-  </si>
-  <si>
-    <t>30.09.202658</t>
-  </si>
-  <si>
-    <t>30.09.202659</t>
-  </si>
-  <si>
-    <t>30.09.202660</t>
-  </si>
-  <si>
-    <t>30.09.202661</t>
-  </si>
-  <si>
-    <t>30.09.202662</t>
-  </si>
-  <si>
-    <t>30.09.202663</t>
-  </si>
-  <si>
-    <t>30.09.202664</t>
-  </si>
-  <si>
-    <t>30.09.202665</t>
-  </si>
-  <si>
-    <t>30.09.202666</t>
-  </si>
-  <si>
-    <t>30.09.202667</t>
-  </si>
-  <si>
-    <t>30.09.202668</t>
-  </si>
-  <si>
-    <t>30.09.202669</t>
-  </si>
-  <si>
-    <t>30.09.202670</t>
-  </si>
-  <si>
-    <t>30.09.202671</t>
-  </si>
-  <si>
-    <t>30.09.202672</t>
-  </si>
-  <si>
-    <t>30.09.202673</t>
-  </si>
-  <si>
-    <t>30.09.202674</t>
-  </si>
-  <si>
-    <t>30.09.202675</t>
-  </si>
-  <si>
-    <t>30.09.202676</t>
-  </si>
-  <si>
-    <t>30.09.202677</t>
-  </si>
-  <si>
-    <t>30.09.202678</t>
-  </si>
-  <si>
-    <t>30.09.202679</t>
-  </si>
-  <si>
-    <t>30.09.202680</t>
-  </si>
-  <si>
-    <t>30.09.202681</t>
-  </si>
-  <si>
-    <t>30.09.202682</t>
-  </si>
-  <si>
-    <t>30.09.202683</t>
-  </si>
-  <si>
-    <t>30.09.202684</t>
-  </si>
-  <si>
-    <t>30.09.202685</t>
-  </si>
-  <si>
-    <t>30.09.202686</t>
-  </si>
-  <si>
-    <t>30.09.202687</t>
-  </si>
-  <si>
-    <t>30.09.202688</t>
-  </si>
-  <si>
-    <t>30.09.202689</t>
-  </si>
-  <si>
-    <t>30.09.202690</t>
-  </si>
-  <si>
-    <t>30.09.202691</t>
-  </si>
-  <si>
-    <t>30.09.202692</t>
-  </si>
-  <si>
-    <t>30.09.202693</t>
-  </si>
-  <si>
-    <t>30.09.202694</t>
-  </si>
-  <si>
-    <t>30.09.202695</t>
-  </si>
-  <si>
-    <t>30.09.202696</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
-        <v>4660</v>
+        <v>5120</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>4640</v>
+        <v>5060</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>4600</v>
+        <v>5020</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>4560</v>
+        <v>5000</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>4520</v>
+        <v>5000</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>4490</v>
+        <v>5000</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>4460</v>
+        <v>5000</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>4450</v>
+        <v>5010</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>4450</v>
+        <v>5060</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>4450</v>
+        <v>5090</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>4460</v>
+        <v>5110</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>4470</v>
+        <v>5130</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>4510</v>
+        <v>5160</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>4560</v>
+        <v>5170</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>4610</v>
+        <v>5180</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>4680</v>
+        <v>5210</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
-        <v>4760</v>
+        <v>5210</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>4840</v>
+        <v>5260</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
-        <v>4940</v>
+        <v>5330</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>5040</v>
+        <v>5420</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
-        <v>5170</v>
+        <v>5550</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>5290</v>
+        <v>5680</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>5420</v>
+        <v>5820</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>5540</v>
+        <v>5960</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
-        <v>5680</v>
+        <v>6120</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
-        <v>5810</v>
+        <v>6230</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>5910</v>
+        <v>6320</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
-        <v>6000</v>
+        <v>6330</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
-        <v>6080</v>
+        <v>6330</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
-        <v>6120</v>
+        <v>6300</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
-        <v>6130</v>
+        <v>6230</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
         <v>6120</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>6080</v>
+        <v>5940</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>6000</v>
+        <v>5790</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>5920</v>
+        <v>5620</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
-        <v>5820</v>
+        <v>5450</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
-        <v>5710</v>
+        <v>5270</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>5600</v>
+        <v>5100</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>5500</v>
+        <v>4940</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
-        <v>5380</v>
+        <v>4790</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>5250</v>
+        <v>4640</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>5160</v>
+        <v>4510</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
-        <v>5100</v>
+        <v>4380</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
-        <v>5050</v>
+        <v>4260</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>5010</v>
+        <v>4130</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>5000</v>
+        <v>4030</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>5000</v>
+        <v>4010</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1970,10 +1970,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
-        <v>5020</v>
+        <v>4060</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
-        <v>5060</v>
+        <v>4120</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
-        <v>5080</v>
+        <v>4180</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
-        <v>5100</v>
+        <v>4230</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
-        <v>5120</v>
+        <v>4270</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
-        <v>5160</v>
+        <v>4330</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
-        <v>5190</v>
+        <v>4390</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>5220</v>
+        <v>4480</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
-        <v>5270</v>
+        <v>4610</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
-        <v>5340</v>
+        <v>4790</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>5420</v>
+        <v>4960</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>5520</v>
+        <v>5140</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>5640</v>
+        <v>5300</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>5770</v>
+        <v>5470</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>5890</v>
+        <v>5650</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>6010</v>
+        <v>5820</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>6150</v>
+        <v>6000</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>6290</v>
+        <v>6180</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>6420</v>
+        <v>6340</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
-        <v>6560</v>
+        <v>6500</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>6720</v>
+        <v>6660</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>6890</v>
+        <v>6820</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>7030</v>
+        <v>6950</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>7110</v>
+        <v>7040</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
-        <v>7150</v>
+        <v>7070</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
-        <v>7150</v>
+        <v>7090</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>7140</v>
+        <v>7090</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>7090</v>
+        <v>7040</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>7020</v>
+        <v>6980</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
-        <v>6900</v>
+        <v>6840</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>6760</v>
+        <v>6710</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
-        <v>6640</v>
+        <v>6600</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>6500</v>
+        <v>6460</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>6320</v>
+        <v>6300</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>6180</v>
+        <v>6170</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>5880</v>
+        <v>5910</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
-        <v>5730</v>
+        <v>5820</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
-        <v>5600</v>
+        <v>5720</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
-        <v>5490</v>
+        <v>5610</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
-        <v>5370</v>
+        <v>5500</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
-        <v>5280</v>
+        <v>5290</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
-        <v>5220</v>
+        <v>5230</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
-        <v>5180</v>
+        <v>5200</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>5130</v>
+        <v>5180</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>5060</v>
+        <v>5150</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>5020</v>
+        <v>5120</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>5000</v>
+        <v>5110</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
-        <v>4970</v>
+        <v>5100</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
-        <v>4950</v>
+        <v>5100</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
-        <v>4940</v>
+        <v>5100</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
-        <v>4940</v>
+        <v>5110</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
-        <v>4920</v>
+        <v>5150</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
-        <v>4920</v>
+        <v>5170</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
-        <v>4920</v>
+        <v>5170</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
-        <v>4930</v>
+        <v>5170</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
-        <v>4960</v>
+        <v>5150</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
-        <v>4970</v>
+        <v>5140</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
-        <v>4980</v>
+        <v>5140</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
-        <v>5010</v>
+        <v>5150</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
-        <v>5040</v>
+        <v>5150</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
-        <v>5100</v>
+        <v>5190</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2866,10 +2866,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>5170</v>
+        <v>5260</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2880,10 +2880,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>5270</v>
+        <v>5380</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>5370</v>
+        <v>5540</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>5500</v>
+        <v>5690</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>5630</v>
+        <v>5850</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
-        <v>5790</v>
+        <v>6000</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
-        <v>5970</v>
+        <v>6150</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>6090</v>
+        <v>6250</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>6180</v>
+        <v>6310</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>6240</v>
+        <v>6330</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>6260</v>
+        <v>6330</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>6270</v>
+        <v>6310</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>6240</v>
+        <v>6250</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
-        <v>6190</v>
+        <v>6130</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>6060</v>
+        <v>5880</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -3076,10 +3076,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
-        <v>5950</v>
+        <v>5680</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
-        <v>5810</v>
+        <v>5500</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
-        <v>5660</v>
+        <v>5340</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>5520</v>
+        <v>5180</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
-        <v>5370</v>
+        <v>5030</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
-        <v>5220</v>
+        <v>4890</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
-        <v>5090</v>
+        <v>4760</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>4930</v>
+        <v>4640</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>4810</v>
+        <v>4530</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
-        <v>4750</v>
+        <v>4430</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
-        <v>4710</v>
+        <v>4340</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
-        <v>4670</v>
+        <v>4250</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
-        <v>4670</v>
+        <v>4180</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>4670</v>
+        <v>4130</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
-        <v>4680</v>
+        <v>4090</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
-        <v>4700</v>
+        <v>4080</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>4720</v>
+        <v>4080</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
-        <v>4740</v>
+        <v>4080</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>4750</v>
+        <v>4100</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>4770</v>
+        <v>4200</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>4790</v>
+        <v>4280</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
-        <v>4820</v>
+        <v>4330</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
-        <v>4850</v>
+        <v>4350</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
-        <v>4900</v>
+        <v>4370</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
-        <v>4950</v>
+        <v>4430</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
-        <v>5000</v>
+        <v>4490</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
-        <v>5070</v>
+        <v>4590</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
-        <v>5170</v>
+        <v>4750</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
-        <v>5280</v>
+        <v>4900</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>5390</v>
+        <v>5050</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>5510</v>
+        <v>5220</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>5650</v>
+        <v>5390</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>5790</v>
+        <v>5570</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>5920</v>
+        <v>5750</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>6050</v>
+        <v>5920</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>6190</v>
+        <v>6120</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>6330</v>
+        <v>6290</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>6470</v>
+        <v>6450</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
-        <v>6610</v>
+        <v>6620</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
-        <v>6740</v>
+        <v>6780</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3636,10 +3636,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
-        <v>6870</v>
+        <v>6920</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
-        <v>6960</v>
+        <v>7020</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
-        <v>7020</v>
+        <v>7080</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
-        <v>7050</v>
+        <v>7080</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>7050</v>
+        <v>7070</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
-        <v>7030</v>
+        <v>7040</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>6990</v>
+        <v>6970</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>6880</v>
+        <v>6850</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>6770</v>
+        <v>6730</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>6650</v>
+        <v>6610</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>6510</v>
+        <v>6480</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>6330</v>
+        <v>6290</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>6160</v>
+        <v>6120</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>6020</v>
+        <v>5960</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
-        <v>5910</v>
+        <v>5840</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>5810</v>
+        <v>5750</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>5670</v>
+        <v>5650</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>5560</v>
+        <v>5540</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
-        <v>5450</v>
+        <v>5430</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
-        <v>5330</v>
+        <v>5340</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3916,10 +3916,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
-        <v>5280</v>
+        <v>5250</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
         <v>5220</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>5170</v>
+        <v>5190</v>
       </c>
       <c r="C193">
         <v>96</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>5090</v>
+        <v>5150</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
-        <v>5050</v>
+        <v>5110</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
-        <v>5040</v>
+        <v>5080</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
-        <v>5040</v>
+        <v>5060</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>5040</v>
+        <v>5010</v>
       </c>
       <c r="C199">
         <v>6</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>5050</v>
+        <v>4990</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -4056,10 +4056,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>5070</v>
+        <v>4970</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>5080</v>
+        <v>4960</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>5100</v>
+        <v>4950</v>
       </c>
       <c r="C203">
         <v>10</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>5110</v>
+        <v>4950</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>5110</v>
+        <v>4940</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
-        <v>5130</v>
+        <v>4940</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
-        <v>5140</v>
+        <v>4950</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>5140</v>
+        <v>4950</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
-        <v>5140</v>
+        <v>4960</v>
       </c>
       <c r="C209">
         <v>16</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
-        <v>5140</v>
+        <v>4970</v>
       </c>
       <c r="C210">
         <v>17</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
-        <v>5150</v>
+        <v>4990</v>
       </c>
       <c r="C211">
         <v>18</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>5210</v>
+        <v>5010</v>
       </c>
       <c r="C212">
         <v>19</v>
@@ -4224,10 +4224,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>5300</v>
+        <v>5030</v>
       </c>
       <c r="C213">
         <v>20</v>
@@ -4238,10 +4238,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>5440</v>
+        <v>5050</v>
       </c>
       <c r="C214">
         <v>21</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>5580</v>
+        <v>5080</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>5720</v>
+        <v>5110</v>
       </c>
       <c r="C216">
         <v>23</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>5860</v>
+        <v>5160</v>
       </c>
       <c r="C217">
         <v>24</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>6060</v>
+        <v>5210</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>6190</v>
+        <v>5240</v>
       </c>
       <c r="C219">
         <v>26</v>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>6260</v>
+        <v>5260</v>
       </c>
       <c r="C220">
         <v>27</v>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>6290</v>
+        <v>5290</v>
       </c>
       <c r="C221">
         <v>28</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>6280</v>
+        <v>5320</v>
       </c>
       <c r="C222">
         <v>29</v>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>6240</v>
+        <v>5310</v>
       </c>
       <c r="C223">
         <v>30</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>6150</v>
+        <v>5280</v>
       </c>
       <c r="C224">
         <v>31</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>6010</v>
+        <v>5210</v>
       </c>
       <c r="C225">
         <v>32</v>
@@ -4406,10 +4406,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>5850</v>
+        <v>5070</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B227">
-        <v>5660</v>
+        <v>4940</v>
       </c>
       <c r="C227">
         <v>34</v>
@@ -4434,10 +4434,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B228">
-        <v>5450</v>
+        <v>4820</v>
       </c>
       <c r="C228">
         <v>35</v>
@@ -4448,10 +4448,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B229">
-        <v>5230</v>
+        <v>4690</v>
       </c>
       <c r="C229">
         <v>36</v>
@@ -4462,10 +4462,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B230">
-        <v>4950</v>
+        <v>4560</v>
       </c>
       <c r="C230">
         <v>37</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B231">
-        <v>4740</v>
+        <v>4430</v>
       </c>
       <c r="C231">
         <v>38</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B232">
-        <v>4550</v>
+        <v>4300</v>
       </c>
       <c r="C232">
         <v>39</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B233">
-        <v>4380</v>
+        <v>4190</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B234">
-        <v>4250</v>
+        <v>4090</v>
       </c>
       <c r="C234">
         <v>41</v>
@@ -4532,10 +4532,10 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B235">
-        <v>4140</v>
+        <v>3990</v>
       </c>
       <c r="C235">
         <v>42</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B236">
-        <v>4050</v>
+        <v>3910</v>
       </c>
       <c r="C236">
         <v>43</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B237">
-        <v>3980</v>
+        <v>3800</v>
       </c>
       <c r="C237">
         <v>44</v>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B238">
-        <v>3910</v>
+        <v>3670</v>
       </c>
       <c r="C238">
         <v>45</v>
@@ -4588,10 +4588,10 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B239">
-        <v>3900</v>
+        <v>3630</v>
       </c>
       <c r="C239">
         <v>46</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B240">
-        <v>3900</v>
+        <v>3630</v>
       </c>
       <c r="C240">
         <v>47</v>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B241">
-        <v>3900</v>
+        <v>3670</v>
       </c>
       <c r="C241">
         <v>48</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B242">
-        <v>3950</v>
+        <v>3690</v>
       </c>
       <c r="C242">
         <v>49</v>
@@ -4644,10 +4644,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B243">
-        <v>3980</v>
+        <v>3700</v>
       </c>
       <c r="C243">
         <v>50</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B244">
-        <v>4010</v>
+        <v>3700</v>
       </c>
       <c r="C244">
         <v>51</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B245">
-        <v>4060</v>
+        <v>3710</v>
       </c>
       <c r="C245">
         <v>52</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B246">
-        <v>4130</v>
+        <v>3730</v>
       </c>
       <c r="C246">
         <v>53</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B247">
-        <v>4190</v>
+        <v>3770</v>
       </c>
       <c r="C247">
         <v>54</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B248">
-        <v>4250</v>
+        <v>3810</v>
       </c>
       <c r="C248">
         <v>55</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B249">
-        <v>4310</v>
+        <v>3890</v>
       </c>
       <c r="C249">
         <v>56</v>
@@ -4742,10 +4742,10 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B250">
-        <v>4410</v>
+        <v>4000</v>
       </c>
       <c r="C250">
         <v>57</v>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B251">
-        <v>4510</v>
+        <v>4090</v>
       </c>
       <c r="C251">
         <v>58</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B252">
-        <v>4620</v>
+        <v>4200</v>
       </c>
       <c r="C252">
         <v>59</v>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B253">
-        <v>4750</v>
+        <v>4310</v>
       </c>
       <c r="C253">
         <v>60</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B254">
-        <v>4920</v>
+        <v>4410</v>
       </c>
       <c r="C254">
         <v>61</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B255">
-        <v>5080</v>
+        <v>4530</v>
       </c>
       <c r="C255">
         <v>62</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B256">
-        <v>5250</v>
+        <v>4660</v>
       </c>
       <c r="C256">
         <v>63</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B257">
-        <v>5430</v>
+        <v>4800</v>
       </c>
       <c r="C257">
         <v>64</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B258">
-        <v>5600</v>
+        <v>4950</v>
       </c>
       <c r="C258">
         <v>65</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B259">
-        <v>5780</v>
+        <v>5110</v>
       </c>
       <c r="C259">
         <v>66</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B260">
-        <v>5940</v>
+        <v>5280</v>
       </c>
       <c r="C260">
         <v>67</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B261">
-        <v>6100</v>
+        <v>5460</v>
       </c>
       <c r="C261">
         <v>68</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B262">
-        <v>6280</v>
+        <v>5660</v>
       </c>
       <c r="C262">
         <v>69</v>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B263">
-        <v>6430</v>
+        <v>5820</v>
       </c>
       <c r="C263">
         <v>70</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B264">
-        <v>6580</v>
+        <v>5980</v>
       </c>
       <c r="C264">
         <v>71</v>
@@ -4952,10 +4952,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B265">
-        <v>6720</v>
+        <v>6140</v>
       </c>
       <c r="C265">
         <v>72</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B266">
-        <v>6850</v>
+        <v>6250</v>
       </c>
       <c r="C266">
         <v>73</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B267">
-        <v>6970</v>
+        <v>6370</v>
       </c>
       <c r="C267">
         <v>74</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B268">
-        <v>7060</v>
+        <v>6460</v>
       </c>
       <c r="C268">
         <v>75</v>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B269">
-        <v>7120</v>
+        <v>6520</v>
       </c>
       <c r="C269">
         <v>76</v>
@@ -5022,10 +5022,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B270">
-        <v>7130</v>
+        <v>6570</v>
       </c>
       <c r="C270">
         <v>77</v>
@@ -5036,10 +5036,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B271">
-        <v>7130</v>
+        <v>6600</v>
       </c>
       <c r="C271">
         <v>78</v>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B272">
-        <v>7100</v>
+        <v>6560</v>
       </c>
       <c r="C272">
         <v>79</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B273">
-        <v>7040</v>
+        <v>6470</v>
       </c>
       <c r="C273">
         <v>80</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B274">
-        <v>6910</v>
+        <v>6310</v>
       </c>
       <c r="C274">
         <v>81</v>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B275">
-        <v>6780</v>
+        <v>6180</v>
       </c>
       <c r="C275">
         <v>82</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B276">
-        <v>6680</v>
+        <v>6020</v>
       </c>
       <c r="C276">
         <v>83</v>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B277">
-        <v>6540</v>
+        <v>5890</v>
       </c>
       <c r="C277">
         <v>84</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B278">
-        <v>6350</v>
+        <v>5760</v>
       </c>
       <c r="C278">
         <v>85</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B279">
-        <v>6190</v>
+        <v>5670</v>
       </c>
       <c r="C279">
         <v>86</v>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B280">
-        <v>6030</v>
+        <v>5540</v>
       </c>
       <c r="C280">
         <v>87</v>
@@ -5176,10 +5176,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B281">
-        <v>5920</v>
+        <v>5430</v>
       </c>
       <c r="C281">
         <v>88</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B282">
-        <v>5850</v>
+        <v>5330</v>
       </c>
       <c r="C282">
         <v>89</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B283">
-        <v>5750</v>
+        <v>5240</v>
       </c>
       <c r="C283">
         <v>90</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B284">
-        <v>5640</v>
+        <v>5160</v>
       </c>
       <c r="C284">
         <v>91</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B285">
-        <v>5530</v>
+        <v>5070</v>
       </c>
       <c r="C285">
         <v>92</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="2">
-        <v>46295.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B286">
-        <v>5400</v>
+        <v>5020</v>
       </c>
       <c r="C286">
         <v>93</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="2">
-        <v>46295.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B287">
-        <v>5330</v>
+        <v>4980</v>
       </c>
       <c r="C287">
         <v>94</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="2">
-        <v>46295.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B288">
-        <v>5290</v>
+        <v>4950</v>
       </c>
       <c r="C288">
         <v>95</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="2">
-        <v>46295.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B289">
-        <v>5250</v>
+        <v>4890</v>
       </c>
       <c r="C289">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,582 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>01.10.20261</t>
-  </si>
-  <si>
-    <t>01.10.20262</t>
-  </si>
-  <si>
-    <t>01.10.20263</t>
-  </si>
-  <si>
-    <t>01.10.20264</t>
-  </si>
-  <si>
-    <t>01.10.20265</t>
-  </si>
-  <si>
-    <t>01.10.20266</t>
-  </si>
-  <si>
-    <t>01.10.20267</t>
-  </si>
-  <si>
-    <t>01.10.20268</t>
-  </si>
-  <si>
-    <t>01.10.20269</t>
-  </si>
-  <si>
-    <t>01.10.202610</t>
-  </si>
-  <si>
-    <t>01.10.202611</t>
-  </si>
-  <si>
-    <t>01.10.202612</t>
-  </si>
-  <si>
-    <t>01.10.202613</t>
-  </si>
-  <si>
-    <t>01.10.202614</t>
-  </si>
-  <si>
-    <t>01.10.202615</t>
-  </si>
-  <si>
-    <t>01.10.202616</t>
-  </si>
-  <si>
-    <t>01.10.202617</t>
-  </si>
-  <si>
-    <t>01.10.202618</t>
-  </si>
-  <si>
-    <t>01.10.202619</t>
-  </si>
-  <si>
-    <t>01.10.202620</t>
-  </si>
-  <si>
-    <t>01.10.202621</t>
-  </si>
-  <si>
-    <t>01.10.202622</t>
-  </si>
-  <si>
-    <t>01.10.202623</t>
-  </si>
-  <si>
-    <t>01.10.202624</t>
-  </si>
-  <si>
-    <t>01.10.202625</t>
-  </si>
-  <si>
-    <t>01.10.202626</t>
-  </si>
-  <si>
-    <t>01.10.202627</t>
-  </si>
-  <si>
-    <t>01.10.202628</t>
-  </si>
-  <si>
-    <t>01.10.202629</t>
-  </si>
-  <si>
-    <t>01.10.202630</t>
-  </si>
-  <si>
-    <t>01.10.202631</t>
-  </si>
-  <si>
-    <t>01.10.202632</t>
-  </si>
-  <si>
-    <t>01.10.202633</t>
-  </si>
-  <si>
-    <t>01.10.202634</t>
-  </si>
-  <si>
-    <t>01.10.202635</t>
-  </si>
-  <si>
-    <t>01.10.202636</t>
-  </si>
-  <si>
-    <t>01.10.202637</t>
-  </si>
-  <si>
-    <t>01.10.202638</t>
-  </si>
-  <si>
-    <t>01.10.202639</t>
-  </si>
-  <si>
-    <t>01.10.202640</t>
-  </si>
-  <si>
-    <t>01.10.202641</t>
-  </si>
-  <si>
-    <t>01.10.202642</t>
-  </si>
-  <si>
-    <t>01.10.202643</t>
-  </si>
-  <si>
-    <t>01.10.202644</t>
-  </si>
-  <si>
-    <t>01.10.202645</t>
-  </si>
-  <si>
-    <t>01.10.202646</t>
-  </si>
-  <si>
-    <t>01.10.202647</t>
-  </si>
-  <si>
-    <t>01.10.202648</t>
-  </si>
-  <si>
-    <t>01.10.202649</t>
-  </si>
-  <si>
-    <t>01.10.202650</t>
-  </si>
-  <si>
-    <t>01.10.202651</t>
-  </si>
-  <si>
-    <t>01.10.202652</t>
-  </si>
-  <si>
-    <t>01.10.202653</t>
-  </si>
-  <si>
-    <t>01.10.202654</t>
-  </si>
-  <si>
-    <t>01.10.202655</t>
-  </si>
-  <si>
-    <t>01.10.202656</t>
-  </si>
-  <si>
-    <t>01.10.202657</t>
-  </si>
-  <si>
-    <t>01.10.202658</t>
-  </si>
-  <si>
-    <t>01.10.202659</t>
-  </si>
-  <si>
-    <t>01.10.202660</t>
-  </si>
-  <si>
-    <t>01.10.202661</t>
-  </si>
-  <si>
-    <t>01.10.202662</t>
-  </si>
-  <si>
-    <t>01.10.202663</t>
-  </si>
-  <si>
-    <t>01.10.202664</t>
-  </si>
-  <si>
-    <t>01.10.202665</t>
-  </si>
-  <si>
-    <t>01.10.202666</t>
-  </si>
-  <si>
-    <t>01.10.202667</t>
-  </si>
-  <si>
-    <t>01.10.202668</t>
-  </si>
-  <si>
-    <t>01.10.202669</t>
-  </si>
-  <si>
-    <t>01.10.202670</t>
-  </si>
-  <si>
-    <t>01.10.202671</t>
-  </si>
-  <si>
-    <t>01.10.202672</t>
-  </si>
-  <si>
-    <t>01.10.202673</t>
-  </si>
-  <si>
-    <t>01.10.202674</t>
-  </si>
-  <si>
-    <t>01.10.202675</t>
-  </si>
-  <si>
-    <t>01.10.202676</t>
-  </si>
-  <si>
-    <t>01.10.202677</t>
-  </si>
-  <si>
-    <t>01.10.202678</t>
-  </si>
-  <si>
-    <t>01.10.202679</t>
-  </si>
-  <si>
-    <t>01.10.202680</t>
-  </si>
-  <si>
-    <t>01.10.202681</t>
-  </si>
-  <si>
-    <t>01.10.202682</t>
-  </si>
-  <si>
-    <t>01.10.202683</t>
-  </si>
-  <si>
-    <t>01.10.202684</t>
-  </si>
-  <si>
-    <t>01.10.202685</t>
-  </si>
-  <si>
-    <t>01.10.202686</t>
-  </si>
-  <si>
-    <t>01.10.202687</t>
-  </si>
-  <si>
-    <t>01.10.202688</t>
-  </si>
-  <si>
-    <t>01.10.202689</t>
-  </si>
-  <si>
-    <t>01.10.202690</t>
-  </si>
-  <si>
-    <t>01.10.202691</t>
-  </si>
-  <si>
-    <t>01.10.202692</t>
-  </si>
-  <si>
-    <t>01.10.202693</t>
-  </si>
-  <si>
-    <t>01.10.202694</t>
-  </si>
-  <si>
-    <t>01.10.202695</t>
-  </si>
-  <si>
-    <t>01.10.202696</t>
-  </si>
-  <si>
-    <t>02.10.20261</t>
-  </si>
-  <si>
-    <t>02.10.20262</t>
-  </si>
-  <si>
-    <t>02.10.20263</t>
-  </si>
-  <si>
-    <t>02.10.20264</t>
-  </si>
-  <si>
-    <t>02.10.20265</t>
-  </si>
-  <si>
-    <t>02.10.20266</t>
-  </si>
-  <si>
-    <t>02.10.20267</t>
-  </si>
-  <si>
-    <t>02.10.20268</t>
-  </si>
-  <si>
-    <t>02.10.20269</t>
-  </si>
-  <si>
-    <t>02.10.202610</t>
-  </si>
-  <si>
-    <t>02.10.202611</t>
-  </si>
-  <si>
-    <t>02.10.202612</t>
-  </si>
-  <si>
-    <t>02.10.202613</t>
-  </si>
-  <si>
-    <t>02.10.202614</t>
-  </si>
-  <si>
-    <t>02.10.202615</t>
-  </si>
-  <si>
-    <t>02.10.202616</t>
-  </si>
-  <si>
-    <t>02.10.202617</t>
-  </si>
-  <si>
-    <t>02.10.202618</t>
-  </si>
-  <si>
-    <t>02.10.202619</t>
-  </si>
-  <si>
-    <t>02.10.202620</t>
-  </si>
-  <si>
-    <t>02.10.202621</t>
-  </si>
-  <si>
-    <t>02.10.202622</t>
-  </si>
-  <si>
-    <t>02.10.202623</t>
-  </si>
-  <si>
-    <t>02.10.202624</t>
-  </si>
-  <si>
-    <t>02.10.202625</t>
-  </si>
-  <si>
-    <t>02.10.202626</t>
-  </si>
-  <si>
-    <t>02.10.202627</t>
-  </si>
-  <si>
-    <t>02.10.202628</t>
-  </si>
-  <si>
-    <t>02.10.202629</t>
-  </si>
-  <si>
-    <t>02.10.202630</t>
-  </si>
-  <si>
-    <t>02.10.202631</t>
-  </si>
-  <si>
-    <t>02.10.202632</t>
-  </si>
-  <si>
-    <t>02.10.202633</t>
-  </si>
-  <si>
-    <t>02.10.202634</t>
-  </si>
-  <si>
-    <t>02.10.202635</t>
-  </si>
-  <si>
-    <t>02.10.202636</t>
-  </si>
-  <si>
-    <t>02.10.202637</t>
-  </si>
-  <si>
-    <t>02.10.202638</t>
-  </si>
-  <si>
-    <t>02.10.202639</t>
-  </si>
-  <si>
-    <t>02.10.202640</t>
-  </si>
-  <si>
-    <t>02.10.202641</t>
-  </si>
-  <si>
-    <t>02.10.202642</t>
-  </si>
-  <si>
-    <t>02.10.202643</t>
-  </si>
-  <si>
-    <t>02.10.202644</t>
-  </si>
-  <si>
-    <t>02.10.202645</t>
-  </si>
-  <si>
-    <t>02.10.202646</t>
-  </si>
-  <si>
-    <t>02.10.202647</t>
-  </si>
-  <si>
-    <t>02.10.202648</t>
-  </si>
-  <si>
-    <t>02.10.202649</t>
-  </si>
-  <si>
-    <t>02.10.202650</t>
-  </si>
-  <si>
-    <t>02.10.202651</t>
-  </si>
-  <si>
-    <t>02.10.202652</t>
-  </si>
-  <si>
-    <t>02.10.202653</t>
-  </si>
-  <si>
-    <t>02.10.202654</t>
-  </si>
-  <si>
-    <t>02.10.202655</t>
-  </si>
-  <si>
-    <t>02.10.202656</t>
-  </si>
-  <si>
-    <t>02.10.202657</t>
-  </si>
-  <si>
-    <t>02.10.202658</t>
-  </si>
-  <si>
-    <t>02.10.202659</t>
-  </si>
-  <si>
-    <t>02.10.202660</t>
-  </si>
-  <si>
-    <t>02.10.202661</t>
-  </si>
-  <si>
-    <t>02.10.202662</t>
-  </si>
-  <si>
-    <t>02.10.202663</t>
-  </si>
-  <si>
-    <t>02.10.202664</t>
-  </si>
-  <si>
-    <t>02.10.202665</t>
-  </si>
-  <si>
-    <t>02.10.202666</t>
-  </si>
-  <si>
-    <t>02.10.202667</t>
-  </si>
-  <si>
-    <t>02.10.202668</t>
-  </si>
-  <si>
-    <t>02.10.202669</t>
-  </si>
-  <si>
-    <t>02.10.202670</t>
-  </si>
-  <si>
-    <t>02.10.202671</t>
-  </si>
-  <si>
-    <t>02.10.202672</t>
-  </si>
-  <si>
-    <t>02.10.202673</t>
-  </si>
-  <si>
-    <t>02.10.202674</t>
-  </si>
-  <si>
-    <t>02.10.202675</t>
-  </si>
-  <si>
-    <t>02.10.202676</t>
-  </si>
-  <si>
-    <t>02.10.202677</t>
-  </si>
-  <si>
-    <t>02.10.202678</t>
-  </si>
-  <si>
-    <t>02.10.202679</t>
-  </si>
-  <si>
-    <t>02.10.202680</t>
-  </si>
-  <si>
-    <t>02.10.202681</t>
-  </si>
-  <si>
-    <t>02.10.202682</t>
-  </si>
-  <si>
-    <t>02.10.202683</t>
-  </si>
-  <si>
-    <t>02.10.202684</t>
-  </si>
-  <si>
-    <t>02.10.202685</t>
-  </si>
-  <si>
-    <t>02.10.202686</t>
-  </si>
-  <si>
-    <t>02.10.202687</t>
-  </si>
-  <si>
-    <t>02.10.202688</t>
-  </si>
-  <si>
-    <t>02.10.202689</t>
-  </si>
-  <si>
-    <t>02.10.202690</t>
-  </si>
-  <si>
-    <t>02.10.202691</t>
-  </si>
-  <si>
-    <t>02.10.202692</t>
-  </si>
-  <si>
-    <t>02.10.202693</t>
-  </si>
-  <si>
-    <t>02.10.202694</t>
-  </si>
-  <si>
-    <t>02.10.202695</t>
-  </si>
-  <si>
-    <t>02.10.202696</t>
-  </si>
-  <si>
     <t>03.10.20261</t>
   </si>
   <si>
@@ -890,6 +314,294 @@
   </si>
   <si>
     <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1270,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>5120</v>
+        <v>5150</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1284,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46296.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>5060</v>
+        <v>5110</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1298,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46296.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>5020</v>
+        <v>5080</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1312,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46296.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>5000</v>
+        <v>5060</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1326,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46296.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>5000</v>
+        <v>5030</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1340,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46296.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>5000</v>
+        <v>5010</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1354,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46296.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1368,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46296.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>5010</v>
+        <v>4970</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1382,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46296.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>5060</v>
+        <v>4960</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1396,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46296.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>5090</v>
+        <v>4950</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1410,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46296.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>5110</v>
+        <v>4950</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1424,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46296.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>5130</v>
+        <v>4940</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1438,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46296.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>5160</v>
+        <v>4940</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1452,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46296.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>5170</v>
+        <v>4950</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1466,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46296.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>5180</v>
+        <v>4950</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1480,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46296.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>5210</v>
+        <v>4960</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1494,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46296.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>5210</v>
+        <v>4970</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1508,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46296.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>5260</v>
+        <v>4990</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1522,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46296.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>5330</v>
+        <v>5010</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1536,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46296.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>5420</v>
+        <v>5030</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1550,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46296.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>5550</v>
+        <v>5050</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1564,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46296.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>5680</v>
+        <v>5080</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1578,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46296.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>5820</v>
+        <v>5110</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1592,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46296.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>5960</v>
+        <v>5160</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1606,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46296.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>6120</v>
+        <v>5210</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1620,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46296.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>6230</v>
+        <v>5240</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1634,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46296.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>6320</v>
+        <v>5260</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1648,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46296.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>6330</v>
+        <v>5290</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1662,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46296.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>6330</v>
+        <v>5320</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1676,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46296.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>6300</v>
+        <v>5310</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1690,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46296.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>6230</v>
+        <v>5280</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1704,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46296.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>6120</v>
+        <v>5210</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1718,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46296.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>5940</v>
+        <v>5070</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1732,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46296.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>5790</v>
+        <v>4940</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1746,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46296.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>5620</v>
+        <v>4820</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1760,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46296.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>5450</v>
+        <v>4690</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1774,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46296.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>5270</v>
+        <v>4560</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1788,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46296.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>5100</v>
+        <v>4430</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1802,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46296.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>4940</v>
+        <v>4300</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1816,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46296.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>4790</v>
+        <v>4190</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1830,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46296.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>4640</v>
+        <v>4090</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1844,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46296.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>4510</v>
+        <v>3990</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1858,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46296.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>4380</v>
+        <v>3910</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1872,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46296.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>4260</v>
+        <v>3800</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1886,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46296.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>4130</v>
+        <v>3670</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1900,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46296.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>4030</v>
+        <v>3630</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1914,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46296.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>4000</v>
+        <v>3630</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1928,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46296.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>4000</v>
+        <v>3670</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1942,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46296.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>4000</v>
+        <v>3690</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1956,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46296.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>4010</v>
+        <v>3700</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1970,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46296.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>4020</v>
+        <v>3700</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1984,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46296.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>4060</v>
+        <v>3710</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1998,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46296.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>4120</v>
+        <v>3730</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -2012,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46296.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>4180</v>
+        <v>3770</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -2026,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46296.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>4230</v>
+        <v>3810</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -2040,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46296.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>4270</v>
+        <v>3890</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -2054,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46296.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>4330</v>
+        <v>4000</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -2068,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46296.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>4390</v>
+        <v>4090</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -2082,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46296.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>4480</v>
+        <v>4200</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -2096,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46296.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>4610</v>
+        <v>4310</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -2110,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46296.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>4790</v>
+        <v>4410</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -2124,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46296.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>4960</v>
+        <v>4530</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -2138,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46296.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>5140</v>
+        <v>4660</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -2152,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46296.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>5300</v>
+        <v>4800</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -2166,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46296.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>5470</v>
+        <v>4950</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2180,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46296.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>5650</v>
+        <v>5110</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2194,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46296.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>5820</v>
+        <v>5280</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2208,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46296.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>6000</v>
+        <v>5460</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2222,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46296.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>6180</v>
+        <v>5660</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2236,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46296.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>6340</v>
+        <v>5820</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2250,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46296.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>6500</v>
+        <v>5980</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2264,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46296.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>6660</v>
+        <v>6140</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2278,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46296.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>6820</v>
+        <v>6250</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2292,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46296.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>6950</v>
+        <v>6370</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2306,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46296.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>7040</v>
+        <v>6460</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2320,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46296.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>7070</v>
+        <v>6520</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2334,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46296.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>7090</v>
+        <v>6570</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2348,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46296.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>7090</v>
+        <v>6600</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2362,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46296.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>7040</v>
+        <v>6560</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2376,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46296.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>6980</v>
+        <v>6470</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2390,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46296.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>6840</v>
+        <v>6310</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2404,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46296.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>6710</v>
+        <v>6180</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2418,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46296.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>6600</v>
+        <v>6020</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2432,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46296.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>6460</v>
+        <v>5890</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2446,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46296.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>6300</v>
+        <v>5760</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2460,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46296.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>6170</v>
+        <v>5670</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2474,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46296.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>6020</v>
+        <v>5540</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2488,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46296.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>5910</v>
+        <v>5430</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2502,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46296.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>5820</v>
+        <v>5330</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2516,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46296.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>5720</v>
+        <v>5240</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2530,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46296.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>5610</v>
+        <v>5160</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2544,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46296.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>5500</v>
+        <v>5070</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2558,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46296.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B94">
-        <v>5290</v>
+        <v>5030</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2572,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46296.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B95">
-        <v>5230</v>
+        <v>4980</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2586,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46296.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B96">
-        <v>5200</v>
+        <v>4920</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2600,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46296.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>5180</v>
+        <v>4870</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2614,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B98">
-        <v>5150</v>
+        <v>4820</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2628,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46297.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>5120</v>
+        <v>4770</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2642,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46297.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B100">
-        <v>5110</v>
+        <v>4720</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2656,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46297.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B101">
-        <v>5100</v>
+        <v>4690</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2670,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46297.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B102">
-        <v>5100</v>
+        <v>4640</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2684,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46297.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B103">
-        <v>5100</v>
+        <v>4610</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2698,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46297.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B104">
-        <v>5100</v>
+        <v>4590</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2712,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46297.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B105">
-        <v>5110</v>
+        <v>4560</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2726,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46297.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B106">
-        <v>5150</v>
+        <v>4540</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2740,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46297.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B107">
-        <v>5170</v>
+        <v>4530</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2754,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46297.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>5170</v>
+        <v>4530</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2768,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46297.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>5170</v>
+        <v>4520</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2782,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46297.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>5150</v>
+        <v>4500</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2796,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46297.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B111">
-        <v>5140</v>
+        <v>4490</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2810,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46297.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B112">
-        <v>5140</v>
+        <v>4500</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2824,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46297.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B113">
-        <v>5150</v>
+        <v>4510</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2838,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46297.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B114">
-        <v>5150</v>
+        <v>4550</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2852,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46297.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B115">
-        <v>5190</v>
+        <v>4570</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2866,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46297.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B116">
-        <v>5260</v>
+        <v>4590</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2880,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46297.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B117">
-        <v>5380</v>
+        <v>4610</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2894,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46297.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>5540</v>
+        <v>4650</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2908,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46297.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>5690</v>
+        <v>4670</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2922,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46297.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>5850</v>
+        <v>4690</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2936,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46297.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>6000</v>
+        <v>4710</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2950,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46297.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>6150</v>
+        <v>4740</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2964,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46297.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>6250</v>
+        <v>4760</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2978,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46297.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>6310</v>
+        <v>4760</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2992,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46297.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>6330</v>
+        <v>4740</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -3006,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46297.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>6330</v>
+        <v>4720</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -3020,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46297.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>6310</v>
+        <v>4690</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -3034,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46297.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>6250</v>
+        <v>4640</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -3048,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46297.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>6130</v>
+        <v>4550</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -3062,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46297.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>5880</v>
+        <v>4370</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -3076,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46297.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>5680</v>
+        <v>4210</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -3090,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46297.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>5500</v>
+        <v>4060</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -3104,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46297.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>5340</v>
+        <v>3920</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -3118,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46297.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>5180</v>
+        <v>3790</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -3132,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46297.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>5030</v>
+        <v>3660</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -3146,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46297.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>4890</v>
+        <v>3500</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -3160,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46297.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>4760</v>
+        <v>3370</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -3174,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46297.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>4640</v>
+        <v>3220</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3188,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46297.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>4530</v>
+        <v>3110</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3202,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46297.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>4430</v>
+        <v>3050</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3216,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46297.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>4340</v>
+        <v>3020</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -3230,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46297.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>4250</v>
+        <v>3000</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3244,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46297.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>4180</v>
+        <v>2990</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3258,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46297.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>4130</v>
+        <v>2990</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3272,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46297.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>4090</v>
+        <v>3020</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3286,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46297.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>4080</v>
+        <v>3050</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3300,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46297.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>4080</v>
+        <v>3080</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3314,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46297.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>4080</v>
+        <v>3110</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3328,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46297.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>4100</v>
+        <v>3160</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3342,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46297.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>4200</v>
+        <v>3210</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3356,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46297.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>4280</v>
+        <v>3270</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3370,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46297.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>4330</v>
+        <v>3330</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3384,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46297.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>4350</v>
+        <v>3390</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3398,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46297.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>4370</v>
+        <v>3450</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3412,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46297.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>4430</v>
+        <v>3510</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3426,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46297.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>4490</v>
+        <v>3580</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3440,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46297.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>4590</v>
+        <v>3660</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3454,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46297.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>4750</v>
+        <v>3750</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3468,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46297.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>4900</v>
+        <v>3870</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3482,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46297.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3496,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46297.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>5220</v>
+        <v>4170</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3510,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46297.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>5390</v>
+        <v>4380</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3524,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46297.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>5570</v>
+        <v>4560</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3538,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46297.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>5750</v>
+        <v>4740</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3552,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46297.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>5920</v>
+        <v>4920</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3566,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46297.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>6120</v>
+        <v>5090</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3580,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46297.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>6290</v>
+        <v>5230</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3594,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46297.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>6450</v>
+        <v>5370</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3608,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46297.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>6620</v>
+        <v>5510</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3622,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46297.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>6780</v>
+        <v>5670</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3636,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46297.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>6920</v>
+        <v>5810</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3650,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46297.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>7020</v>
+        <v>5920</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3664,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46297.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>7080</v>
+        <v>6000</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3678,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46297.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>7080</v>
+        <v>6050</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3692,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46297.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>7070</v>
+        <v>6070</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3706,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46297.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>7040</v>
+        <v>6060</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3720,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46297.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>6970</v>
+        <v>6020</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3734,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46297.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>6850</v>
+        <v>5900</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3748,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46297.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>6730</v>
+        <v>5750</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3762,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46297.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>6610</v>
+        <v>5620</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3776,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46297.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>6480</v>
+        <v>5530</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3790,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46297.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>6290</v>
+        <v>5420</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3804,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46297.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>6120</v>
+        <v>5340</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3818,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46297.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>5960</v>
+        <v>5260</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3832,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46297.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>5840</v>
+        <v>5180</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3846,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46297.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>5750</v>
+        <v>5090</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3860,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46297.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>5650</v>
+        <v>5010</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3874,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46297.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>5540</v>
+        <v>4960</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3888,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46297.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B189">
-        <v>5430</v>
+        <v>4940</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3902,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46297.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="B190">
-        <v>5340</v>
+        <v>4920</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3916,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46297.96875</v>
+        <v>46299.96875</v>
       </c>
       <c r="B191">
-        <v>5250</v>
+        <v>4900</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3930,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46297.97916666666</v>
+        <v>46299.97916666666</v>
       </c>
       <c r="B192">
-        <v>5220</v>
+        <v>4840</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3944,1360 +3656,16 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46297.98958333334</v>
+        <v>46299.98958333334</v>
       </c>
       <c r="B193">
-        <v>5190</v>
+        <v>4770</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" s="2">
-        <v>46298</v>
-      </c>
-      <c r="B194">
-        <v>5150</v>
-      </c>
-      <c r="C194">
-        <v>1</v>
-      </c>
-      <c r="D194" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195" s="2">
-        <v>46298.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>5110</v>
-      </c>
-      <c r="C195">
-        <v>2</v>
-      </c>
-      <c r="D195" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196" s="2">
-        <v>46298.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>5080</v>
-      </c>
-      <c r="C196">
-        <v>3</v>
-      </c>
-      <c r="D196" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197" s="2">
-        <v>46298.03125</v>
-      </c>
-      <c r="B197">
-        <v>5060</v>
-      </c>
-      <c r="C197">
-        <v>4</v>
-      </c>
-      <c r="D197" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198" s="2">
-        <v>46298.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>5030</v>
-      </c>
-      <c r="C198">
-        <v>5</v>
-      </c>
-      <c r="D198" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
-      <c r="A199" s="2">
-        <v>46298.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>5010</v>
-      </c>
-      <c r="C199">
-        <v>6</v>
-      </c>
-      <c r="D199" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
-      <c r="A200" s="2">
-        <v>46298.0625</v>
-      </c>
-      <c r="B200">
-        <v>4990</v>
-      </c>
-      <c r="C200">
-        <v>7</v>
-      </c>
-      <c r="D200" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
-      <c r="A201" s="2">
-        <v>46298.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>4970</v>
-      </c>
-      <c r="C201">
-        <v>8</v>
-      </c>
-      <c r="D201" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202" s="2">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>4960</v>
-      </c>
-      <c r="C202">
-        <v>9</v>
-      </c>
-      <c r="D202" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
-      <c r="A203" s="2">
-        <v>46298.09375</v>
-      </c>
-      <c r="B203">
-        <v>4950</v>
-      </c>
-      <c r="C203">
-        <v>10</v>
-      </c>
-      <c r="D203" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204" s="2">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>4950</v>
-      </c>
-      <c r="C204">
-        <v>11</v>
-      </c>
-      <c r="D204" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
-      <c r="A205" s="2">
-        <v>46298.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>4940</v>
-      </c>
-      <c r="C205">
-        <v>12</v>
-      </c>
-      <c r="D205" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
-      <c r="A206" s="2">
-        <v>46298.125</v>
-      </c>
-      <c r="B206">
-        <v>4940</v>
-      </c>
-      <c r="C206">
-        <v>13</v>
-      </c>
-      <c r="D206" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
-      <c r="A207" s="2">
-        <v>46298.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>4950</v>
-      </c>
-      <c r="C207">
-        <v>14</v>
-      </c>
-      <c r="D207" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
-      <c r="A208" s="2">
-        <v>46298.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>4950</v>
-      </c>
-      <c r="C208">
-        <v>15</v>
-      </c>
-      <c r="D208" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="2">
-        <v>46298.15625</v>
-      </c>
-      <c r="B209">
-        <v>4960</v>
-      </c>
-      <c r="C209">
-        <v>16</v>
-      </c>
-      <c r="D209" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
-      <c r="A210" s="2">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>4970</v>
-      </c>
-      <c r="C210">
-        <v>17</v>
-      </c>
-      <c r="D210" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="2">
-        <v>46298.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>4990</v>
-      </c>
-      <c r="C211">
-        <v>18</v>
-      </c>
-      <c r="D211" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="2">
-        <v>46298.1875</v>
-      </c>
-      <c r="B212">
-        <v>5010</v>
-      </c>
-      <c r="C212">
-        <v>19</v>
-      </c>
-      <c r="D212" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213" s="2">
-        <v>46298.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>5030</v>
-      </c>
-      <c r="C213">
-        <v>20</v>
-      </c>
-      <c r="D213" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="2">
-        <v>46298.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>5050</v>
-      </c>
-      <c r="C214">
-        <v>21</v>
-      </c>
-      <c r="D214" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
-      <c r="A215" s="2">
-        <v>46298.21875</v>
-      </c>
-      <c r="B215">
-        <v>5080</v>
-      </c>
-      <c r="C215">
-        <v>22</v>
-      </c>
-      <c r="D215" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
-      <c r="A216" s="2">
-        <v>46298.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>5110</v>
-      </c>
-      <c r="C216">
-        <v>23</v>
-      </c>
-      <c r="D216" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
-      <c r="A217" s="2">
-        <v>46298.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>5160</v>
-      </c>
-      <c r="C217">
-        <v>24</v>
-      </c>
-      <c r="D217" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4">
-      <c r="A218" s="2">
-        <v>46298.25</v>
-      </c>
-      <c r="B218">
-        <v>5210</v>
-      </c>
-      <c r="C218">
-        <v>25</v>
-      </c>
-      <c r="D218" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4">
-      <c r="A219" s="2">
-        <v>46298.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>5240</v>
-      </c>
-      <c r="C219">
-        <v>26</v>
-      </c>
-      <c r="D219" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
-      <c r="A220" s="2">
-        <v>46298.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>5260</v>
-      </c>
-      <c r="C220">
-        <v>27</v>
-      </c>
-      <c r="D220" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="A221" s="2">
-        <v>46298.28125</v>
-      </c>
-      <c r="B221">
-        <v>5290</v>
-      </c>
-      <c r="C221">
-        <v>28</v>
-      </c>
-      <c r="D221" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="A222" s="2">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>5320</v>
-      </c>
-      <c r="C222">
-        <v>29</v>
-      </c>
-      <c r="D222" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
-      <c r="A223" s="2">
-        <v>46298.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>5310</v>
-      </c>
-      <c r="C223">
-        <v>30</v>
-      </c>
-      <c r="D223" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="A224" s="2">
-        <v>46298.3125</v>
-      </c>
-      <c r="B224">
-        <v>5280</v>
-      </c>
-      <c r="C224">
-        <v>31</v>
-      </c>
-      <c r="D224" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
-      <c r="A225" s="2">
-        <v>46298.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>5210</v>
-      </c>
-      <c r="C225">
-        <v>32</v>
-      </c>
-      <c r="D225" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4">
-      <c r="A226" s="2">
-        <v>46298.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>5070</v>
-      </c>
-      <c r="C226">
-        <v>33</v>
-      </c>
-      <c r="D226" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="2">
-        <v>46298.34375</v>
-      </c>
-      <c r="B227">
-        <v>4940</v>
-      </c>
-      <c r="C227">
-        <v>34</v>
-      </c>
-      <c r="D227" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4">
-      <c r="A228" s="2">
-        <v>46298.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>4820</v>
-      </c>
-      <c r="C228">
-        <v>35</v>
-      </c>
-      <c r="D228" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4">
-      <c r="A229" s="2">
-        <v>46298.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>4690</v>
-      </c>
-      <c r="C229">
-        <v>36</v>
-      </c>
-      <c r="D229" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="2">
-        <v>46298.375</v>
-      </c>
-      <c r="B230">
-        <v>4560</v>
-      </c>
-      <c r="C230">
-        <v>37</v>
-      </c>
-      <c r="D230" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="2">
-        <v>46298.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>4430</v>
-      </c>
-      <c r="C231">
-        <v>38</v>
-      </c>
-      <c r="D231" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4">
-      <c r="A232" s="2">
-        <v>46298.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>4300</v>
-      </c>
-      <c r="C232">
-        <v>39</v>
-      </c>
-      <c r="D232" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4">
-      <c r="A233" s="2">
-        <v>46298.40625</v>
-      </c>
-      <c r="B233">
-        <v>4190</v>
-      </c>
-      <c r="C233">
-        <v>40</v>
-      </c>
-      <c r="D233" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4">
-      <c r="A234" s="2">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>4090</v>
-      </c>
-      <c r="C234">
-        <v>41</v>
-      </c>
-      <c r="D234" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4">
-      <c r="A235" s="2">
-        <v>46298.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>3990</v>
-      </c>
-      <c r="C235">
-        <v>42</v>
-      </c>
-      <c r="D235" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4">
-      <c r="A236" s="2">
-        <v>46298.4375</v>
-      </c>
-      <c r="B236">
-        <v>3910</v>
-      </c>
-      <c r="C236">
-        <v>43</v>
-      </c>
-      <c r="D236" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
-      <c r="A237" s="2">
-        <v>46298.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>3800</v>
-      </c>
-      <c r="C237">
-        <v>44</v>
-      </c>
-      <c r="D237" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
-      <c r="A238" s="2">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>3670</v>
-      </c>
-      <c r="C238">
-        <v>45</v>
-      </c>
-      <c r="D238" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4">
-      <c r="A239" s="2">
-        <v>46298.46875</v>
-      </c>
-      <c r="B239">
-        <v>3630</v>
-      </c>
-      <c r="C239">
-        <v>46</v>
-      </c>
-      <c r="D239" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4">
-      <c r="A240" s="2">
-        <v>46298.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>3630</v>
-      </c>
-      <c r="C240">
-        <v>47</v>
-      </c>
-      <c r="D240" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4">
-      <c r="A241" s="2">
-        <v>46298.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>3670</v>
-      </c>
-      <c r="C241">
-        <v>48</v>
-      </c>
-      <c r="D241" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
-      <c r="A242" s="2">
-        <v>46298.5</v>
-      </c>
-      <c r="B242">
-        <v>3690</v>
-      </c>
-      <c r="C242">
-        <v>49</v>
-      </c>
-      <c r="D242" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
-      <c r="A243" s="2">
-        <v>46298.51041666666</v>
-      </c>
-      <c r="B243">
-        <v>3700</v>
-      </c>
-      <c r="C243">
-        <v>50</v>
-      </c>
-      <c r="D243" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
-      <c r="A244" s="2">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="B244">
-        <v>3700</v>
-      </c>
-      <c r="C244">
-        <v>51</v>
-      </c>
-      <c r="D244" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
-      <c r="A245" s="2">
-        <v>46298.53125</v>
-      </c>
-      <c r="B245">
-        <v>3710</v>
-      </c>
-      <c r="C245">
-        <v>52</v>
-      </c>
-      <c r="D245" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
-      <c r="A246" s="2">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="B246">
-        <v>3730</v>
-      </c>
-      <c r="C246">
-        <v>53</v>
-      </c>
-      <c r="D246" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
-      <c r="A247" s="2">
-        <v>46298.55208333334</v>
-      </c>
-      <c r="B247">
-        <v>3770</v>
-      </c>
-      <c r="C247">
-        <v>54</v>
-      </c>
-      <c r="D247" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
-      <c r="A248" s="2">
-        <v>46298.5625</v>
-      </c>
-      <c r="B248">
-        <v>3810</v>
-      </c>
-      <c r="C248">
-        <v>55</v>
-      </c>
-      <c r="D248" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
-      <c r="A249" s="2">
-        <v>46298.57291666666</v>
-      </c>
-      <c r="B249">
-        <v>3890</v>
-      </c>
-      <c r="C249">
-        <v>56</v>
-      </c>
-      <c r="D249" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
-      <c r="A250" s="2">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="B250">
-        <v>4000</v>
-      </c>
-      <c r="C250">
-        <v>57</v>
-      </c>
-      <c r="D250" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
-      <c r="A251" s="2">
-        <v>46298.59375</v>
-      </c>
-      <c r="B251">
-        <v>4090</v>
-      </c>
-      <c r="C251">
-        <v>58</v>
-      </c>
-      <c r="D251" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="A252" s="2">
-        <v>46298.60416666666</v>
-      </c>
-      <c r="B252">
-        <v>4200</v>
-      </c>
-      <c r="C252">
-        <v>59</v>
-      </c>
-      <c r="D252" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="2">
-        <v>46298.61458333334</v>
-      </c>
-      <c r="B253">
-        <v>4310</v>
-      </c>
-      <c r="C253">
-        <v>60</v>
-      </c>
-      <c r="D253" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="2">
-        <v>46298.625</v>
-      </c>
-      <c r="B254">
-        <v>4410</v>
-      </c>
-      <c r="C254">
-        <v>61</v>
-      </c>
-      <c r="D254" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
-      <c r="A255" s="2">
-        <v>46298.63541666666</v>
-      </c>
-      <c r="B255">
-        <v>4530</v>
-      </c>
-      <c r="C255">
-        <v>62</v>
-      </c>
-      <c r="D255" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
-      <c r="A256" s="2">
-        <v>46298.64583333334</v>
-      </c>
-      <c r="B256">
-        <v>4660</v>
-      </c>
-      <c r="C256">
-        <v>63</v>
-      </c>
-      <c r="D256" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
-      <c r="A257" s="2">
-        <v>46298.65625</v>
-      </c>
-      <c r="B257">
-        <v>4800</v>
-      </c>
-      <c r="C257">
-        <v>64</v>
-      </c>
-      <c r="D257" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
-      <c r="A258" s="2">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="B258">
-        <v>4950</v>
-      </c>
-      <c r="C258">
-        <v>65</v>
-      </c>
-      <c r="D258" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
-      <c r="A259" s="2">
-        <v>46298.67708333334</v>
-      </c>
-      <c r="B259">
-        <v>5110</v>
-      </c>
-      <c r="C259">
-        <v>66</v>
-      </c>
-      <c r="D259" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
-      <c r="A260" s="2">
-        <v>46298.6875</v>
-      </c>
-      <c r="B260">
-        <v>5280</v>
-      </c>
-      <c r="C260">
-        <v>67</v>
-      </c>
-      <c r="D260" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
-      <c r="A261" s="2">
-        <v>46298.69791666666</v>
-      </c>
-      <c r="B261">
-        <v>5460</v>
-      </c>
-      <c r="C261">
-        <v>68</v>
-      </c>
-      <c r="D261" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
-      <c r="A262" s="2">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="B262">
-        <v>5660</v>
-      </c>
-      <c r="C262">
-        <v>69</v>
-      </c>
-      <c r="D262" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
-      <c r="A263" s="2">
-        <v>46298.71875</v>
-      </c>
-      <c r="B263">
-        <v>5820</v>
-      </c>
-      <c r="C263">
-        <v>70</v>
-      </c>
-      <c r="D263" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
-      <c r="A264" s="2">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="B264">
-        <v>5980</v>
-      </c>
-      <c r="C264">
-        <v>71</v>
-      </c>
-      <c r="D264" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
-      <c r="A265" s="2">
-        <v>46298.73958333334</v>
-      </c>
-      <c r="B265">
-        <v>6140</v>
-      </c>
-      <c r="C265">
-        <v>72</v>
-      </c>
-      <c r="D265" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
-      <c r="A266" s="2">
-        <v>46298.75</v>
-      </c>
-      <c r="B266">
-        <v>6250</v>
-      </c>
-      <c r="C266">
-        <v>73</v>
-      </c>
-      <c r="D266" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
-      <c r="A267" s="2">
-        <v>46298.76041666666</v>
-      </c>
-      <c r="B267">
-        <v>6370</v>
-      </c>
-      <c r="C267">
-        <v>74</v>
-      </c>
-      <c r="D267" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
-      <c r="A268" s="2">
-        <v>46298.77083333334</v>
-      </c>
-      <c r="B268">
-        <v>6460</v>
-      </c>
-      <c r="C268">
-        <v>75</v>
-      </c>
-      <c r="D268" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
-      <c r="A269" s="2">
-        <v>46298.78125</v>
-      </c>
-      <c r="B269">
-        <v>6520</v>
-      </c>
-      <c r="C269">
-        <v>76</v>
-      </c>
-      <c r="D269" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" s="2">
-        <v>46298.79166666666</v>
-      </c>
-      <c r="B270">
-        <v>6570</v>
-      </c>
-      <c r="C270">
-        <v>77</v>
-      </c>
-      <c r="D270" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="2">
-        <v>46298.80208333334</v>
-      </c>
-      <c r="B271">
-        <v>6600</v>
-      </c>
-      <c r="C271">
-        <v>78</v>
-      </c>
-      <c r="D271" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="2">
-        <v>46298.8125</v>
-      </c>
-      <c r="B272">
-        <v>6560</v>
-      </c>
-      <c r="C272">
-        <v>79</v>
-      </c>
-      <c r="D272" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
-      <c r="A273" s="2">
-        <v>46298.82291666666</v>
-      </c>
-      <c r="B273">
-        <v>6470</v>
-      </c>
-      <c r="C273">
-        <v>80</v>
-      </c>
-      <c r="D273" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
-      <c r="A274" s="2">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="B274">
-        <v>6310</v>
-      </c>
-      <c r="C274">
-        <v>81</v>
-      </c>
-      <c r="D274" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" s="2">
-        <v>46298.84375</v>
-      </c>
-      <c r="B275">
-        <v>6180</v>
-      </c>
-      <c r="C275">
-        <v>82</v>
-      </c>
-      <c r="D275" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="2">
-        <v>46298.85416666666</v>
-      </c>
-      <c r="B276">
-        <v>6020</v>
-      </c>
-      <c r="C276">
-        <v>83</v>
-      </c>
-      <c r="D276" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="2">
-        <v>46298.86458333334</v>
-      </c>
-      <c r="B277">
-        <v>5890</v>
-      </c>
-      <c r="C277">
-        <v>84</v>
-      </c>
-      <c r="D277" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="2">
-        <v>46298.875</v>
-      </c>
-      <c r="B278">
-        <v>5760</v>
-      </c>
-      <c r="C278">
-        <v>85</v>
-      </c>
-      <c r="D278" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="2">
-        <v>46298.88541666666</v>
-      </c>
-      <c r="B279">
-        <v>5670</v>
-      </c>
-      <c r="C279">
-        <v>86</v>
-      </c>
-      <c r="D279" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="2">
-        <v>46298.89583333334</v>
-      </c>
-      <c r="B280">
-        <v>5540</v>
-      </c>
-      <c r="C280">
-        <v>87</v>
-      </c>
-      <c r="D280" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
-      <c r="A281" s="2">
-        <v>46298.90625</v>
-      </c>
-      <c r="B281">
-        <v>5430</v>
-      </c>
-      <c r="C281">
-        <v>88</v>
-      </c>
-      <c r="D281" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282" s="2">
-        <v>46298.91666666666</v>
-      </c>
-      <c r="B282">
-        <v>5330</v>
-      </c>
-      <c r="C282">
-        <v>89</v>
-      </c>
-      <c r="D282" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
-      <c r="A283" s="2">
-        <v>46298.92708333334</v>
-      </c>
-      <c r="B283">
-        <v>5240</v>
-      </c>
-      <c r="C283">
-        <v>90</v>
-      </c>
-      <c r="D283" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4">
-      <c r="A284" s="2">
-        <v>46298.9375</v>
-      </c>
-      <c r="B284">
-        <v>5160</v>
-      </c>
-      <c r="C284">
-        <v>91</v>
-      </c>
-      <c r="D284" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
-      <c r="A285" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B285">
-        <v>5070</v>
-      </c>
-      <c r="C285">
-        <v>92</v>
-      </c>
-      <c r="D285" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
-      <c r="A286" s="2">
-        <v>46298.95833333334</v>
-      </c>
-      <c r="B286">
-        <v>5020</v>
-      </c>
-      <c r="C286">
-        <v>93</v>
-      </c>
-      <c r="D286" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
-      <c r="A287" s="2">
-        <v>46298.96875</v>
-      </c>
-      <c r="B287">
-        <v>4980</v>
-      </c>
-      <c r="C287">
-        <v>94</v>
-      </c>
-      <c r="D287" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288" s="2">
-        <v>46298.97916666666</v>
-      </c>
-      <c r="B288">
-        <v>4950</v>
-      </c>
-      <c r="C288">
-        <v>95</v>
-      </c>
-      <c r="D288" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
-      <c r="A289" s="2">
-        <v>46298.98958333334</v>
-      </c>
-      <c r="B289">
-        <v>4890</v>
-      </c>
-      <c r="C289">
-        <v>96</v>
-      </c>
-      <c r="D289" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t>Timestamp</t>
   </si>
@@ -602,6 +602,870 @@
   </si>
   <si>
     <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
+  </si>
+  <si>
+    <t>07.10.202642</t>
+  </si>
+  <si>
+    <t>07.10.202643</t>
+  </si>
+  <si>
+    <t>07.10.202644</t>
+  </si>
+  <si>
+    <t>07.10.202645</t>
+  </si>
+  <si>
+    <t>07.10.202646</t>
+  </si>
+  <si>
+    <t>07.10.202647</t>
+  </si>
+  <si>
+    <t>07.10.202648</t>
+  </si>
+  <si>
+    <t>07.10.202649</t>
+  </si>
+  <si>
+    <t>07.10.202650</t>
+  </si>
+  <si>
+    <t>07.10.202651</t>
+  </si>
+  <si>
+    <t>07.10.202652</t>
+  </si>
+  <si>
+    <t>07.10.202653</t>
+  </si>
+  <si>
+    <t>07.10.202654</t>
+  </si>
+  <si>
+    <t>07.10.202655</t>
+  </si>
+  <si>
+    <t>07.10.202656</t>
+  </si>
+  <si>
+    <t>07.10.202657</t>
+  </si>
+  <si>
+    <t>07.10.202658</t>
+  </si>
+  <si>
+    <t>07.10.202659</t>
+  </si>
+  <si>
+    <t>07.10.202660</t>
+  </si>
+  <si>
+    <t>07.10.202661</t>
+  </si>
+  <si>
+    <t>07.10.202662</t>
+  </si>
+  <si>
+    <t>07.10.202663</t>
+  </si>
+  <si>
+    <t>07.10.202664</t>
+  </si>
+  <si>
+    <t>07.10.202665</t>
+  </si>
+  <si>
+    <t>07.10.202666</t>
+  </si>
+  <si>
+    <t>07.10.202667</t>
+  </si>
+  <si>
+    <t>07.10.202668</t>
+  </si>
+  <si>
+    <t>07.10.202669</t>
+  </si>
+  <si>
+    <t>07.10.202670</t>
+  </si>
+  <si>
+    <t>07.10.202671</t>
+  </si>
+  <si>
+    <t>07.10.202672</t>
+  </si>
+  <si>
+    <t>07.10.202673</t>
+  </si>
+  <si>
+    <t>07.10.202674</t>
+  </si>
+  <si>
+    <t>07.10.202675</t>
+  </si>
+  <si>
+    <t>07.10.202676</t>
+  </si>
+  <si>
+    <t>07.10.202677</t>
+  </si>
+  <si>
+    <t>07.10.202678</t>
+  </si>
+  <si>
+    <t>07.10.202679</t>
+  </si>
+  <si>
+    <t>07.10.202680</t>
+  </si>
+  <si>
+    <t>07.10.202681</t>
+  </si>
+  <si>
+    <t>07.10.202682</t>
+  </si>
+  <si>
+    <t>07.10.202683</t>
+  </si>
+  <si>
+    <t>07.10.202684</t>
+  </si>
+  <si>
+    <t>07.10.202685</t>
+  </si>
+  <si>
+    <t>07.10.202686</t>
+  </si>
+  <si>
+    <t>07.10.202687</t>
+  </si>
+  <si>
+    <t>07.10.202688</t>
+  </si>
+  <si>
+    <t>07.10.202689</t>
+  </si>
+  <si>
+    <t>07.10.202690</t>
+  </si>
+  <si>
+    <t>07.10.202691</t>
+  </si>
+  <si>
+    <t>07.10.202692</t>
+  </si>
+  <si>
+    <t>07.10.202693</t>
+  </si>
+  <si>
+    <t>07.10.202694</t>
+  </si>
+  <si>
+    <t>07.10.202695</t>
+  </si>
+  <si>
+    <t>07.10.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3668,6 +4532,4038 @@
         <v>195</v>
       </c>
     </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>4720</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4680</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4650</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>4630</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4610</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4600</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>4600</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4610</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4630</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>4650</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4690</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4720</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>4750</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4790</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4830</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>4890</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4950</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>5040</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>5140</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>5270</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5420</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>5580</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>5750</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>5910</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>6050</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>6180</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>6270</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>6300</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>6290</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>6270</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>6210</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>6090</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>5940</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>5770</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>5580</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>5380</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>5190</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>5000</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>4820</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>4670</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>4530</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>4420</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>4330</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>4260</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>4220</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>4200</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>4190</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>4200</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>4220</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>4240</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>4260</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>4290</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>4320</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>4360</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>4400</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>4460</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>4520</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>4600</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>4700</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>4800</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>4920</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>5050</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>5180</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>5330</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>5470</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>5630</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>5780</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>5940</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>6090</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>6230</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>6360</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>6480</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>6590</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>6700</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>6810</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>6910</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>7010</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>7050</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>7030</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>6940</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6720</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>6480</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>6360</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>6310</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>6220</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>6100</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5880</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>5800</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5750</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5670</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>5620</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5530</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5250</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>5180</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>5130</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>5090</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>5040</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>5000</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4990</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>4980</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4950</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4950</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>4950</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4960</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4980</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>4990</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>5000</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>5020</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>5040</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>5050</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>5050</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>5070</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>5090</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>5140</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>5210</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5300</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5400</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>5520</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5650</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5780</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>5970</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>6090</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6180</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>6240</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6260</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6260</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>6230</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>6130</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>6010</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>5870</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>5700</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>5520</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>5310</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>5130</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4960</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>4810</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4650</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4540</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>4450</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>4370</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>4320</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>4300</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>4300</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>4300</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>4320</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>4340</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>4360</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>4390</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>4430</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>4470</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>4510</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>4560</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>4620</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>4690</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>4750</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>4840</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>4940</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>5050</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>5180</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>5330</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>5480</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>5640</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>5800</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>5970</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6160</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>6320</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6480</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>6630</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>6780</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>6900</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>6990</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>7040</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>7050</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>7040</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>7000</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>6910</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6770</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>6630</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6510</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6400</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>6270</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6140</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>6010</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>5900</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5800</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5670</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>5560</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5450</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5430</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>5360</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5300</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5230</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>5120</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>5060</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>5050</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>5050</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>5050</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>5050</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>5070</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>5110</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>5140</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>5180</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>5190</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>5190</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>5200</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>5180</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>5160</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>5140</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>5140</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>5140</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>5170</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>5270</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5480</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>5670</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>5840</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>6010</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>6220</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>6360</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>6450</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>6510</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>6520</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>6510</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>6480</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>6420</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>6320</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>6200</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>6060</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>5900</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>5710</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>5530</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>5360</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>5200</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>5010</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>4880</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>4760</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>4670</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>4600</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>4560</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>4540</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>4540</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>4560</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>4580</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>4610</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>4650</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>4700</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>4730</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>4750</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>4820</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>4910</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>4990</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>5070</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>5160</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>5260</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>5370</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>5480</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>5600</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>5760</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>5910</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>6050</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>6200</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>6350</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>6490</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>6620</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>6740</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>6870</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>6980</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>7060</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>7100</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>7100</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>7090</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>7050</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>6970</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>6840</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>6710</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>6580</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>6470</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>6280</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>6140</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>6000</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46302.90625</v>
+      </c>
+      <c r="B473">
+        <v>5890</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>5800</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46302.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>5720</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46302.9375</v>
+      </c>
+      <c r="B476">
+        <v>5630</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46302.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>5530</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46302.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>5440</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46302.96875</v>
+      </c>
+      <c r="B479">
+        <v>5400</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46302.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>5350</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46302.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>5260</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>5120</v>
+        <v>5100</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>5060</v>
+        <v>5100</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>5050</v>
+        <v>5090</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>5070</v>
+        <v>5100</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
         <v>5110</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>5140</v>
+        <v>5120</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>5180</v>
+        <v>5150</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>5190</v>
+        <v>5150</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>5190</v>
+        <v>5150</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>5180</v>
+        <v>5150</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>5160</v>
+        <v>5150</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>5140</v>
+        <v>5150</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
         <v>5140</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
         <v>5140</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>5170</v>
+        <v>5150</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>5270</v>
+        <v>5150</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>5480</v>
+        <v>5490</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>5670</v>
+        <v>5690</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>5840</v>
+        <v>5830</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>6220</v>
+        <v>6160</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>6360</v>
+        <v>6290</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>6450</v>
+        <v>6390</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>6510</v>
+        <v>6440</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>6520</v>
+        <v>6450</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>6510</v>
+        <v>6440</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>6480</v>
+        <v>6400</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>6420</v>
+        <v>6340</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>6320</v>
+        <v>6230</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>6060</v>
+        <v>5930</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>5900</v>
+        <v>5730</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>5710</v>
+        <v>5470</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>5530</v>
+        <v>5260</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>5360</v>
+        <v>5070</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>5200</v>
+        <v>4890</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>5010</v>
+        <v>4750</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>4880</v>
+        <v>4640</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>4760</v>
+        <v>4540</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>4670</v>
+        <v>4470</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>4600</v>
+        <v>4430</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>4560</v>
+        <v>4420</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>4540</v>
+        <v>4420</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>4540</v>
+        <v>4420</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>4560</v>
+        <v>4500</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>4580</v>
+        <v>4520</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>4610</v>
+        <v>4530</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>4650</v>
+        <v>4540</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>4700</v>
+        <v>4550</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>4730</v>
+        <v>4550</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>4750</v>
+        <v>4550</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>4820</v>
+        <v>4570</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>4910</v>
+        <v>4630</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>4990</v>
+        <v>4710</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>5070</v>
+        <v>4780</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>5160</v>
+        <v>4880</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>5260</v>
+        <v>4990</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>5370</v>
+        <v>5120</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>5480</v>
+        <v>5270</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>5600</v>
+        <v>5430</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>5760</v>
+        <v>5610</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>5910</v>
+        <v>5780</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>6050</v>
+        <v>5930</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>6200</v>
+        <v>6080</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>6350</v>
+        <v>6240</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>6490</v>
+        <v>6380</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>6620</v>
+        <v>6520</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>6740</v>
+        <v>6660</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>6870</v>
+        <v>6820</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>6980</v>
+        <v>6930</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>7060</v>
+        <v>7010</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>7100</v>
+        <v>7040</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>7100</v>
+        <v>7030</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>7090</v>
+        <v>6990</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>7050</v>
+        <v>6930</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>6970</v>
+        <v>6850</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>6840</v>
+        <v>6730</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>6710</v>
+        <v>6610</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>6580</v>
+        <v>6500</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>6470</v>
+        <v>6360</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>6280</v>
+        <v>6180</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>6140</v>
+        <v>6030</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>6000</v>
+        <v>5890</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>5890</v>
+        <v>5780</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>5800</v>
+        <v>5680</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>5720</v>
+        <v>5570</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>5630</v>
+        <v>5450</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>5530</v>
+        <v>5340</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>5220</v>
+        <v>5260</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>5170</v>
+        <v>5190</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>5130</v>
+        <v>5150</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
         <v>5120</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>5100</v>
+        <v>5090</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>5100</v>
+        <v>5070</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>5100</v>
+        <v>5030</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>5090</v>
+        <v>4980</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>5100</v>
+        <v>4980</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>5100</v>
+        <v>4980</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>5110</v>
+        <v>4980</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>5120</v>
+        <v>5030</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>5150</v>
+        <v>5020</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>5150</v>
+        <v>5000</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>5150</v>
+        <v>5000</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>5150</v>
+        <v>5010</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>5140</v>
+        <v>5080</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
         <v>5140</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>5150</v>
+        <v>5230</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>5150</v>
+        <v>5350</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>5490</v>
+        <v>5470</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>5690</v>
+        <v>5610</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>5830</v>
+        <v>5750</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>6000</v>
+        <v>5920</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>6160</v>
+        <v>6150</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>6290</v>
+        <v>6310</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
         <v>6390</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>6440</v>
+        <v>6460</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>6450</v>
+        <v>6500</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>6440</v>
+        <v>6520</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>6400</v>
+        <v>6510</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>6340</v>
+        <v>6470</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>6230</v>
+        <v>6370</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>6100</v>
+        <v>6250</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>5930</v>
+        <v>6120</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>5730</v>
+        <v>5980</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>5470</v>
+        <v>5850</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
-        <v>5260</v>
+        <v>5700</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>5070</v>
+        <v>5550</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>4890</v>
+        <v>5410</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>4750</v>
+        <v>5250</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
-        <v>4640</v>
+        <v>5140</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
-        <v>4540</v>
+        <v>5050</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
-        <v>4470</v>
+        <v>4980</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
-        <v>4430</v>
+        <v>4930</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
-        <v>4500</v>
+        <v>4980</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
-        <v>4520</v>
+        <v>5000</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
-        <v>4530</v>
+        <v>5010</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
-        <v>4540</v>
+        <v>5020</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
-        <v>4570</v>
+        <v>5030</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
-        <v>4630</v>
+        <v>5070</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
-        <v>4710</v>
+        <v>5110</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
-        <v>4780</v>
+        <v>5140</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
-        <v>4880</v>
+        <v>5200</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
-        <v>4990</v>
+        <v>5300</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
-        <v>5120</v>
+        <v>5400</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
-        <v>5270</v>
+        <v>5510</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
-        <v>5430</v>
+        <v>5630</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
-        <v>5610</v>
+        <v>5750</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
-        <v>5780</v>
+        <v>5890</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
-        <v>5930</v>
+        <v>6020</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
-        <v>6080</v>
+        <v>6150</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
-        <v>6240</v>
+        <v>6300</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
-        <v>6380</v>
+        <v>6430</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
-        <v>6520</v>
+        <v>6560</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
-        <v>6660</v>
+        <v>6690</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
         <v>6820</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
-        <v>7010</v>
+        <v>6980</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
-        <v>7040</v>
+        <v>7000</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
-        <v>7030</v>
+        <v>7000</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
-        <v>6990</v>
+        <v>6980</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
-        <v>6850</v>
+        <v>6860</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
         <v>6730</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
-        <v>6500</v>
+        <v>6490</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
-        <v>6360</v>
+        <v>6370</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B184">
-        <v>5890</v>
+        <v>5930</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B185">
-        <v>5780</v>
+        <v>5800</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B186">
-        <v>5680</v>
+        <v>5700</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B187">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B188">
-        <v>5450</v>
+        <v>5470</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B189">
-        <v>5340</v>
+        <v>5360</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B190">
-        <v>5350</v>
+        <v>5290</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B191">
-        <v>5300</v>
+        <v>5240</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B192">
-        <v>5240</v>
+        <v>5190</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B193">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="C193">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -602,6 +314,870 @@
   </si>
   <si>
     <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
+  </si>
+  <si>
+    <t>12.10.202639</t>
+  </si>
+  <si>
+    <t>12.10.202640</t>
+  </si>
+  <si>
+    <t>12.10.202641</t>
+  </si>
+  <si>
+    <t>12.10.202642</t>
+  </si>
+  <si>
+    <t>12.10.202643</t>
+  </si>
+  <si>
+    <t>12.10.202644</t>
+  </si>
+  <si>
+    <t>12.10.202645</t>
+  </si>
+  <si>
+    <t>12.10.202646</t>
+  </si>
+  <si>
+    <t>12.10.202647</t>
+  </si>
+  <si>
+    <t>12.10.202648</t>
+  </si>
+  <si>
+    <t>12.10.202649</t>
+  </si>
+  <si>
+    <t>12.10.202650</t>
+  </si>
+  <si>
+    <t>12.10.202651</t>
+  </si>
+  <si>
+    <t>12.10.202652</t>
+  </si>
+  <si>
+    <t>12.10.202653</t>
+  </si>
+  <si>
+    <t>12.10.202654</t>
+  </si>
+  <si>
+    <t>12.10.202655</t>
+  </si>
+  <si>
+    <t>12.10.202656</t>
+  </si>
+  <si>
+    <t>12.10.202657</t>
+  </si>
+  <si>
+    <t>12.10.202658</t>
+  </si>
+  <si>
+    <t>12.10.202659</t>
+  </si>
+  <si>
+    <t>12.10.202660</t>
+  </si>
+  <si>
+    <t>12.10.202661</t>
+  </si>
+  <si>
+    <t>12.10.202662</t>
+  </si>
+  <si>
+    <t>12.10.202663</t>
+  </si>
+  <si>
+    <t>12.10.202664</t>
+  </si>
+  <si>
+    <t>12.10.202665</t>
+  </si>
+  <si>
+    <t>12.10.202666</t>
+  </si>
+  <si>
+    <t>12.10.202667</t>
+  </si>
+  <si>
+    <t>12.10.202668</t>
+  </si>
+  <si>
+    <t>12.10.202669</t>
+  </si>
+  <si>
+    <t>12.10.202670</t>
+  </si>
+  <si>
+    <t>12.10.202671</t>
+  </si>
+  <si>
+    <t>12.10.202672</t>
+  </si>
+  <si>
+    <t>12.10.202673</t>
+  </si>
+  <si>
+    <t>12.10.202674</t>
+  </si>
+  <si>
+    <t>12.10.202675</t>
+  </si>
+  <si>
+    <t>12.10.202676</t>
+  </si>
+  <si>
+    <t>12.10.202677</t>
+  </si>
+  <si>
+    <t>12.10.202678</t>
+  </si>
+  <si>
+    <t>12.10.202679</t>
+  </si>
+  <si>
+    <t>12.10.202680</t>
+  </si>
+  <si>
+    <t>12.10.202681</t>
+  </si>
+  <si>
+    <t>12.10.202682</t>
+  </si>
+  <si>
+    <t>12.10.202683</t>
+  </si>
+  <si>
+    <t>12.10.202684</t>
+  </si>
+  <si>
+    <t>12.10.202685</t>
+  </si>
+  <si>
+    <t>12.10.202686</t>
+  </si>
+  <si>
+    <t>12.10.202687</t>
+  </si>
+  <si>
+    <t>12.10.202688</t>
+  </si>
+  <si>
+    <t>12.10.202689</t>
+  </si>
+  <si>
+    <t>12.10.202690</t>
+  </si>
+  <si>
+    <t>12.10.202691</t>
+  </si>
+  <si>
+    <t>12.10.202692</t>
+  </si>
+  <si>
+    <t>12.10.202693</t>
+  </si>
+  <si>
+    <t>12.10.202694</t>
+  </si>
+  <si>
+    <t>12.10.202695</t>
+  </si>
+  <si>
+    <t>12.10.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +1558,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>5100</v>
+        <v>5090</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +1572,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>5100</v>
+        <v>5070</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1586,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1600,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>5100</v>
+        <v>5030</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1614,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>5090</v>
+        <v>4980</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1628,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>5100</v>
+        <v>4980</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1642,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>5100</v>
+        <v>4980</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1656,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>5110</v>
+        <v>4980</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1670,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>5120</v>
+        <v>5030</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1684,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1698,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1712,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1726,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>5150</v>
+        <v>5020</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1740,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>5150</v>
+        <v>5000</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1754,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>5150</v>
+        <v>5000</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>5150</v>
+        <v>5010</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1782,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>5140</v>
+        <v>5080</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,7 +1796,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
         <v>5140</v>
@@ -1234,10 +1810,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>5150</v>
+        <v>5230</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1824,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>5150</v>
+        <v>5350</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1838,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>5490</v>
+        <v>5470</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>5690</v>
+        <v>5610</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1866,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>5830</v>
+        <v>5750</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1880,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>6000</v>
+        <v>5920</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1894,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>6160</v>
+        <v>6150</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1908,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>6290</v>
+        <v>6310</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,7 +1922,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
         <v>6390</v>
@@ -1360,10 +1936,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>6440</v>
+        <v>6460</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1950,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>6450</v>
+        <v>6500</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1964,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>6440</v>
+        <v>6520</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1978,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>6400</v>
+        <v>6510</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1992,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>6340</v>
+        <v>6470</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2006,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>6230</v>
+        <v>6370</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2020,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>6100</v>
+        <v>6250</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2034,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>5930</v>
+        <v>6120</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2048,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>5730</v>
+        <v>5980</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2062,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>5470</v>
+        <v>5850</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2076,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>5260</v>
+        <v>5700</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2090,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>5070</v>
+        <v>5550</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2104,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>4890</v>
+        <v>5410</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2118,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>4750</v>
+        <v>5250</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2132,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>4640</v>
+        <v>5140</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2146,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>4540</v>
+        <v>5050</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2160,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>4470</v>
+        <v>4980</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2174,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>4430</v>
+        <v>4930</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2188,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2202,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2216,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>4420</v>
+        <v>4920</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2230,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>4500</v>
+        <v>4980</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2244,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>4520</v>
+        <v>5000</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2258,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>4530</v>
+        <v>5010</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2272,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>4540</v>
+        <v>5020</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2286,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2300,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2314,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>4550</v>
+        <v>5020</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2328,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>4570</v>
+        <v>5030</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2342,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>4630</v>
+        <v>5070</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2356,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>4710</v>
+        <v>5110</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2370,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>4780</v>
+        <v>5140</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2384,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>4880</v>
+        <v>5200</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2398,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>4990</v>
+        <v>5300</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2412,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>5120</v>
+        <v>5400</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +2426,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>5270</v>
+        <v>5510</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +2440,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>5430</v>
+        <v>5630</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +2454,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>5610</v>
+        <v>5750</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +2468,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>5780</v>
+        <v>5890</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +2482,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>5930</v>
+        <v>6020</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +2496,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>6080</v>
+        <v>6150</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +2510,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>6240</v>
+        <v>6300</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +2524,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>6380</v>
+        <v>6430</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +2538,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>6520</v>
+        <v>6560</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +2552,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>6660</v>
+        <v>6690</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,7 +2566,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
         <v>6820</v>
@@ -2004,10 +2580,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2594,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>7010</v>
+        <v>6980</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2608,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>7040</v>
+        <v>7000</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2622,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>7030</v>
+        <v>7000</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2636,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>6990</v>
+        <v>6980</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2650,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2664,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>6850</v>
+        <v>6860</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,7 +2678,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
         <v>6730</v>
@@ -2116,10 +2692,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2706,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>6500</v>
+        <v>6490</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2720,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>6360</v>
+        <v>6370</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2734,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2748,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2762,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>5890</v>
+        <v>5930</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2776,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>5780</v>
+        <v>5800</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2790,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>5680</v>
+        <v>5700</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2804,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>5570</v>
+        <v>5580</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2818,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>5450</v>
+        <v>5470</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2832,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>5340</v>
+        <v>5360</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2846,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>5260</v>
+        <v>5300</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2860,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>5190</v>
+        <v>5220</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2874,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>5150</v>
+        <v>5180</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,7 +2888,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
         <v>5120</v>
@@ -2326,10 +2902,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>5090</v>
+        <v>5050</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2916,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>5070</v>
+        <v>5010</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2930,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>5050</v>
+        <v>4990</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2944,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>5030</v>
+        <v>4960</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>4980</v>
+        <v>4940</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2972,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>4980</v>
+        <v>4920</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2986,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>4980</v>
+        <v>4910</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3000,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>4980</v>
+        <v>4910</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3014,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>5030</v>
+        <v>4900</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3028,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3042,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3056,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3070,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>5020</v>
+        <v>4920</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3084,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>5000</v>
+        <v>4930</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3098,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>5000</v>
+        <v>4930</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3112,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>5010</v>
+        <v>4940</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3126,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>5080</v>
+        <v>4980</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3140,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>5140</v>
+        <v>5010</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3154,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>5230</v>
+        <v>5030</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3168,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>5350</v>
+        <v>5060</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3182,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>5470</v>
+        <v>5100</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3196,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>5610</v>
+        <v>5130</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3210,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>5750</v>
+        <v>5170</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3224,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>5920</v>
+        <v>5230</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3238,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>6150</v>
+        <v>5320</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3252,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>6310</v>
+        <v>5380</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3266,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>6390</v>
+        <v>5430</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3280,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>6460</v>
+        <v>5480</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3294,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>6500</v>
+        <v>5530</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3308,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>6520</v>
+        <v>5550</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3322,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>6510</v>
+        <v>5520</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3336,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>6470</v>
+        <v>5480</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3350,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>6370</v>
+        <v>5370</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3364,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>6250</v>
+        <v>5260</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3378,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>6120</v>
+        <v>5150</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3392,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>5980</v>
+        <v>5020</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3406,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="B134">
-        <v>5850</v>
+        <v>4870</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3420,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46304.38541666666</v>
+        <v>46305.38541666666</v>
       </c>
       <c r="B135">
-        <v>5700</v>
+        <v>4720</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +3434,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46304.39583333334</v>
+        <v>46305.39583333334</v>
       </c>
       <c r="B136">
-        <v>5550</v>
+        <v>4570</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +3448,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46304.40625</v>
+        <v>46305.40625</v>
       </c>
       <c r="B137">
-        <v>5410</v>
+        <v>4440</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +3462,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46304.41666666666</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="B138">
-        <v>5250</v>
+        <v>4290</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +3476,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46304.42708333334</v>
+        <v>46305.42708333334</v>
       </c>
       <c r="B139">
-        <v>5140</v>
+        <v>4180</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +3490,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46304.4375</v>
+        <v>46305.4375</v>
       </c>
       <c r="B140">
-        <v>5050</v>
+        <v>4100</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +3504,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46304.44791666666</v>
+        <v>46305.44791666666</v>
       </c>
       <c r="B141">
-        <v>4980</v>
+        <v>4010</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +3518,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46304.45833333334</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="B142">
-        <v>4930</v>
+        <v>3920</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +3532,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46304.46875</v>
+        <v>46305.46875</v>
       </c>
       <c r="B143">
-        <v>4920</v>
+        <v>3900</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +3546,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46304.47916666666</v>
+        <v>46305.47916666666</v>
       </c>
       <c r="B144">
-        <v>4920</v>
+        <v>3900</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +3560,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46304.48958333334</v>
+        <v>46305.48958333334</v>
       </c>
       <c r="B145">
-        <v>4920</v>
+        <v>3900</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +3574,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46304.5</v>
+        <v>46305.5</v>
       </c>
       <c r="B146">
-        <v>4980</v>
+        <v>3930</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3588,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46304.51041666666</v>
+        <v>46305.51041666666</v>
       </c>
       <c r="B147">
-        <v>5000</v>
+        <v>3940</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3602,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46304.52083333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="B148">
-        <v>5010</v>
+        <v>3960</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3616,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46304.53125</v>
+        <v>46305.53125</v>
       </c>
       <c r="B149">
-        <v>5020</v>
+        <v>3970</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3630,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46304.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="B150">
-        <v>5020</v>
+        <v>3970</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3644,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46304.55208333334</v>
+        <v>46305.55208333334</v>
       </c>
       <c r="B151">
-        <v>5020</v>
+        <v>3980</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3658,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46304.5625</v>
+        <v>46305.5625</v>
       </c>
       <c r="B152">
-        <v>5020</v>
+        <v>4000</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3672,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46304.57291666666</v>
+        <v>46305.57291666666</v>
       </c>
       <c r="B153">
-        <v>5030</v>
+        <v>4050</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3686,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46304.58333333334</v>
+        <v>46305.58333333334</v>
       </c>
       <c r="B154">
-        <v>5070</v>
+        <v>4130</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3700,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46304.59375</v>
+        <v>46305.59375</v>
       </c>
       <c r="B155">
-        <v>5110</v>
+        <v>4210</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3714,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46304.60416666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="B156">
-        <v>5140</v>
+        <v>4290</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3728,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46304.61458333334</v>
+        <v>46305.61458333334</v>
       </c>
       <c r="B157">
-        <v>5200</v>
+        <v>4380</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3742,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46304.625</v>
+        <v>46305.625</v>
       </c>
       <c r="B158">
-        <v>5300</v>
+        <v>4490</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3756,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46304.63541666666</v>
+        <v>46305.63541666666</v>
       </c>
       <c r="B159">
-        <v>5400</v>
+        <v>4610</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3770,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46304.64583333334</v>
+        <v>46305.64583333334</v>
       </c>
       <c r="B160">
-        <v>5510</v>
+        <v>4740</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3784,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46304.65625</v>
+        <v>46305.65625</v>
       </c>
       <c r="B161">
-        <v>5630</v>
+        <v>4880</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3798,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46304.66666666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="B162">
-        <v>5750</v>
+        <v>5020</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3812,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46304.67708333334</v>
+        <v>46305.67708333334</v>
       </c>
       <c r="B163">
-        <v>5890</v>
+        <v>5180</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3826,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46304.6875</v>
+        <v>46305.6875</v>
       </c>
       <c r="B164">
-        <v>6020</v>
+        <v>5330</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3840,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46304.69791666666</v>
+        <v>46305.69791666666</v>
       </c>
       <c r="B165">
-        <v>6150</v>
+        <v>5490</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3854,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46304.70833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="B166">
-        <v>6300</v>
+        <v>5700</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3868,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46304.71875</v>
+        <v>46305.71875</v>
       </c>
       <c r="B167">
-        <v>6430</v>
+        <v>5850</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3882,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46304.72916666666</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="B168">
-        <v>6560</v>
+        <v>6010</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3896,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46304.73958333334</v>
+        <v>46305.73958333334</v>
       </c>
       <c r="B169">
-        <v>6690</v>
+        <v>6160</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3910,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46304.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B170">
-        <v>6820</v>
+        <v>6290</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3924,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46304.76041666666</v>
+        <v>46305.76041666666</v>
       </c>
       <c r="B171">
-        <v>6920</v>
+        <v>6390</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3938,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46304.77083333334</v>
+        <v>46305.77083333334</v>
       </c>
       <c r="B172">
-        <v>6980</v>
+        <v>6450</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3952,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46304.78125</v>
+        <v>46305.78125</v>
       </c>
       <c r="B173">
-        <v>7000</v>
+        <v>6470</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3966,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46304.79166666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="B174">
-        <v>7000</v>
+        <v>6450</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3980,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46304.80208333334</v>
+        <v>46305.80208333334</v>
       </c>
       <c r="B175">
-        <v>6980</v>
+        <v>6420</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3994,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46304.8125</v>
+        <v>46305.8125</v>
       </c>
       <c r="B176">
-        <v>6920</v>
+        <v>6390</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4008,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46304.82291666666</v>
+        <v>46305.82291666666</v>
       </c>
       <c r="B177">
-        <v>6860</v>
+        <v>6350</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4022,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46304.83333333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="B178">
-        <v>6730</v>
+        <v>6270</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4036,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46304.84375</v>
+        <v>46305.84375</v>
       </c>
       <c r="B179">
-        <v>6600</v>
+        <v>6180</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4050,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46304.85416666666</v>
+        <v>46305.85416666666</v>
       </c>
       <c r="B180">
-        <v>6490</v>
+        <v>6090</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4064,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46304.86458333334</v>
+        <v>46305.86458333334</v>
       </c>
       <c r="B181">
-        <v>6370</v>
+        <v>5990</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4078,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46304.875</v>
+        <v>46305.875</v>
       </c>
       <c r="B182">
-        <v>6210</v>
+        <v>5850</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4092,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46304.88541666666</v>
+        <v>46305.88541666666</v>
       </c>
       <c r="B183">
-        <v>6080</v>
+        <v>5720</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4106,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46304.89583333334</v>
+        <v>46305.89583333334</v>
       </c>
       <c r="B184">
-        <v>5930</v>
+        <v>5580</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4120,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46304.90625</v>
+        <v>46305.90625</v>
       </c>
       <c r="B185">
-        <v>5800</v>
+        <v>5470</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4134,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46304.91666666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="B186">
-        <v>5700</v>
+        <v>5390</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4148,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46304.92708333334</v>
+        <v>46305.92708333334</v>
       </c>
       <c r="B187">
-        <v>5580</v>
+        <v>5290</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4162,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46304.9375</v>
+        <v>46305.9375</v>
       </c>
       <c r="B188">
-        <v>5470</v>
+        <v>5190</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4176,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46304.94791666666</v>
+        <v>46305.94791666666</v>
       </c>
       <c r="B189">
-        <v>5360</v>
+        <v>5090</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4190,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46304.95833333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="B190">
-        <v>5290</v>
+        <v>4990</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4204,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46304.96875</v>
+        <v>46305.96875</v>
       </c>
       <c r="B191">
-        <v>5240</v>
+        <v>4920</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4218,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46304.97916666666</v>
+        <v>46305.97916666666</v>
       </c>
       <c r="B192">
-        <v>5190</v>
+        <v>4870</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4232,2704 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46304.98958333334</v>
+        <v>46305.98958333334</v>
       </c>
       <c r="B193">
-        <v>5120</v>
+        <v>4820</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>4760</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4710</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4680</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>4630</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4580</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4560</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>4560</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4550</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4550</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>4550</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4550</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4550</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>4550</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4550</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4550</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>4560</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4580</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4600</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>4600</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4620</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4660</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>4680</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4680</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4700</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>4740</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4760</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>4770</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>4780</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>4800</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>4800</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>4800</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>4780</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>4720</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>4660</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>4590</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>4510</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>4420</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>4330</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>4260</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>4190</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>4130</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>4090</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>4060</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>4030</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>4010</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>4000</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>4000</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>4000</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>4020</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>4040</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>4050</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>4070</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>4110</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>4150</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>4170</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>4210</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>4270</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>4330</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>4370</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>4420</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>4480</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>4550</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>4630</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>4740</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>4860</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>4990</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>5110</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>5240</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>5400</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>5530</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>5660</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>5790</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>5930</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>6060</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>6100</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>6100</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>6090</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>6070</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>6040</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>6000</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>5920</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>5840</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>5760</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>5670</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>5540</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5440</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5330</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>5220</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5130</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5040</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>4950</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>4850</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>4830</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>4770</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4730</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4690</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>4650</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4610</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4590</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>4570</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4530</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4520</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>4520</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4520</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4530</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>4530</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4530</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4540</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>4560</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4580</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4610</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>4650</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4700</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4790</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>4920</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5070</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5260</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>5450</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5640</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5850</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>6070</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>6240</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6390</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>6500</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6600</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6650</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>6670</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>6680</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>6680</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>6670</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>6650</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>6610</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>6550</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>6500</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>6460</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46307.40625</v>
+      </c>
+      <c r="B329">
+        <v>6410</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>6350</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46307.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>6290</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46307.4375</v>
+      </c>
+      <c r="B332">
+        <v>6260</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46307.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>6220</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>6180</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46307.46875</v>
+      </c>
+      <c r="B335">
+        <v>6150</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46307.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>6140</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46307.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>6130</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46307.5</v>
+      </c>
+      <c r="B338">
+        <v>6110</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46307.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>6100</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46307.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>6090</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46307.53125</v>
+      </c>
+      <c r="B341">
+        <v>6100</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>6100</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46307.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>6100</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46307.5625</v>
+      </c>
+      <c r="B344">
+        <v>6100</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46307.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>6100</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>6140</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46307.59375</v>
+      </c>
+      <c r="B347">
+        <v>6150</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>6150</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46307.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>6160</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46307.625</v>
+      </c>
+      <c r="B350">
+        <v>6190</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46307.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>6230</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46307.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>6260</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46307.65625</v>
+      </c>
+      <c r="B353">
+        <v>6320</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>6390</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46307.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>6460</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46307.6875</v>
+      </c>
+      <c r="B356">
+        <v>6520</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46307.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>6610</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6710</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46307.71875</v>
+      </c>
+      <c r="B359">
+        <v>6800</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46307.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6890</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46307.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>7000</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46307.75</v>
+      </c>
+      <c r="B362">
+        <v>7110</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46307.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>7220</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46307.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>7270</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46307.78125</v>
+      </c>
+      <c r="B365">
+        <v>7280</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46307.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>7270</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46307.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>7250</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46307.8125</v>
+      </c>
+      <c r="B368">
+        <v>7180</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46307.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>7100</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46307.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6960</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46307.84375</v>
+      </c>
+      <c r="B371">
+        <v>6830</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46307.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6710</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46307.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6580</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46307.875</v>
+      </c>
+      <c r="B374">
+        <v>6430</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46307.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6300</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46307.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>6150</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46307.90625</v>
+      </c>
+      <c r="B377">
+        <v>6020</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5910</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46307.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5790</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46307.9375</v>
+      </c>
+      <c r="B380">
+        <v>5680</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46307.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5570</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46307.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5420</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46307.96875</v>
+      </c>
+      <c r="B383">
+        <v>5360</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46307.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5310</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46307.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5260</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
+  </si>
+  <si>
+    <t>14.10.202660</t>
+  </si>
+  <si>
+    <t>14.10.202661</t>
+  </si>
+  <si>
+    <t>14.10.202662</t>
+  </si>
+  <si>
+    <t>14.10.202663</t>
+  </si>
+  <si>
+    <t>14.10.202664</t>
+  </si>
+  <si>
+    <t>14.10.202665</t>
+  </si>
+  <si>
+    <t>14.10.202666</t>
+  </si>
+  <si>
+    <t>14.10.202667</t>
+  </si>
+  <si>
+    <t>14.10.202668</t>
+  </si>
+  <si>
+    <t>14.10.202669</t>
+  </si>
+  <si>
+    <t>14.10.202670</t>
+  </si>
+  <si>
+    <t>14.10.202671</t>
+  </si>
+  <si>
+    <t>14.10.202672</t>
+  </si>
+  <si>
+    <t>14.10.202673</t>
+  </si>
+  <si>
+    <t>14.10.202674</t>
+  </si>
+  <si>
+    <t>14.10.202675</t>
+  </si>
+  <si>
+    <t>14.10.202676</t>
+  </si>
+  <si>
+    <t>14.10.202677</t>
+  </si>
+  <si>
+    <t>14.10.202678</t>
+  </si>
+  <si>
+    <t>14.10.202679</t>
+  </si>
+  <si>
+    <t>14.10.202680</t>
+  </si>
+  <si>
+    <t>14.10.202681</t>
+  </si>
+  <si>
+    <t>14.10.202682</t>
+  </si>
+  <si>
+    <t>14.10.202683</t>
+  </si>
+  <si>
+    <t>14.10.202684</t>
+  </si>
+  <si>
+    <t>14.10.202685</t>
+  </si>
+  <si>
+    <t>14.10.202686</t>
+  </si>
+  <si>
+    <t>14.10.202687</t>
+  </si>
+  <si>
+    <t>14.10.202688</t>
+  </si>
+  <si>
+    <t>14.10.202689</t>
+  </si>
+  <si>
+    <t>14.10.202690</t>
+  </si>
+  <si>
+    <t>14.10.202691</t>
+  </si>
+  <si>
+    <t>14.10.202692</t>
+  </si>
+  <si>
+    <t>14.10.202693</t>
+  </si>
+  <si>
+    <t>14.10.202694</t>
+  </si>
+  <si>
+    <t>14.10.202695</t>
+  </si>
+  <si>
+    <t>14.10.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>4650</v>
+        <v>5160</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>4610</v>
+        <v>5120</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>4590</v>
+        <v>5100</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>4570</v>
+        <v>5080</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>4530</v>
+        <v>5080</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>4520</v>
+        <v>5080</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>4520</v>
+        <v>5090</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>4520</v>
+        <v>5110</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>4530</v>
+        <v>5130</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>4530</v>
+        <v>5150</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>4530</v>
+        <v>5160</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>4540</v>
+        <v>5160</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>4560</v>
+        <v>5150</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>4580</v>
+        <v>5140</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>4610</v>
+        <v>5130</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>4650</v>
+        <v>5130</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>4700</v>
+        <v>5150</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>4790</v>
+        <v>5200</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>4920</v>
+        <v>5270</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>5070</v>
+        <v>5380</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>5260</v>
+        <v>5500</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>5640</v>
+        <v>5810</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>5850</v>
+        <v>5970</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>6070</v>
+        <v>6140</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>6240</v>
+        <v>6290</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>6390</v>
+        <v>6440</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>6500</v>
+        <v>6570</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>6600</v>
+        <v>6680</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>6650</v>
+        <v>6780</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>6670</v>
+        <v>6850</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>6680</v>
+        <v>6900</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>6680</v>
+        <v>6930</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>6670</v>
+        <v>6940</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>6650</v>
+        <v>6940</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>6610</v>
+        <v>6920</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>6550</v>
+        <v>6880</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>6500</v>
+        <v>6840</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>6460</v>
+        <v>6790</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>6410</v>
+        <v>6720</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>6350</v>
+        <v>6660</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>6290</v>
+        <v>6610</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>6260</v>
+        <v>6570</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>6220</v>
+        <v>6530</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>6180</v>
+        <v>6510</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>6150</v>
+        <v>6490</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>6140</v>
+        <v>6470</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>6130</v>
+        <v>6450</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>6110</v>
+        <v>6440</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>6100</v>
+        <v>6440</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>6090</v>
+        <v>6440</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>6100</v>
+        <v>6440</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>6100</v>
+        <v>6430</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>6100</v>
+        <v>6430</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>6100</v>
+        <v>6420</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>6100</v>
+        <v>6420</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>6140</v>
+        <v>6410</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>6150</v>
+        <v>6400</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>6150</v>
+        <v>6390</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>6160</v>
+        <v>6380</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>6190</v>
+        <v>6400</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>6230</v>
+        <v>6430</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>6260</v>
+        <v>6480</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>6320</v>
+        <v>6530</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>6390</v>
+        <v>6600</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>6460</v>
+        <v>6670</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>6520</v>
+        <v>6750</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>6610</v>
+        <v>6830</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>6710</v>
+        <v>6910</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>6890</v>
+        <v>7090</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>7000</v>
+        <v>7180</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>7110</v>
+        <v>7260</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>7220</v>
+        <v>7330</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>7270</v>
+        <v>7370</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>7280</v>
+        <v>7380</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>7270</v>
+        <v>7370</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>7250</v>
+        <v>7340</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>7180</v>
+        <v>7280</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>7100</v>
+        <v>7180</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>6960</v>
+        <v>7080</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>6830</v>
+        <v>6970</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>6710</v>
+        <v>6850</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>6580</v>
+        <v>6720</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>6430</v>
+        <v>6570</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>6300</v>
+        <v>6450</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>6150</v>
+        <v>6300</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>6020</v>
+        <v>6150</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>5910</v>
+        <v>6010</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>5790</v>
+        <v>5880</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>5680</v>
+        <v>5740</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>5570</v>
+        <v>5630</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>5340</v>
+        <v>5270</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>5260</v>
+        <v>5210</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>5200</v>
+        <v>5170</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>5160</v>
+        <v>5140</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
         <v>5120</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
         <v>5100</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
         <v>5080</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
         <v>5080</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
         <v>5080</v>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
         <v>5090</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
         <v>5110</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>5130</v>
+        <v>5140</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
         <v>5150</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>5160</v>
+        <v>5170</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>5160</v>
+        <v>5180</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>5150</v>
+        <v>5190</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>5140</v>
+        <v>5190</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>5130</v>
+        <v>5170</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>5130</v>
+        <v>5160</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>5150</v>
+        <v>5160</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>5200</v>
+        <v>5210</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>5270</v>
+        <v>5280</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
         <v>5380</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>5500</v>
+        <v>5510</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>5650</v>
+        <v>5670</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>5810</v>
+        <v>5830</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>5970</v>
+        <v>5990</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
         <v>6140</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>6290</v>
+        <v>6280</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>6440</v>
+        <v>6380</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>6570</v>
+        <v>6450</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>6680</v>
+        <v>6490</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>6780</v>
+        <v>6500</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>6850</v>
+        <v>6470</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>6900</v>
+        <v>6420</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>6930</v>
+        <v>6340</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>6940</v>
+        <v>6240</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>6940</v>
+        <v>6130</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>6920</v>
+        <v>6010</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>6880</v>
+        <v>5880</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>6840</v>
+        <v>5760</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>6790</v>
+        <v>5630</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>6720</v>
+        <v>5520</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>6660</v>
+        <v>5410</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>6610</v>
+        <v>5310</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>6570</v>
+        <v>5230</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>6530</v>
+        <v>5170</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>6510</v>
+        <v>5120</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>6490</v>
+        <v>5080</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>6470</v>
+        <v>5070</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>6450</v>
+        <v>5060</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>6440</v>
+        <v>5070</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>6440</v>
+        <v>5080</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>6440</v>
+        <v>5100</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>6440</v>
+        <v>5120</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>6430</v>
+        <v>5140</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>6430</v>
+        <v>5160</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>6420</v>
+        <v>5180</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B153">
-        <v>6420</v>
+        <v>5210</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B154">
-        <v>6410</v>
+        <v>5240</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B155">
-        <v>6400</v>
+        <v>5290</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B156">
-        <v>6390</v>
+        <v>5350</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B157">
-        <v>6380</v>
+        <v>5430</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B158">
-        <v>6400</v>
+        <v>5520</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B159">
-        <v>6430</v>
+        <v>5640</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B160">
-        <v>6480</v>
+        <v>5760</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B161">
-        <v>6530</v>
+        <v>5890</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B162">
-        <v>6600</v>
+        <v>6030</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B163">
-        <v>6670</v>
+        <v>6160</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B164">
-        <v>6750</v>
+        <v>6290</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B165">
-        <v>6830</v>
+        <v>6410</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B166">
-        <v>6910</v>
+        <v>6540</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B167">
-        <v>7000</v>
+        <v>6660</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B168">
-        <v>7090</v>
+        <v>6800</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B169">
-        <v>7180</v>
+        <v>6930</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B170">
-        <v>7260</v>
+        <v>7040</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B171">
-        <v>7330</v>
+        <v>7120</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B172">
-        <v>7370</v>
+        <v>7170</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B173">
-        <v>7380</v>
+        <v>7160</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B174">
-        <v>7370</v>
+        <v>7140</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B175">
-        <v>7340</v>
+        <v>7110</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B176">
-        <v>7280</v>
+        <v>7040</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B177">
-        <v>7180</v>
+        <v>6970</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B178">
-        <v>7080</v>
+        <v>6860</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B179">
-        <v>6970</v>
+        <v>6760</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B180">
-        <v>6850</v>
+        <v>6650</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B181">
-        <v>6720</v>
+        <v>6540</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B182">
-        <v>6570</v>
+        <v>6400</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B183">
-        <v>6450</v>
+        <v>6280</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B184">
-        <v>6300</v>
+        <v>6130</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B185">
-        <v>6150</v>
+        <v>6000</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B186">
-        <v>6010</v>
+        <v>5860</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46308.92708333334</v>
+        <v>46309.92708333334</v>
       </c>
       <c r="B187">
-        <v>5880</v>
+        <v>5740</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46308.9375</v>
+        <v>46309.9375</v>
       </c>
       <c r="B188">
-        <v>5740</v>
+        <v>5600</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46308.94791666666</v>
+        <v>46309.94791666666</v>
       </c>
       <c r="B189">
-        <v>5630</v>
+        <v>5500</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46308.95833333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="B190">
-        <v>5340</v>
+        <v>5480</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46308.96875</v>
+        <v>46309.96875</v>
       </c>
       <c r="B191">
-        <v>5270</v>
+        <v>5420</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46308.97916666666</v>
+        <v>46309.97916666666</v>
       </c>
       <c r="B192">
-        <v>5210</v>
+        <v>5380</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46308.98958333334</v>
+        <v>46309.98958333334</v>
       </c>
       <c r="B193">
-        <v>5170</v>
+        <v>5330</v>
       </c>
       <c r="C193">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
-  </si>
-  <si>
-    <t>14.10.202660</t>
-  </si>
-  <si>
-    <t>14.10.202661</t>
-  </si>
-  <si>
-    <t>14.10.202662</t>
-  </si>
-  <si>
-    <t>14.10.202663</t>
-  </si>
-  <si>
-    <t>14.10.202664</t>
-  </si>
-  <si>
-    <t>14.10.202665</t>
-  </si>
-  <si>
-    <t>14.10.202666</t>
-  </si>
-  <si>
-    <t>14.10.202667</t>
-  </si>
-  <si>
-    <t>14.10.202668</t>
-  </si>
-  <si>
-    <t>14.10.202669</t>
-  </si>
-  <si>
-    <t>14.10.202670</t>
-  </si>
-  <si>
-    <t>14.10.202671</t>
-  </si>
-  <si>
-    <t>14.10.202672</t>
-  </si>
-  <si>
-    <t>14.10.202673</t>
-  </si>
-  <si>
-    <t>14.10.202674</t>
-  </si>
-  <si>
-    <t>14.10.202675</t>
-  </si>
-  <si>
-    <t>14.10.202676</t>
-  </si>
-  <si>
-    <t>14.10.202677</t>
-  </si>
-  <si>
-    <t>14.10.202678</t>
-  </si>
-  <si>
-    <t>14.10.202679</t>
-  </si>
-  <si>
-    <t>14.10.202680</t>
-  </si>
-  <si>
-    <t>14.10.202681</t>
-  </si>
-  <si>
-    <t>14.10.202682</t>
-  </si>
-  <si>
-    <t>14.10.202683</t>
-  </si>
-  <si>
-    <t>14.10.202684</t>
-  </si>
-  <si>
-    <t>14.10.202685</t>
-  </si>
-  <si>
-    <t>14.10.202686</t>
-  </si>
-  <si>
-    <t>14.10.202687</t>
-  </si>
-  <si>
-    <t>14.10.202688</t>
-  </si>
-  <si>
-    <t>14.10.202689</t>
-  </si>
-  <si>
-    <t>14.10.202690</t>
-  </si>
-  <si>
-    <t>14.10.202691</t>
-  </si>
-  <si>
-    <t>14.10.202692</t>
-  </si>
-  <si>
-    <t>14.10.202693</t>
-  </si>
-  <si>
-    <t>14.10.202694</t>
-  </si>
-  <si>
-    <t>14.10.202695</t>
-  </si>
-  <si>
-    <t>14.10.202696</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
+  </si>
+  <si>
+    <t>16.10.202653</t>
+  </si>
+  <si>
+    <t>16.10.202654</t>
+  </si>
+  <si>
+    <t>16.10.202655</t>
+  </si>
+  <si>
+    <t>16.10.202656</t>
+  </si>
+  <si>
+    <t>16.10.202657</t>
+  </si>
+  <si>
+    <t>16.10.202658</t>
+  </si>
+  <si>
+    <t>16.10.202659</t>
+  </si>
+  <si>
+    <t>16.10.202660</t>
+  </si>
+  <si>
+    <t>16.10.202661</t>
+  </si>
+  <si>
+    <t>16.10.202662</t>
+  </si>
+  <si>
+    <t>16.10.202663</t>
+  </si>
+  <si>
+    <t>16.10.202664</t>
+  </si>
+  <si>
+    <t>16.10.202665</t>
+  </si>
+  <si>
+    <t>16.10.202666</t>
+  </si>
+  <si>
+    <t>16.10.202667</t>
+  </si>
+  <si>
+    <t>16.10.202668</t>
+  </si>
+  <si>
+    <t>16.10.202669</t>
+  </si>
+  <si>
+    <t>16.10.202670</t>
+  </si>
+  <si>
+    <t>16.10.202671</t>
+  </si>
+  <si>
+    <t>16.10.202672</t>
+  </si>
+  <si>
+    <t>16.10.202673</t>
+  </si>
+  <si>
+    <t>16.10.202674</t>
+  </si>
+  <si>
+    <t>16.10.202675</t>
+  </si>
+  <si>
+    <t>16.10.202676</t>
+  </si>
+  <si>
+    <t>16.10.202677</t>
+  </si>
+  <si>
+    <t>16.10.202678</t>
+  </si>
+  <si>
+    <t>16.10.202679</t>
+  </si>
+  <si>
+    <t>16.10.202680</t>
+  </si>
+  <si>
+    <t>16.10.202681</t>
+  </si>
+  <si>
+    <t>16.10.202682</t>
+  </si>
+  <si>
+    <t>16.10.202683</t>
+  </si>
+  <si>
+    <t>16.10.202684</t>
+  </si>
+  <si>
+    <t>16.10.202685</t>
+  </si>
+  <si>
+    <t>16.10.202686</t>
+  </si>
+  <si>
+    <t>16.10.202687</t>
+  </si>
+  <si>
+    <t>16.10.202688</t>
+  </si>
+  <si>
+    <t>16.10.202689</t>
+  </si>
+  <si>
+    <t>16.10.202690</t>
+  </si>
+  <si>
+    <t>16.10.202691</t>
+  </si>
+  <si>
+    <t>16.10.202692</t>
+  </si>
+  <si>
+    <t>16.10.202693</t>
+  </si>
+  <si>
+    <t>16.10.202694</t>
+  </si>
+  <si>
+    <t>16.10.202695</t>
+  </si>
+  <si>
+    <t>16.10.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>5160</v>
+        <v>5270</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>5120</v>
+        <v>5230</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>5080</v>
+        <v>5150</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>5150</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>5090</v>
+        <v>5150</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>5110</v>
+        <v>5170</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>5130</v>
+        <v>5230</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>5150</v>
+        <v>5270</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>5160</v>
+        <v>5310</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>5160</v>
+        <v>5320</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>5150</v>
+        <v>5360</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>5140</v>
+        <v>5350</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>5130</v>
+        <v>5350</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>5130</v>
+        <v>5340</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>5150</v>
+        <v>5340</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>5200</v>
+        <v>5340</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>5270</v>
+        <v>5340</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>5380</v>
+        <v>5360</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>5500</v>
+        <v>5620</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>5650</v>
+        <v>5820</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>5810</v>
+        <v>5990</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>5970</v>
+        <v>6170</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>6140</v>
+        <v>6370</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>6290</v>
+        <v>6540</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>6440</v>
+        <v>6690</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>6570</v>
+        <v>6800</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>6680</v>
+        <v>6900</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>6780</v>
+        <v>6950</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>6850</v>
+        <v>6960</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>6900</v>
+        <v>6950</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>6930</v>
+        <v>6890</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>6940</v>
+        <v>6800</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>6940</v>
+        <v>6710</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>6920</v>
+        <v>6600</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>6880</v>
+        <v>6480</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>6840</v>
+        <v>6360</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>6790</v>
+        <v>6250</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>6720</v>
+        <v>6130</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>6660</v>
+        <v>6030</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>6610</v>
+        <v>5950</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>6570</v>
+        <v>5890</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>6530</v>
+        <v>5810</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>6510</v>
+        <v>5700</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>6490</v>
+        <v>5660</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>6470</v>
+        <v>5630</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>6450</v>
+        <v>5620</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>6440</v>
+        <v>5670</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>6440</v>
+        <v>5700</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>6440</v>
+        <v>5700</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>6440</v>
+        <v>5710</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>6430</v>
+        <v>5730</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>6430</v>
+        <v>5750</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>6420</v>
+        <v>5750</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>6420</v>
+        <v>5770</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>6410</v>
+        <v>5810</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>6400</v>
+        <v>5830</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>6390</v>
+        <v>5860</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>6380</v>
+        <v>5910</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>6400</v>
+        <v>5980</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>6430</v>
+        <v>6050</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>6480</v>
+        <v>6140</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>6530</v>
+        <v>6230</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>6600</v>
+        <v>6340</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>6670</v>
+        <v>6450</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>6750</v>
+        <v>6560</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>6830</v>
+        <v>6680</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>6910</v>
+        <v>6810</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>7000</v>
+        <v>6920</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>7090</v>
+        <v>7030</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>7180</v>
+        <v>7140</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>7260</v>
+        <v>7240</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
         <v>7330</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
         <v>7370</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
         <v>7380</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>7370</v>
+        <v>7360</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>7340</v>
+        <v>7310</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>7280</v>
+        <v>7260</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>7080</v>
+        <v>7070</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>6970</v>
+        <v>6940</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>6850</v>
+        <v>6820</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>6720</v>
+        <v>6700</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>6570</v>
+        <v>6520</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>6450</v>
+        <v>6380</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>6300</v>
+        <v>6230</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>6150</v>
+        <v>6090</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>6010</v>
+        <v>5980</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>5880</v>
+        <v>5850</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>5740</v>
+        <v>5730</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>5340</v>
+        <v>5480</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>5270</v>
+        <v>5430</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>5210</v>
+        <v>5380</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>5170</v>
+        <v>5320</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>5140</v>
+        <v>5280</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>5120</v>
+        <v>5260</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>5100</v>
+        <v>5240</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>5080</v>
+        <v>5220</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>5080</v>
+        <v>5210</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>5080</v>
+        <v>5210</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>5090</v>
+        <v>5230</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>5110</v>
+        <v>5240</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>5140</v>
+        <v>5310</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>5150</v>
+        <v>5330</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>5170</v>
+        <v>5330</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>5180</v>
+        <v>5320</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>5190</v>
+        <v>5280</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>5190</v>
+        <v>5260</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>5170</v>
+        <v>5250</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>5160</v>
+        <v>5250</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>5160</v>
+        <v>5270</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>5210</v>
+        <v>5310</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>5280</v>
+        <v>5370</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>5380</v>
+        <v>5480</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>5510</v>
+        <v>5650</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>5670</v>
+        <v>5870</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>5830</v>
+        <v>6060</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>5990</v>
+        <v>6280</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>6140</v>
+        <v>6500</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>6280</v>
+        <v>6670</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>6380</v>
+        <v>6780</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>6450</v>
+        <v>6870</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>6490</v>
+        <v>6930</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>6500</v>
+        <v>6950</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>6470</v>
+        <v>6960</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>6420</v>
+        <v>6940</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>6340</v>
+        <v>6890</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>6240</v>
+        <v>6840</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>6130</v>
+        <v>6770</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>6010</v>
+        <v>6700</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>5880</v>
+        <v>6620</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>5760</v>
+        <v>6540</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>5630</v>
+        <v>6460</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>5520</v>
+        <v>6380</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>5410</v>
+        <v>6300</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>5310</v>
+        <v>6230</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>5230</v>
+        <v>6170</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>5170</v>
+        <v>6120</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>5120</v>
+        <v>6060</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>5080</v>
+        <v>6020</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>5070</v>
+        <v>5990</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>5060</v>
+        <v>5960</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>5070</v>
+        <v>5950</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>5080</v>
+        <v>5940</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>5100</v>
+        <v>5940</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
-        <v>5120</v>
+        <v>5940</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B150">
-        <v>5140</v>
+        <v>5930</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B151">
-        <v>5160</v>
+        <v>5920</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B152">
-        <v>5180</v>
+        <v>5920</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B153">
-        <v>5210</v>
+        <v>5910</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B154">
-        <v>5240</v>
+        <v>5900</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B155">
-        <v>5290</v>
+        <v>5900</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B156">
-        <v>5350</v>
+        <v>5910</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B157">
-        <v>5430</v>
+        <v>5920</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B158">
-        <v>5520</v>
+        <v>5950</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B159">
-        <v>5640</v>
+        <v>6000</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B160">
-        <v>5760</v>
+        <v>6080</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B161">
-        <v>5890</v>
+        <v>6170</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B162">
-        <v>6030</v>
+        <v>6280</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B163">
-        <v>6160</v>
+        <v>6400</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B164">
-        <v>6290</v>
+        <v>6510</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B165">
-        <v>6410</v>
+        <v>6620</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B166">
-        <v>6540</v>
+        <v>6750</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B167">
-        <v>6660</v>
+        <v>6860</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B168">
-        <v>6800</v>
+        <v>6970</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B169">
-        <v>6930</v>
+        <v>7080</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B170">
-        <v>7040</v>
+        <v>7170</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B171">
-        <v>7120</v>
+        <v>7250</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B172">
-        <v>7170</v>
+        <v>7280</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B173">
-        <v>7160</v>
+        <v>7280</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B174">
-        <v>7140</v>
+        <v>7270</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B175">
-        <v>7110</v>
+        <v>7250</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B176">
-        <v>7040</v>
+        <v>7200</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B177">
-        <v>6970</v>
+        <v>7150</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B178">
-        <v>6860</v>
+        <v>7040</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B179">
-        <v>6760</v>
+        <v>6920</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B180">
-        <v>6650</v>
+        <v>6790</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B181">
-        <v>6540</v>
+        <v>6640</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B182">
-        <v>6400</v>
+        <v>6480</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B183">
-        <v>6280</v>
+        <v>6350</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B184">
-        <v>6130</v>
+        <v>6210</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B185">
-        <v>6000</v>
+        <v>6090</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B186">
-        <v>5860</v>
+        <v>5960</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46309.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B187">
-        <v>5740</v>
+        <v>5840</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46309.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B188">
-        <v>5600</v>
+        <v>5740</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46309.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B189">
-        <v>5500</v>
+        <v>5630</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46309.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="B190">
-        <v>5480</v>
+        <v>5450</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46309.96875</v>
+        <v>46311.96875</v>
       </c>
       <c r="B191">
-        <v>5420</v>
+        <v>5380</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46309.97916666666</v>
+        <v>46311.97916666666</v>
       </c>
       <c r="B192">
-        <v>5380</v>
+        <v>5340</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46309.98958333334</v>
+        <v>46311.98958333334</v>
       </c>
       <c r="B193">
-        <v>5330</v>
+        <v>5300</v>
       </c>
       <c r="C193">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
-  </si>
-  <si>
-    <t>16.10.202653</t>
-  </si>
-  <si>
-    <t>16.10.202654</t>
-  </si>
-  <si>
-    <t>16.10.202655</t>
-  </si>
-  <si>
-    <t>16.10.202656</t>
-  </si>
-  <si>
-    <t>16.10.202657</t>
-  </si>
-  <si>
-    <t>16.10.202658</t>
-  </si>
-  <si>
-    <t>16.10.202659</t>
-  </si>
-  <si>
-    <t>16.10.202660</t>
-  </si>
-  <si>
-    <t>16.10.202661</t>
-  </si>
-  <si>
-    <t>16.10.202662</t>
-  </si>
-  <si>
-    <t>16.10.202663</t>
-  </si>
-  <si>
-    <t>16.10.202664</t>
-  </si>
-  <si>
-    <t>16.10.202665</t>
-  </si>
-  <si>
-    <t>16.10.202666</t>
-  </si>
-  <si>
-    <t>16.10.202667</t>
-  </si>
-  <si>
-    <t>16.10.202668</t>
-  </si>
-  <si>
-    <t>16.10.202669</t>
-  </si>
-  <si>
-    <t>16.10.202670</t>
-  </si>
-  <si>
-    <t>16.10.202671</t>
-  </si>
-  <si>
-    <t>16.10.202672</t>
-  </si>
-  <si>
-    <t>16.10.202673</t>
-  </si>
-  <si>
-    <t>16.10.202674</t>
-  </si>
-  <si>
-    <t>16.10.202675</t>
-  </si>
-  <si>
-    <t>16.10.202676</t>
-  </si>
-  <si>
-    <t>16.10.202677</t>
-  </si>
-  <si>
-    <t>16.10.202678</t>
-  </si>
-  <si>
-    <t>16.10.202679</t>
-  </si>
-  <si>
-    <t>16.10.202680</t>
-  </si>
-  <si>
-    <t>16.10.202681</t>
-  </si>
-  <si>
-    <t>16.10.202682</t>
-  </si>
-  <si>
-    <t>16.10.202683</t>
-  </si>
-  <si>
-    <t>16.10.202684</t>
-  </si>
-  <si>
-    <t>16.10.202685</t>
-  </si>
-  <si>
-    <t>16.10.202686</t>
-  </si>
-  <si>
-    <t>16.10.202687</t>
-  </si>
-  <si>
-    <t>16.10.202688</t>
-  </si>
-  <si>
-    <t>16.10.202689</t>
-  </si>
-  <si>
-    <t>16.10.202690</t>
-  </si>
-  <si>
-    <t>16.10.202691</t>
-  </si>
-  <si>
-    <t>16.10.202692</t>
-  </si>
-  <si>
-    <t>16.10.202693</t>
-  </si>
-  <si>
-    <t>16.10.202694</t>
-  </si>
-  <si>
-    <t>16.10.202695</t>
-  </si>
-  <si>
-    <t>16.10.202696</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
+  </si>
+  <si>
+    <t>21.10.202636</t>
+  </si>
+  <si>
+    <t>21.10.202637</t>
+  </si>
+  <si>
+    <t>21.10.202638</t>
+  </si>
+  <si>
+    <t>21.10.202639</t>
+  </si>
+  <si>
+    <t>21.10.202640</t>
+  </si>
+  <si>
+    <t>21.10.202641</t>
+  </si>
+  <si>
+    <t>21.10.202642</t>
+  </si>
+  <si>
+    <t>21.10.202643</t>
+  </si>
+  <si>
+    <t>21.10.202644</t>
+  </si>
+  <si>
+    <t>21.10.202645</t>
+  </si>
+  <si>
+    <t>21.10.202646</t>
+  </si>
+  <si>
+    <t>21.10.202647</t>
+  </si>
+  <si>
+    <t>21.10.202648</t>
+  </si>
+  <si>
+    <t>21.10.202649</t>
+  </si>
+  <si>
+    <t>21.10.202650</t>
+  </si>
+  <si>
+    <t>21.10.202651</t>
+  </si>
+  <si>
+    <t>21.10.202652</t>
+  </si>
+  <si>
+    <t>21.10.202653</t>
+  </si>
+  <si>
+    <t>21.10.202654</t>
+  </si>
+  <si>
+    <t>21.10.202655</t>
+  </si>
+  <si>
+    <t>21.10.202656</t>
+  </si>
+  <si>
+    <t>21.10.202657</t>
+  </si>
+  <si>
+    <t>21.10.202658</t>
+  </si>
+  <si>
+    <t>21.10.202659</t>
+  </si>
+  <si>
+    <t>21.10.202660</t>
+  </si>
+  <si>
+    <t>21.10.202661</t>
+  </si>
+  <si>
+    <t>21.10.202662</t>
+  </si>
+  <si>
+    <t>21.10.202663</t>
+  </si>
+  <si>
+    <t>21.10.202664</t>
+  </si>
+  <si>
+    <t>21.10.202665</t>
+  </si>
+  <si>
+    <t>21.10.202666</t>
+  </si>
+  <si>
+    <t>21.10.202667</t>
+  </si>
+  <si>
+    <t>21.10.202668</t>
+  </si>
+  <si>
+    <t>21.10.202669</t>
+  </si>
+  <si>
+    <t>21.10.202670</t>
+  </si>
+  <si>
+    <t>21.10.202671</t>
+  </si>
+  <si>
+    <t>21.10.202672</t>
+  </si>
+  <si>
+    <t>21.10.202673</t>
+  </si>
+  <si>
+    <t>21.10.202674</t>
+  </si>
+  <si>
+    <t>21.10.202675</t>
+  </si>
+  <si>
+    <t>21.10.202676</t>
+  </si>
+  <si>
+    <t>21.10.202677</t>
+  </si>
+  <si>
+    <t>21.10.202678</t>
+  </si>
+  <si>
+    <t>21.10.202679</t>
+  </si>
+  <si>
+    <t>21.10.202680</t>
+  </si>
+  <si>
+    <t>21.10.202681</t>
+  </si>
+  <si>
+    <t>21.10.202682</t>
+  </si>
+  <si>
+    <t>21.10.202683</t>
+  </si>
+  <si>
+    <t>21.10.202684</t>
+  </si>
+  <si>
+    <t>21.10.202685</t>
+  </si>
+  <si>
+    <t>21.10.202686</t>
+  </si>
+  <si>
+    <t>21.10.202687</t>
+  </si>
+  <si>
+    <t>21.10.202688</t>
+  </si>
+  <si>
+    <t>21.10.202689</t>
+  </si>
+  <si>
+    <t>21.10.202690</t>
+  </si>
+  <si>
+    <t>21.10.202691</t>
+  </si>
+  <si>
+    <t>21.10.202692</t>
+  </si>
+  <si>
+    <t>21.10.202693</t>
+  </si>
+  <si>
+    <t>21.10.202694</t>
+  </si>
+  <si>
+    <t>21.10.202695</t>
+  </si>
+  <si>
+    <t>21.10.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>5270</v>
+        <v>5230</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>5230</v>
+        <v>5200</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
         <v>5200</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
         <v>5180</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>5150</v>
+        <v>5160</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
         <v>5150</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
         <v>5150</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>5170</v>
+        <v>5180</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>5230</v>
+        <v>5210</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>5270</v>
+        <v>5250</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>5310</v>
+        <v>5270</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>5320</v>
+        <v>5280</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>5360</v>
+        <v>5300</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>5340</v>
+        <v>5300</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>5340</v>
+        <v>5300</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>5340</v>
+        <v>5310</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>5340</v>
+        <v>5380</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>5360</v>
+        <v>5500</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>5620</v>
+        <v>5680</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>5820</v>
+        <v>5890</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>5990</v>
+        <v>6070</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>6170</v>
+        <v>6260</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>6370</v>
+        <v>6460</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>6540</v>
+        <v>6620</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>6690</v>
+        <v>6740</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>6800</v>
+        <v>6840</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>6900</v>
+        <v>6920</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>6950</v>
+        <v>6940</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>6960</v>
+        <v>6930</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>6950</v>
+        <v>6890</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>6890</v>
+        <v>6790</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>6710</v>
+        <v>6610</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>6600</v>
+        <v>6510</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>6480</v>
+        <v>6410</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>6360</v>
+        <v>6310</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>6130</v>
+        <v>6080</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>6030</v>
+        <v>5940</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>5950</v>
+        <v>5830</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>5890</v>
+        <v>5750</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>5810</v>
+        <v>5680</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>5660</v>
+        <v>5550</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>5630</v>
+        <v>5510</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>5620</v>
+        <v>5510</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>5670</v>
+        <v>5550</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>5700</v>
+        <v>5550</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>5700</v>
+        <v>5550</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>5710</v>
+        <v>5550</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>5730</v>
+        <v>5520</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>5750</v>
+        <v>5520</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>5750</v>
+        <v>5520</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>5770</v>
+        <v>5520</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>5810</v>
+        <v>5560</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>5830</v>
+        <v>5590</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>5860</v>
+        <v>5640</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>5910</v>
+        <v>5710</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>5980</v>
+        <v>5810</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>6050</v>
+        <v>5920</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>6140</v>
+        <v>6040</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>6230</v>
+        <v>6160</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>6340</v>
+        <v>6270</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>6450</v>
+        <v>6390</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>6560</v>
+        <v>6510</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>6680</v>
+        <v>6630</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>6810</v>
+        <v>6780</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>6920</v>
+        <v>6900</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
         <v>7140</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
         <v>7240</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>7330</v>
+        <v>7320</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
         <v>7370</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>7380</v>
+        <v>7370</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>7360</v>
+        <v>7340</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
         <v>7310</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>7260</v>
+        <v>7250</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>7190</v>
+        <v>7180</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>7070</v>
+        <v>7040</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>6940</v>
+        <v>6920</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>6820</v>
+        <v>6790</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>6700</v>
+        <v>6660</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>6520</v>
+        <v>6500</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>6380</v>
+        <v>6350</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>6230</v>
+        <v>6190</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>6090</v>
+        <v>6080</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
         <v>5980</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>5850</v>
+        <v>5860</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>5730</v>
+        <v>5760</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>5620</v>
+        <v>5650</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
         <v>5480</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>5430</v>
+        <v>5410</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>5380</v>
+        <v>5370</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>5320</v>
+        <v>5340</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>5280</v>
+        <v>5330</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>5260</v>
+        <v>5330</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>5240</v>
+        <v>5320</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>5220</v>
+        <v>5310</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>5210</v>
+        <v>5280</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>5210</v>
+        <v>5250</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
         <v>5230</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>5240</v>
+        <v>5220</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>5310</v>
+        <v>5200</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>5330</v>
+        <v>5200</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>5330</v>
+        <v>5200</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>5320</v>
+        <v>5210</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>5280</v>
+        <v>5230</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>5260</v>
+        <v>5230</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>5250</v>
+        <v>5230</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>5250</v>
+        <v>5230</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>5270</v>
+        <v>5230</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>5310</v>
+        <v>5290</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
         <v>5370</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>5480</v>
+        <v>5470</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>5650</v>
+        <v>5620</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>5870</v>
+        <v>5780</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>6060</v>
+        <v>5950</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>6280</v>
+        <v>6130</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>6500</v>
+        <v>6370</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>6670</v>
+        <v>6550</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>6780</v>
+        <v>6680</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>6870</v>
+        <v>6800</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>6930</v>
+        <v>6920</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>6950</v>
+        <v>6970</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>6960</v>
+        <v>6970</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
         <v>6940</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>6890</v>
+        <v>6840</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>6840</v>
+        <v>6730</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>6770</v>
+        <v>6610</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B133">
-        <v>6700</v>
+        <v>6470</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B134">
-        <v>6620</v>
+        <v>6330</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B135">
-        <v>6540</v>
+        <v>6170</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B136">
-        <v>6460</v>
+        <v>5980</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B137">
-        <v>6380</v>
+        <v>5800</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B138">
-        <v>6300</v>
+        <v>5590</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B139">
-        <v>6230</v>
+        <v>5420</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B140">
-        <v>6170</v>
+        <v>5260</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B141">
-        <v>6120</v>
+        <v>5140</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B142">
-        <v>6060</v>
+        <v>5020</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B143">
-        <v>6020</v>
+        <v>4940</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B144">
-        <v>5990</v>
+        <v>4920</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B145">
-        <v>5960</v>
+        <v>4940</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B146">
-        <v>5950</v>
+        <v>4960</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B147">
-        <v>5940</v>
+        <v>4980</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B148">
-        <v>5940</v>
+        <v>4990</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B149">
-        <v>5940</v>
+        <v>4990</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B150">
-        <v>5930</v>
+        <v>5020</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B151">
-        <v>5920</v>
+        <v>5030</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B152">
-        <v>5920</v>
+        <v>5030</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B153">
-        <v>5910</v>
+        <v>5040</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B154">
-        <v>5900</v>
+        <v>5100</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B155">
-        <v>5900</v>
+        <v>5150</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B156">
-        <v>5910</v>
+        <v>5220</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B157">
-        <v>5920</v>
+        <v>5330</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B158">
-        <v>5950</v>
+        <v>5460</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B159">
-        <v>6000</v>
+        <v>5600</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B160">
-        <v>6080</v>
+        <v>5750</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B161">
-        <v>6170</v>
+        <v>5920</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B162">
-        <v>6280</v>
+        <v>6090</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B163">
-        <v>6400</v>
+        <v>6250</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B164">
-        <v>6510</v>
+        <v>6400</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B165">
-        <v>6620</v>
+        <v>6560</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B166">
-        <v>6750</v>
+        <v>6740</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B167">
-        <v>6860</v>
+        <v>6890</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B168">
-        <v>6970</v>
+        <v>7020</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B169">
-        <v>7080</v>
+        <v>7150</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B170">
-        <v>7170</v>
+        <v>7250</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B171">
-        <v>7250</v>
+        <v>7330</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B172">
-        <v>7280</v>
+        <v>7370</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B173">
-        <v>7280</v>
+        <v>7370</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B174">
-        <v>7270</v>
+        <v>7330</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B175">
-        <v>7250</v>
+        <v>7290</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B176">
-        <v>7200</v>
+        <v>7230</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B177">
         <v>7150</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B178">
-        <v>7040</v>
+        <v>7020</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B179">
-        <v>6920</v>
+        <v>6890</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B180">
-        <v>6790</v>
+        <v>6770</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B181">
         <v>6640</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B182">
-        <v>6480</v>
+        <v>6470</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B183">
-        <v>6350</v>
+        <v>6320</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B184">
-        <v>6210</v>
+        <v>6170</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B185">
-        <v>6090</v>
+        <v>6060</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B186">
-        <v>5960</v>
+        <v>5970</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B187">
-        <v>5840</v>
+        <v>5860</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B188">
         <v>5740</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B189">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46311.95833333334</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="B190">
-        <v>5450</v>
+        <v>5500</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46311.96875</v>
+        <v>46316.96875</v>
       </c>
       <c r="B191">
-        <v>5380</v>
+        <v>5440</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46311.97916666666</v>
+        <v>46316.97916666666</v>
       </c>
       <c r="B192">
-        <v>5340</v>
+        <v>5390</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46311.98958333334</v>
+        <v>46316.98958333334</v>
       </c>
       <c r="B193">
-        <v>5300</v>
+        <v>5340</v>
       </c>
       <c r="C193">
         <v>96</v>

--- a/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="196">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
-  </si>
-  <si>
-    <t>21.10.202636</t>
-  </si>
-  <si>
-    <t>21.10.202637</t>
-  </si>
-  <si>
-    <t>21.10.202638</t>
-  </si>
-  <si>
-    <t>21.10.202639</t>
-  </si>
-  <si>
-    <t>21.10.202640</t>
-  </si>
-  <si>
-    <t>21.10.202641</t>
-  </si>
-  <si>
-    <t>21.10.202642</t>
-  </si>
-  <si>
-    <t>21.10.202643</t>
-  </si>
-  <si>
-    <t>21.10.202644</t>
-  </si>
-  <si>
-    <t>21.10.202645</t>
-  </si>
-  <si>
-    <t>21.10.202646</t>
-  </si>
-  <si>
-    <t>21.10.202647</t>
-  </si>
-  <si>
-    <t>21.10.202648</t>
-  </si>
-  <si>
-    <t>21.10.202649</t>
-  </si>
-  <si>
-    <t>21.10.202650</t>
-  </si>
-  <si>
-    <t>21.10.202651</t>
-  </si>
-  <si>
-    <t>21.10.202652</t>
-  </si>
-  <si>
-    <t>21.10.202653</t>
-  </si>
-  <si>
-    <t>21.10.202654</t>
-  </si>
-  <si>
-    <t>21.10.202655</t>
-  </si>
-  <si>
-    <t>21.10.202656</t>
-  </si>
-  <si>
-    <t>21.10.202657</t>
-  </si>
-  <si>
-    <t>21.10.202658</t>
-  </si>
-  <si>
-    <t>21.10.202659</t>
-  </si>
-  <si>
-    <t>21.10.202660</t>
-  </si>
-  <si>
-    <t>21.10.202661</t>
-  </si>
-  <si>
-    <t>21.10.202662</t>
-  </si>
-  <si>
-    <t>21.10.202663</t>
-  </si>
-  <si>
-    <t>21.10.202664</t>
-  </si>
-  <si>
-    <t>21.10.202665</t>
-  </si>
-  <si>
-    <t>21.10.202666</t>
-  </si>
-  <si>
-    <t>21.10.202667</t>
-  </si>
-  <si>
-    <t>21.10.202668</t>
-  </si>
-  <si>
-    <t>21.10.202669</t>
-  </si>
-  <si>
-    <t>21.10.202670</t>
-  </si>
-  <si>
-    <t>21.10.202671</t>
-  </si>
-  <si>
-    <t>21.10.202672</t>
-  </si>
-  <si>
-    <t>21.10.202673</t>
-  </si>
-  <si>
-    <t>21.10.202674</t>
-  </si>
-  <si>
-    <t>21.10.202675</t>
-  </si>
-  <si>
-    <t>21.10.202676</t>
-  </si>
-  <si>
-    <t>21.10.202677</t>
-  </si>
-  <si>
-    <t>21.10.202678</t>
-  </si>
-  <si>
-    <t>21.10.202679</t>
-  </si>
-  <si>
-    <t>21.10.202680</t>
-  </si>
-  <si>
-    <t>21.10.202681</t>
-  </si>
-  <si>
-    <t>21.10.202682</t>
-  </si>
-  <si>
-    <t>21.10.202683</t>
-  </si>
-  <si>
-    <t>21.10.202684</t>
-  </si>
-  <si>
-    <t>21.10.202685</t>
-  </si>
-  <si>
-    <t>21.10.202686</t>
-  </si>
-  <si>
-    <t>21.10.202687</t>
-  </si>
-  <si>
-    <t>21.10.202688</t>
-  </si>
-  <si>
-    <t>21.10.202689</t>
-  </si>
-  <si>
-    <t>21.10.202690</t>
-  </si>
-  <si>
-    <t>21.10.202691</t>
-  </si>
-  <si>
-    <t>21.10.202692</t>
-  </si>
-  <si>
-    <t>21.10.202693</t>
-  </si>
-  <si>
-    <t>21.10.202694</t>
-  </si>
-  <si>
-    <t>21.10.202695</t>
-  </si>
-  <si>
-    <t>21.10.202696</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
+  </si>
+  <si>
+    <t>25.10.202638</t>
+  </si>
+  <si>
+    <t>25.10.202639</t>
+  </si>
+  <si>
+    <t>25.10.202640</t>
+  </si>
+  <si>
+    <t>25.10.202641</t>
+  </si>
+  <si>
+    <t>25.10.202642</t>
+  </si>
+  <si>
+    <t>25.10.202643</t>
+  </si>
+  <si>
+    <t>25.10.202644</t>
+  </si>
+  <si>
+    <t>25.10.202645</t>
+  </si>
+  <si>
+    <t>25.10.202646</t>
+  </si>
+  <si>
+    <t>25.10.202647</t>
+  </si>
+  <si>
+    <t>25.10.202648</t>
+  </si>
+  <si>
+    <t>25.10.202649</t>
+  </si>
+  <si>
+    <t>25.10.202650</t>
+  </si>
+  <si>
+    <t>25.10.202651</t>
+  </si>
+  <si>
+    <t>25.10.202652</t>
+  </si>
+  <si>
+    <t>25.10.202653</t>
+  </si>
+  <si>
+    <t>25.10.202654</t>
+  </si>
+  <si>
+    <t>25.10.202655</t>
+  </si>
+  <si>
+    <t>25.10.202656</t>
+  </si>
+  <si>
+    <t>25.10.202657</t>
+  </si>
+  <si>
+    <t>25.10.202658</t>
+  </si>
+  <si>
+    <t>25.10.202659</t>
+  </si>
+  <si>
+    <t>25.10.202660</t>
+  </si>
+  <si>
+    <t>25.10.202661</t>
+  </si>
+  <si>
+    <t>25.10.202662</t>
+  </si>
+  <si>
+    <t>25.10.202663</t>
+  </si>
+  <si>
+    <t>25.10.202664</t>
+  </si>
+  <si>
+    <t>25.10.202665</t>
+  </si>
+  <si>
+    <t>25.10.202666</t>
+  </si>
+  <si>
+    <t>25.10.202667</t>
+  </si>
+  <si>
+    <t>25.10.202668</t>
+  </si>
+  <si>
+    <t>25.10.202669</t>
+  </si>
+  <si>
+    <t>25.10.202670</t>
+  </si>
+  <si>
+    <t>25.10.202671</t>
+  </si>
+  <si>
+    <t>25.10.202672</t>
+  </si>
+  <si>
+    <t>25.10.202673</t>
+  </si>
+  <si>
+    <t>25.10.202674</t>
+  </si>
+  <si>
+    <t>25.10.202675</t>
+  </si>
+  <si>
+    <t>25.10.202676</t>
+  </si>
+  <si>
+    <t>25.10.202677</t>
+  </si>
+  <si>
+    <t>25.10.202678</t>
+  </si>
+  <si>
+    <t>25.10.202679</t>
+  </si>
+  <si>
+    <t>25.10.202680</t>
+  </si>
+  <si>
+    <t>25.10.202681</t>
+  </si>
+  <si>
+    <t>25.10.202682</t>
+  </si>
+  <si>
+    <t>25.10.202683</t>
+  </si>
+  <si>
+    <t>25.10.202684</t>
+  </si>
+  <si>
+    <t>25.10.202685</t>
+  </si>
+  <si>
+    <t>25.10.202686</t>
+  </si>
+  <si>
+    <t>25.10.202687</t>
+  </si>
+  <si>
+    <t>25.10.202688</t>
+  </si>
+  <si>
+    <t>25.10.202689</t>
+  </si>
+  <si>
+    <t>25.10.202690</t>
+  </si>
+  <si>
+    <t>25.10.202691</t>
+  </si>
+  <si>
+    <t>25.10.202692</t>
+  </si>
+  <si>
+    <t>25.10.202693</t>
+  </si>
+  <si>
+    <t>25.10.202694</t>
+  </si>
+  <si>
+    <t>25.10.202695</t>
+  </si>
+  <si>
+    <t>25.10.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>5230</v>
+        <v>5320</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>5200</v>
+        <v>5280</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>5180</v>
+        <v>5220</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>5160</v>
+        <v>5170</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
         <v>5150</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
         <v>5150</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>5180</v>
+        <v>5150</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>5210</v>
+        <v>5180</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>5270</v>
+        <v>5210</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>5280</v>
+        <v>5220</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>5300</v>
+        <v>5240</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>5300</v>
+        <v>5260</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>5300</v>
+        <v>5260</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>5310</v>
+        <v>5270</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>5380</v>
+        <v>5270</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>5500</v>
+        <v>5290</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>5680</v>
+        <v>5320</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>5890</v>
+        <v>5370</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>6070</v>
+        <v>5420</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>6260</v>
+        <v>5490</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>6460</v>
+        <v>5580</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>6620</v>
+        <v>5680</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>6740</v>
+        <v>5740</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>6840</v>
+        <v>5820</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>6920</v>
+        <v>5900</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>6940</v>
+        <v>5940</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>6930</v>
+        <v>5940</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>6890</v>
+        <v>5940</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>6790</v>
+        <v>5910</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>6700</v>
+        <v>5850</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>6610</v>
+        <v>5770</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>6510</v>
+        <v>5680</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>6410</v>
+        <v>5550</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>6310</v>
+        <v>5440</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>6200</v>
+        <v>5330</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>6080</v>
+        <v>5220</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>5940</v>
+        <v>5120</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>5830</v>
+        <v>5030</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>5750</v>
+        <v>4960</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>5680</v>
+        <v>4880</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>5550</v>
+        <v>4750</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>5510</v>
+        <v>4710</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>5510</v>
+        <v>4670</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>5520</v>
+        <v>4650</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>5520</v>
+        <v>4650</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>5520</v>
+        <v>4650</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>5520</v>
+        <v>4660</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>5560</v>
+        <v>4710</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>5590</v>
+        <v>4760</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>5640</v>
+        <v>4820</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>5710</v>
+        <v>4920</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>5810</v>
+        <v>5060</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>5920</v>
+        <v>5210</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>6040</v>
+        <v>5380</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>6160</v>
+        <v>5560</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>6270</v>
+        <v>5750</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>6390</v>
+        <v>5930</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>6510</v>
+        <v>6090</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>6630</v>
+        <v>6230</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>6780</v>
+        <v>6380</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>6900</v>
+        <v>6500</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>7020</v>
+        <v>6610</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>7140</v>
+        <v>6700</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>7240</v>
+        <v>6790</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>7320</v>
+        <v>6850</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>7370</v>
+        <v>6880</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>7370</v>
+        <v>6880</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>7340</v>
+        <v>6840</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>7310</v>
+        <v>6790</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>7250</v>
+        <v>6740</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>7180</v>
+        <v>6660</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>7040</v>
+        <v>6570</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>6920</v>
+        <v>6480</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>6790</v>
+        <v>6390</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>6660</v>
+        <v>6260</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>6500</v>
+        <v>6080</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>6350</v>
+        <v>5960</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>6190</v>
+        <v>5830</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>6080</v>
+        <v>5740</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>5980</v>
+        <v>5680</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>5860</v>
+        <v>5590</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>5760</v>
+        <v>5500</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>5650</v>
+        <v>5400</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>5480</v>
+        <v>5160</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>5410</v>
+        <v>5100</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>5370</v>
+        <v>5050</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>5340</v>
+        <v>4990</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>5330</v>
+        <v>4920</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>5330</v>
+        <v>4870</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>5320</v>
+        <v>4830</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>5310</v>
+        <v>4790</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>5280</v>
+        <v>4770</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>5250</v>
+        <v>4730</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>5230</v>
+        <v>4700</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>5220</v>
+        <v>4680</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>5200</v>
+        <v>4650</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
-        <v>5200</v>
+        <v>4640</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
-        <v>5200</v>
+        <v>4630</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
-        <v>5210</v>
+        <v>4620</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>5230</v>
+        <v>4610</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>5230</v>
+        <v>4600</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>5230</v>
+        <v>4600</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>5230</v>
+        <v>4600</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>5230</v>
+        <v>4600</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>5290</v>
+        <v>4610</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>5370</v>
+        <v>4620</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>5470</v>
+        <v>4640</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>5620</v>
+        <v>4660</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>5780</v>
+        <v>4690</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>5950</v>
+        <v>4720</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>6130</v>
+        <v>4760</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>6370</v>
+        <v>4820</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>6550</v>
+        <v>4870</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>6680</v>
+        <v>4920</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>6800</v>
+        <v>4960</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>6920</v>
+        <v>5010</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>6970</v>
+        <v>5060</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>6970</v>
+        <v>5110</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>6940</v>
+        <v>5160</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>6840</v>
+        <v>5200</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>6730</v>
+        <v>5210</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>6610</v>
+        <v>5220</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B133">
-        <v>6470</v>
+        <v>5220</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B134">
-        <v>6330</v>
+        <v>5210</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B135">
-        <v>6170</v>
+        <v>5180</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B136">
-        <v>5980</v>
+        <v>5150</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B137">
-        <v>5800</v>
+        <v>5100</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B138">
-        <v>5590</v>
+        <v>5040</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B139">
-        <v>5420</v>
+        <v>4980</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B140">
-        <v>5260</v>
+        <v>4920</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B141">
-        <v>5140</v>
+        <v>4860</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B142">
-        <v>5020</v>
+        <v>4810</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B143">
-        <v>4940</v>
+        <v>4760</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B144">
-        <v>4920</v>
+        <v>4720</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B145">
-        <v>4940</v>
+        <v>4690</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B146">
-        <v>4960</v>
+        <v>4640</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B147">
-        <v>4980</v>
+        <v>4610</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B148">
-        <v>4990</v>
+        <v>4600</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B149">
-        <v>4990</v>
+        <v>4600</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B150">
-        <v>5020</v>
+        <v>4600</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B151">
-        <v>5030</v>
+        <v>4600</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B152">
-        <v>5030</v>
+        <v>4600</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B153">
-        <v>5040</v>
+        <v>4620</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B154">
-        <v>5100</v>
+        <v>4660</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B155">
-        <v>5150</v>
+        <v>4710</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B156">
-        <v>5220</v>
+        <v>4770</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B157">
-        <v>5330</v>
+        <v>4830</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B158">
-        <v>5460</v>
+        <v>4910</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B159">
-        <v>5600</v>
+        <v>4990</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B160">
-        <v>5750</v>
+        <v>5070</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B161">
-        <v>5920</v>
+        <v>5170</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B162">
-        <v>6090</v>
+        <v>5280</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B163">
-        <v>6250</v>
+        <v>5420</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B164">
-        <v>6400</v>
+        <v>5550</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B165">
-        <v>6560</v>
+        <v>5700</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B166">
-        <v>6740</v>
+        <v>5860</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B167">
-        <v>6890</v>
+        <v>6000</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B168">
-        <v>7020</v>
+        <v>6130</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B169">
-        <v>7150</v>
+        <v>6220</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B170">
-        <v>7250</v>
+        <v>6300</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B171">
-        <v>7330</v>
+        <v>6350</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B172">
-        <v>7370</v>
+        <v>6360</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B173">
-        <v>7370</v>
+        <v>6370</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B174">
-        <v>7330</v>
+        <v>6370</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B175">
-        <v>7290</v>
+        <v>6360</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B176">
-        <v>7230</v>
+        <v>6350</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B177">
-        <v>7150</v>
+        <v>6320</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B178">
-        <v>7020</v>
+        <v>6270</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B179">
-        <v>6890</v>
+        <v>6220</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B180">
-        <v>6770</v>
+        <v>6160</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B181">
-        <v>6640</v>
+        <v>6100</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B182">
-        <v>6470</v>
+        <v>6000</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B183">
-        <v>6320</v>
+        <v>5920</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B184">
-        <v>6170</v>
+        <v>5830</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B185">
-        <v>6060</v>
+        <v>5720</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B186">
-        <v>5970</v>
+        <v>5600</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B187">
-        <v>5860</v>
+        <v>5500</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B188">
-        <v>5740</v>
+        <v>5410</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B189">
-        <v>5620</v>
+        <v>5310</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46316.95833333334</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="B190">
-        <v>5500</v>
+        <v>5220</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46316.96875</v>
+        <v>46320.92708333334</v>
       </c>
       <c r="B191">
-        <v>5440</v>
+        <v>5140</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46316.97916666666</v>
+        <v>46320.9375</v>
       </c>
       <c r="B192">
-        <v>5390</v>
+        <v>5060</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +3656,72 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46316.98958333334</v>
+        <v>46320.94791666666</v>
       </c>
       <c r="B193">
-        <v>5340</v>
+        <v>4980</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46320.95833333334</v>
+      </c>
+      <c r="B194">
+        <v>4980</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46320.96875</v>
+      </c>
+      <c r="B195">
+        <v>4950</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46320.97916666666</v>
+      </c>
+      <c r="B196">
+        <v>4900</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46320.98958333334</v>
+      </c>
+      <c r="B197">
+        <v>4830</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
